--- a/model/PLS_Valuation_Model_FMAA_2026.xlsx
+++ b/model/PLS_Valuation_Model_FMAA_2026.xlsx
@@ -24,8 +24,9 @@
     <sheet name="Precedents" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="Football Field" sheetId="15" state="visible" r:id="rId17"/>
     <sheet name="ESG Value Bridge" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="Returns" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="Sources" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Downstream Option" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Returns" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Sources" sheetId="19" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="784">
   <si>
     <t xml:space="preserve">PLS GROUP LIMITED</t>
   </si>
@@ -192,6 +193,12 @@
     <t xml:space="preserve">Shared-value levers converted to A$/share of the target</t>
   </si>
   <si>
+    <t xml:space="preserve">Downstream Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The low-carbon downstream prize, sized and risked, held outside the target</t>
+  </si>
+  <si>
     <t xml:space="preserve">Returns</t>
   </si>
   <si>
@@ -1533,10 +1540,10 @@
     <t xml:space="preserve">Reference only. Transaction EV/EBITDA could not be sourced on a consistent basis, and applying a premium to our own DCF would be circular</t>
   </si>
   <si>
-    <t xml:space="preserve">Broker consensus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor consensus range, Aug-Sep 2026 - reference only</t>
+    <t xml:space="preserve">Broker target range (individual analysts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full individual spread across 17-20 analysts, Aug-Sep 2026. Vendor averages cluster A$4.50-5.70; our A$6.12 sits inside the individual range, below the most bullish. Reference only</t>
   </si>
   <si>
     <t xml:space="preserve">52-week trading range</t>
@@ -1701,13 +1708,25 @@
     <t xml:space="preserve">Shared value as a share of the target price</t>
   </si>
   <si>
-    <t xml:space="preserve">How to read this. The levers below the line are already inside the base case: they are embedded in the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A$569/t FY26 cost base and in the P2000 schedule the model assumes. The bridge does not add them on top of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the valuation - it isolates how much of the existing valuation depends on ESG-linked operating decisions.</t>
+    <t xml:space="preserve">THIS IS AN ATTRIBUTION, NOT AN ADDITION.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing on this sheet is added to the DCF. The ore-sorting and power benefits are already inside the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A$569/t FY26 unit cost and the A$575-625/t FY27 guidance that the model discounts, and the P2000 schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is already in the production profile. Adding them again would double-count the same cash flow once through</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCFF and once through narrative. What the bridge does is decompose the valuation we have already struck and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ask: how much of it exists because of ESG-linked operating decisions? The answer is A$0.43 per share - which</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is 4.6% of the A$6.12 target, but 67% of the A$0.64 of upside between the last close and that target.</t>
   </si>
   <si>
     <t xml:space="preserve">Two levers are deliberately carried at nil. The Calix mid-stream plant is real and opened in June 2026, but</t>
@@ -1722,6 +1741,108 @@
     <t xml:space="preserve">PLS's disclosed contracts, so we score it as unproven and value it at zero rather than manufacture a number.</t>
   </si>
   <si>
+    <t xml:space="preserve">The low-carbon downstream option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sized deliberately OUTSIDE the target price. This is where the shared value actually is.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why this sits outside the target. None of the three levers below is earning yet: the mid-stream plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">produces its first lithium phosphate in the September 2026 quarter, the POSCO joint venture is still ramping,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and we found no verified carbon-linked premium in any disclosed PLS contract. We size them here so the reader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">can see the prize, and we keep them out of the A$6.12 target so the recommendation does not depend on them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA A$m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPV A$m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-stream lithium phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kt of concentrate calcined in-house (20% of a 2Mtpa base), at the conversion margin retained rather than ceded to a third-party converter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POSCO JV equity earnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ktpa lithium hydroxide at Gwangyang, A$/t conversion margin, PLS share 18%. PLS holds an option to lift that stake to 30%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-carbon qualification premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kt of qualified volume at an A$/t premium. Illustrative only: no verified carbon-linked premium exists in PLS's disclosed contracts today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrisked total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risking and per-share value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant is built and commissioned; first product due Sep-qtr 2026. Scale-up beyond the demonstration unit is not funded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both trains built; Train 2 ramping. Lowest execution risk of the three.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directionally supported by EU and US policy, but unproven in PLS's contracts. Priced sceptically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risked downstream option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What this does to the recommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside in the target (A$/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared value already inside the target (A$/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of the upside attributable to shared value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus the downstream option, outside the target (A$/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target plus the risked option (A$/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The point of this sheet. Measured against the A$6.12 target, the shared-value bridge looks like a rounding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjustment. Measured against the UPSIDE - the A$0.64 per share between the last close and the target - it is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">most of the investment case. The market is paying for a lithium miner. We are paying for the operator whose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carbon position and downstream reach let it sell tonnes the others cannot. That gap is the recommendation.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Against the fund's benchmark and mandate</t>
   </si>
   <si>
@@ -1780,6 +1901,33 @@
   </si>
   <si>
     <t xml:space="preserve">Upside to bull divided by downside to bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stress test: does the bear case clear the price the market actually printed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52-week low, actually traded (A$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reached when spodumene was at its trough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our bear case (A$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear case premium to the traded low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the A$1.91 low the company held A$974m of cash and was loss-making. It now holds A$2,290m and earned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A$526m. Our bear case assumes prices revert to the marginal cost, P2000 is never sanctioned, Colina never</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proceeds and volumes stay flat for a decade - all at once. Reaching the old low from here would take</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conditions materially worse than the trough the market has already lived through.</t>
   </si>
   <si>
     <t xml:space="preserve">A long-only fund benchmarked to the ASX 200 needs positions where the asymmetry, not just the point estimate, is favourable.</t>
@@ -2264,7 +2412,7 @@
     <numFmt numFmtId="176" formatCode="0.00\x"/>
     <numFmt numFmtId="177" formatCode="0.0\x;\(0.0&quot;x)&quot;;\-"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2552,6 +2700,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFB3261E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FF5A6472"/>
       <name val="Arial"/>
@@ -2649,7 +2805,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="110">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3058,6 +3214,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3070,7 +3238,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3331,7 +3499,7 @@
     <tabColor rgb="FF0B2545"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C44"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3573,24 +3741,32 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="10" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="9" t="s">
         <v>55</v>
       </c>
+      <c r="C40" s="8" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="11" t="s">
-        <v>56</v>
+      <c r="B42" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3622,37 +3798,37 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="15"/>
       <c r="C6" s="61" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="61" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F6" s="61" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C7" s="62" t="n">
         <v>0.25</v>
@@ -3670,7 +3846,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$34</f>
@@ -3691,7 +3867,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C9" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$36</f>
@@ -3712,7 +3888,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C10" s="63" t="n">
         <f aca="false">'Scenario Engine'!$C$37</f>
@@ -3733,7 +3909,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C11" s="35" t="n">
         <f aca="false">'Scenario Engine'!$C$38</f>
@@ -3754,12 +3930,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C14" s="40" t="n">
         <f aca="false">'Scenario Engine'!I7</f>
@@ -3776,7 +3952,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="50" t="n">
         <f aca="false">'Scenario Engine'!I8</f>
@@ -3793,7 +3969,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C16" s="50" t="n">
         <f aca="false">'Scenario Engine'!I10</f>
@@ -3810,7 +3986,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C17" s="50" t="n">
         <f aca="false">'Scenario Engine'!I15</f>
@@ -3827,15 +4003,15 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20" s="67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D20" s="67"/>
       <c r="E20" s="67"/>
@@ -3845,10 +4021,10 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" s="67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D21" s="67"/>
       <c r="E21" s="67"/>
@@ -3858,10 +4034,10 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="67" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D22" s="67"/>
       <c r="E22" s="67"/>
@@ -3901,22 +4077,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -3929,7 +4105,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C7" s="69" t="n">
         <v>0.0788</v>
@@ -4074,12 +4250,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="19" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -4092,51 +4268,51 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="37" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I17" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L17" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M17" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N17" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O17" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F18" s="46" t="n">
         <f aca="false">'Scenario Engine'!F42</f>
@@ -4181,7 +4357,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F19" s="48" t="n">
         <f aca="false">'Scenario Engine'!F44</f>
@@ -4226,7 +4402,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F20" s="48" t="n">
         <f aca="false">'Scenario Engine'!F45</f>
@@ -4271,7 +4447,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F21" s="49" t="n">
         <f aca="false">'Scenario Engine'!F58</f>
@@ -4316,7 +4492,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F22" s="50" t="n">
         <f aca="false">F18/1000*F19*(1-'Revenue Build'!F20)*(1-Assumptions!$C$42)*(1-Assumptions!$C$31)*F21</f>
@@ -4361,7 +4537,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F23" s="50" t="n">
         <f aca="false">F18/1000*F20*(1-Assumptions!$C$31)*F21</f>
@@ -4406,7 +4582,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C25" s="23" t="n">
         <f aca="false">SUM(F22:O22)+O22*(1+Assumptions!$C$36)/(Assumptions!$C$33-Assumptions!$C$36)</f>
@@ -4415,7 +4591,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C26" s="23" t="n">
         <f aca="false">SUM(F23:O23)+O23*(1+Assumptions!$C$36)/(Assumptions!$C$33-Assumptions!$C$36)</f>
@@ -4424,7 +4600,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="19" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -4437,7 +4613,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="68" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C29" s="73" t="n">
         <v>-0.2</v>
@@ -4582,12 +4758,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -4622,42 +4798,42 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="68" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F6" s="68" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G6" s="68" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>9800</v>
@@ -4674,12 +4850,12 @@
         <v>3.04347826086957</v>
       </c>
       <c r="G7" s="75" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C8" s="25" t="n">
         <v>1450</v>
@@ -4696,12 +4872,12 @@
         <v>0.427795031055901</v>
       </c>
       <c r="G8" s="75" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C9" s="25" t="n">
         <v>2600</v>
@@ -4718,12 +4894,12 @@
         <v>0.565217391304348</v>
       </c>
       <c r="G9" s="75" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>900</v>
@@ -4740,12 +4916,12 @@
         <v>0.111801242236025</v>
       </c>
       <c r="G10" s="75" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>260</v>
@@ -4762,12 +4938,12 @@
         <v>0.0403726708074534</v>
       </c>
       <c r="G11" s="75" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C12" s="25" t="n">
         <v>320</v>
@@ -4784,12 +4960,12 @@
         <v>0.084472049689441</v>
       </c>
       <c r="G12" s="75" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>180</v>
@@ -4806,12 +4982,12 @@
         <v>0.0279503105590062</v>
       </c>
       <c r="G13" s="75" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C14" s="25" t="n">
         <v>-900</v>
@@ -4828,12 +5004,12 @@
         <v>-0.279503105590062</v>
       </c>
       <c r="G14" s="75" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="66" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E15" s="76" t="n">
         <f aca="false">SUM(E7:E14)</f>
@@ -4846,7 +5022,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E16" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
@@ -4859,7 +5035,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E17" s="78" t="n">
         <f aca="false">E15+E16</f>
@@ -4872,7 +5048,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F18" s="80" t="n">
         <f aca="false">Assumptions!$C$11/F17-1</f>
@@ -4881,22 +5057,22 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4931,22 +5107,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -4959,39 +5135,39 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="68" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E7" s="68" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F7" s="68" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H7" s="68" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I7" s="68" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J7" s="68" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>312560</v>
@@ -5003,7 +5179,7 @@
         <v>50600</v>
       </c>
       <c r="G8" s="82" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H8" s="83" t="n">
         <v>17.38</v>
@@ -5012,15 +5188,15 @@
         <v>0.0431</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D9" s="25" t="n">
         <v>220530</v>
@@ -5041,15 +5217,15 @@
         <v>0.0355</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D10" s="25" t="n">
         <v>68680</v>
@@ -5070,15 +5246,15 @@
         <v>0.07</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D11" s="25" t="n">
         <v>17190</v>
@@ -5099,15 +5275,15 @@
         <v>0.0249</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D12" s="25" t="n">
         <v>10400</v>
@@ -5125,15 +5301,15 @@
         <v>15.5</v>
       </c>
       <c r="I12" s="84" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="85" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G13" s="86" t="n">
         <f aca="false">MEDIAN(G8:G12)</f>
@@ -5150,7 +5326,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="19" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -5163,7 +5339,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D16" s="50" t="n">
         <f aca="false">'Scenario Engine'!F50</f>
@@ -5172,7 +5348,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D17" s="83" t="n">
         <v>8</v>
@@ -5180,7 +5356,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D18" s="83" t="n">
         <v>11</v>
@@ -5188,7 +5364,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D19" s="87" t="n">
         <f aca="false">(D16*D17+Assumptions!$C$21)/Assumptions!$C$12</f>
@@ -5197,7 +5373,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D20" s="87" t="n">
         <f aca="false">(D16*D18+Assumptions!$C$21)/Assumptions!$C$12</f>
@@ -5206,7 +5382,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="85" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D21" s="88" t="n">
         <f aca="false">AVERAGE(D19,D20)</f>
@@ -5215,32 +5391,32 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -5273,202 +5449,202 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="68" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F6" s="68" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G6" s="68" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G7" s="75" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G8" s="75" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G9" s="75" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G10" s="75" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G11" s="75" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G12" s="75" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G13" s="75" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G14" s="75" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="19" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -5478,7 +5654,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E17" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
@@ -5487,18 +5663,18 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>0.266</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="85" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E19" s="88" t="n">
         <f aca="false">E17*(1+E18)</f>
@@ -5507,32 +5683,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -5565,42 +5741,42 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="68" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F6" s="68" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G6" s="68" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C7" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
@@ -5618,12 +5794,12 @@
         <v>0.6</v>
       </c>
       <c r="G7" s="75" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C8" s="53" t="n">
         <f aca="false">'Scenario Summary'!$F$10</f>
@@ -5641,12 +5817,12 @@
         <v>0</v>
       </c>
       <c r="G8" s="75" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C9" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$37</f>
@@ -5664,12 +5840,12 @@
         <v>0</v>
       </c>
       <c r="G9" s="75" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C10" s="53" t="n">
         <f aca="false">'Trading Comps'!$D$19</f>
@@ -5687,12 +5863,12 @@
         <v>0.4</v>
       </c>
       <c r="G10" s="75" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C11" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
@@ -5710,33 +5886,33 @@
         <v>0</v>
       </c>
       <c r="G11" s="75" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C12" s="21" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>5.7</v>
+        <v>6.83</v>
       </c>
       <c r="E12" s="87" t="n">
         <f aca="false">AVERAGE(C12:D12)</f>
-        <v>5.1</v>
+        <v>4.665</v>
       </c>
       <c r="F12" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="75" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C13" s="21" t="n">
         <v>1.91</v>
@@ -5752,12 +5928,12 @@
         <v>0</v>
       </c>
       <c r="G13" s="75" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F14" s="35" t="n">
         <f aca="false">SUM(F7:F13)</f>
@@ -5766,7 +5942,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="89" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C16" s="90" t="n">
         <f aca="false">SUMPRODUCT(E7:E13,F7:F13)/SUM(F7:F13)</f>
@@ -5775,7 +5951,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C17" s="53" t="n">
         <f aca="false">Assumptions!$C$11</f>
@@ -5784,7 +5960,7 @@
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C18" s="91" t="n">
         <f aca="false">C16/C17-1</f>
@@ -5793,7 +5969,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">'Income Statement'!F25</f>
@@ -5802,7 +5978,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="66" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C20" s="92" t="n">
         <f aca="false">C18+C19</f>
@@ -5811,7 +5987,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C21" s="24" t="n">
         <f aca="false">Assumptions!$C$58</f>
@@ -5820,7 +5996,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="66" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C22" s="92" t="n">
         <f aca="false">C20-C21</f>
@@ -5829,7 +6005,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -5849,7 +6025,7 @@
     <tabColor rgb="FF0E7C7B"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:O41"/>
+  <dimension ref="B2:O46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -5862,27 +6038,27 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="66" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F7" s="46" t="n">
         <f aca="false">'Scenario Engine'!F42</f>
@@ -5927,7 +6103,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F8" s="49" t="n">
         <f aca="false">'Scenario Engine'!F58</f>
@@ -5972,7 +6148,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F9" s="93" t="n">
         <f aca="false">F7/1000*(1-Assumptions!$C$31)*F8</f>
@@ -6017,7 +6193,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D11" s="94" t="n">
         <f aca="false">SUM(F9:O9)+O9*(1+Assumptions!$C$36)/(Assumptions!$C$33-Assumptions!$C$36)</f>
@@ -6026,33 +6202,33 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="95" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C13" s="95" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="9" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C14" s="75" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>30</v>
@@ -6066,18 +6242,18 @@
         <v>0.190604271583364</v>
       </c>
       <c r="G14" s="96" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H14" s="75" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C15" s="75" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>18</v>
@@ -6091,84 +6267,84 @@
         <v>0.114362562950018</v>
       </c>
       <c r="G15" s="97" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H15" s="75" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="C16" s="75" t="s">
+        <v>532</v>
+      </c>
+      <c r="D16" s="98" t="s">
+        <v>533</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="F16" s="98" t="s">
+        <v>533</v>
+      </c>
+      <c r="G16" s="97" t="s">
         <v>529</v>
       </c>
-      <c r="C16" s="75" t="s">
-        <v>530</v>
-      </c>
-      <c r="D16" s="98" t="s">
-        <v>531</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="F16" s="98" t="s">
-        <v>531</v>
-      </c>
-      <c r="G16" s="97" t="s">
-        <v>527</v>
-      </c>
       <c r="H16" s="75" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="C17" s="75" t="s">
+        <v>537</v>
+      </c>
+      <c r="D17" s="98" t="s">
+        <v>533</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="C17" s="75" t="s">
-        <v>535</v>
-      </c>
-      <c r="D17" s="98" t="s">
-        <v>531</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>532</v>
-      </c>
       <c r="F17" s="98" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G17" s="97" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H17" s="75" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C18" s="75" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D18" s="98" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F18" s="98" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G18" s="99" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H18" s="75" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="66" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D19" s="76" t="n">
         <f aca="false">SUM(D14:D18)</f>
@@ -6185,7 +6361,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="19" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
@@ -6196,29 +6372,29 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D22" s="25" t="n">
         <v>2600</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D23" s="36" t="n">
         <v>2</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D24" s="23" t="n">
         <f aca="false">D22*(1-1/(1+Assumptions!$C$33)^D23)</f>
@@ -6227,7 +6403,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D25" s="59" t="n">
         <f aca="false">D24/Assumptions!$C$12</f>
@@ -6236,7 +6412,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="19" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -6247,7 +6423,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D28" s="53" t="n">
         <f aca="false">F19</f>
@@ -6256,7 +6432,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D29" s="53" t="n">
         <f aca="false">D25</f>
@@ -6265,7 +6441,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="66" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D30" s="101" t="n">
         <f aca="false">D28+D29</f>
@@ -6274,7 +6450,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D31" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
@@ -6283,7 +6459,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D32" s="80" t="n">
         <f aca="false">D30/D31</f>
@@ -6291,41 +6467,64 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="11" t="s">
-        <v>554</v>
+      <c r="B34" s="102" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="11" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="11" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="11"/>
+      <c r="B37" s="11" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="11" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="11" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="11" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="11" t="s">
-        <v>560</v>
+      <c r="B41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="11" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="11" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="11" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="11" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -6342,206 +6541,369 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF8FBF3F"/>
+    <tabColor rgb="FF0E7C7B"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F27"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="7" style="0" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="9" style="0" width="11.5"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>51</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="s">
-        <v>562</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="B6" s="13" t="s">
+        <v>569</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="24" t="n">
-        <f aca="false">Assumptions!$C$58</f>
-        <v>0.059</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>563</v>
+      <c r="B7" s="13" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>564</v>
+      <c r="B8" s="13" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="C9" s="26" t="n">
-        <v>0.02</v>
+      <c r="B9" s="13" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="19" t="s">
-        <v>566</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="C12" s="53" t="n">
+      <c r="B11" s="68" t="s">
+        <v>517</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>573</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>574</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>575</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>576</v>
+      </c>
+      <c r="G11" s="68" t="s">
+        <v>577</v>
+      </c>
+      <c r="H11" s="68" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>400</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>480</v>
+      </c>
+      <c r="E12" s="50" t="n">
+        <f aca="false">C12*D12/1000</f>
+        <v>192</v>
+      </c>
+      <c r="F12" s="83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <f aca="false">E12*F12</f>
+        <v>1536</v>
+      </c>
+      <c r="H12" s="75" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <f aca="false">C13*D13/1000*0.18</f>
+        <v>32.508</v>
+      </c>
+      <c r="F13" s="83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <f aca="false">E13*F13</f>
+        <v>260.064</v>
+      </c>
+      <c r="H13" s="75" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="E14" s="50" t="n">
+        <f aca="false">C14*D14/1000</f>
+        <v>75</v>
+      </c>
+      <c r="F14" s="83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <f aca="false">E14*F14</f>
+        <v>600</v>
+      </c>
+      <c r="H14" s="75" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="66" t="s">
+        <v>584</v>
+      </c>
+      <c r="E15" s="76" t="n">
+        <f aca="false">SUM(E12:E14)</f>
+        <v>299.508</v>
+      </c>
+      <c r="G15" s="76" t="n">
+        <f aca="false">SUM(G12:G14)</f>
+        <v>2396.064</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="68" t="s">
+        <v>517</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>577</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>586</v>
+      </c>
+      <c r="E18" s="68" t="s">
+        <v>355</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="C19" s="50" t="n">
+        <f aca="false">G12</f>
+        <v>1536</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E19" s="50" t="n">
+        <f aca="false">C19*D19</f>
+        <v>691.2</v>
+      </c>
+      <c r="F19" s="87" t="n">
+        <f aca="false">E19/Assumptions!$C$12</f>
+        <v>0.214658385093168</v>
+      </c>
+      <c r="G19" s="75" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C20" s="50" t="n">
+        <f aca="false">G13</f>
+        <v>260.064</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E20" s="50" t="n">
+        <f aca="false">C20*D20</f>
+        <v>182.0448</v>
+      </c>
+      <c r="F20" s="87" t="n">
+        <f aca="false">E20/Assumptions!$C$12</f>
+        <v>0.056535652173913</v>
+      </c>
+      <c r="G20" s="75" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="C21" s="50" t="n">
+        <f aca="false">G14</f>
+        <v>600</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E21" s="50" t="n">
+        <f aca="false">C21*D21</f>
+        <v>150</v>
+      </c>
+      <c r="F21" s="87" t="n">
+        <f aca="false">E21/Assumptions!$C$12</f>
+        <v>0.046583850931677</v>
+      </c>
+      <c r="G21" s="75" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E22" s="78" t="n">
+        <f aca="false">SUM(E19:E21)</f>
+        <v>1023.2448</v>
+      </c>
+      <c r="F22" s="79" t="n">
+        <f aca="false">SUM(F19:F21)</f>
+        <v>0.317777888198758</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="D25" s="53" t="n">
+        <f aca="false">'Football Field'!$C$16</f>
+        <v>6.12330732138286</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D26" s="53" t="n">
         <f aca="false">Assumptions!$C$11</f>
         <v>5.48</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="C13" s="53" t="n">
-        <f aca="false">'Football Field'!$C$16</f>
-        <v>6.12330732138286</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="C14" s="24" t="n">
-        <f aca="false">'Football Field'!$C$18</f>
-        <v>0.117391846967675</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="C15" s="24" t="n">
-        <f aca="false">'Income Statement'!F25</f>
-        <v>0.0166988356870835</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <f aca="false">'Football Field'!$C$20</f>
-        <v>0.134090682654759</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <f aca="false">C16-C7</f>
-        <v>0.0750906826547586</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="C20" s="53" t="n">
-        <f aca="false">'Scenario Engine'!$C$37</f>
-        <v>2.26471244820927</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="C21" s="53" t="n">
-        <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="C22" s="53" t="n">
-        <f aca="false">'Scenario Engine'!$C$107</f>
-        <v>8.93434732226067</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="C23" s="24" t="n">
-        <f aca="false">C20/Assumptions!$C$11-1</f>
-        <v>-0.586731305071302</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="C24" s="24" t="n">
-        <f aca="false">C22/Assumptions!$C$11-1</f>
-        <v>0.630355350777494</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="C25" s="102" t="n">
-        <f aca="false">IFERROR(ABS(C24/C23),0)</f>
-        <v>1.07435097689374</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>580</v>
-      </c>
-    </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="s">
-        <v>581</v>
+      <c r="B27" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="D27" s="87" t="n">
+        <f aca="false">D25-D26</f>
+        <v>0.64330732138286</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="D28" s="53" t="n">
+        <f aca="false">'ESG Value Bridge'!$D$30</f>
+        <v>0.431297729098335</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="66" t="s">
+        <v>594</v>
+      </c>
+      <c r="D29" s="103" t="n">
+        <f aca="false">D28/D27</f>
+        <v>0.670438085752254</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="D30" s="53" t="n">
+        <f aca="false">F22</f>
+        <v>0.317777888198758</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="66" t="s">
+        <v>596</v>
+      </c>
+      <c r="D31" s="104" t="n">
+        <f aca="false">D25+F22</f>
+        <v>6.44108520958162</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="11" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="11" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="11" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="11" t="s">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -6556,6 +6918,280 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF8FBF3F"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:F37"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="7" style="0" width="11.5"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="13" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <f aca="false">Assumptions!$C$58</f>
+        <v>0.059</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="C12" s="53" t="n">
+        <f aca="false">Assumptions!$C$11</f>
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C13" s="53" t="n">
+        <f aca="false">'Football Field'!$C$16</f>
+        <v>6.12330732138286</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <f aca="false">'Football Field'!$C$18</f>
+        <v>0.117391846967675</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="C15" s="24" t="n">
+        <f aca="false">'Income Statement'!F25</f>
+        <v>0.0166988356870835</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="C16" s="35" t="n">
+        <f aca="false">'Football Field'!$C$20</f>
+        <v>0.134090682654759</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="C17" s="35" t="n">
+        <f aca="false">C16-C7</f>
+        <v>0.0750906826547586</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="C20" s="53" t="n">
+        <f aca="false">'Scenario Engine'!$C$37</f>
+        <v>2.26471244820927</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="C21" s="53" t="n">
+        <f aca="false">'Scenario Engine'!$C$72</f>
+        <v>6.4975771608969</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="C22" s="53" t="n">
+        <f aca="false">'Scenario Engine'!$C$107</f>
+        <v>8.93434732226067</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <f aca="false">C20/Assumptions!$C$11-1</f>
+        <v>-0.586731305071302</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <f aca="false">C22/Assumptions!$C$11-1</f>
+        <v>0.630355350777494</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="C25" s="105" t="n">
+        <f aca="false">IFERROR(ABS(C24/C23),0)</f>
+        <v>1.07435097689374</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="19" t="s">
+        <v>621</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="C29" s="53" t="n">
+        <f aca="false">C20</f>
+        <v>2.26471244820927</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C30" s="35" t="n">
+        <f aca="false">C29/C28-1</f>
+        <v>0.185713323669774</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="11" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="11" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="11" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="11" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="11" t="s">
+        <v>630</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF5A6472"/>
@@ -6574,733 +7210,733 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>582</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>583</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="68" t="s">
-        <v>584</v>
+        <v>633</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>585</v>
+        <v>634</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>586</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="103" t="s">
-        <v>587</v>
-      </c>
-      <c r="D7" s="104" t="s">
-        <v>588</v>
+        <v>92</v>
+      </c>
+      <c r="C7" s="106" t="s">
+        <v>636</v>
+      </c>
+      <c r="D7" s="107" t="s">
+        <v>637</v>
       </c>
       <c r="E7" s="75" t="s">
-        <v>589</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>590</v>
-      </c>
-      <c r="D8" s="104" t="s">
-        <v>588</v>
+        <v>94</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>639</v>
+      </c>
+      <c r="D8" s="107" t="s">
+        <v>637</v>
       </c>
       <c r="E8" s="75" t="s">
-        <v>591</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="103" t="s">
-        <v>592</v>
-      </c>
-      <c r="D9" s="104" t="s">
-        <v>588</v>
+        <v>95</v>
+      </c>
+      <c r="C9" s="106" t="s">
+        <v>641</v>
+      </c>
+      <c r="D9" s="107" t="s">
+        <v>637</v>
       </c>
       <c r="E9" s="75" t="s">
-        <v>593</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="C10" s="103" t="s">
-        <v>595</v>
-      </c>
-      <c r="D10" s="104" t="s">
-        <v>588</v>
+        <v>643</v>
+      </c>
+      <c r="C10" s="106" t="s">
+        <v>644</v>
+      </c>
+      <c r="D10" s="107" t="s">
+        <v>637</v>
       </c>
       <c r="E10" s="75" t="s">
-        <v>596</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="C11" s="103" t="s">
-        <v>598</v>
-      </c>
-      <c r="D11" s="105" t="s">
-        <v>599</v>
+        <v>646</v>
+      </c>
+      <c r="C11" s="106" t="s">
+        <v>647</v>
+      </c>
+      <c r="D11" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E11" s="75" t="s">
-        <v>600</v>
+        <v>649</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="C12" s="103" t="s">
-        <v>602</v>
-      </c>
-      <c r="D12" s="105" t="s">
-        <v>599</v>
+        <v>650</v>
+      </c>
+      <c r="C12" s="106" t="s">
+        <v>651</v>
+      </c>
+      <c r="D12" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>603</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="C13" s="103" t="s">
-        <v>605</v>
-      </c>
-      <c r="D13" s="105" t="s">
-        <v>599</v>
+        <v>653</v>
+      </c>
+      <c r="C13" s="106" t="s">
+        <v>654</v>
+      </c>
+      <c r="D13" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E13" s="75" t="s">
-        <v>606</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="C14" s="103" t="s">
-        <v>608</v>
-      </c>
-      <c r="D14" s="106" t="s">
-        <v>609</v>
+        <v>656</v>
+      </c>
+      <c r="C14" s="106" t="s">
+        <v>657</v>
+      </c>
+      <c r="D14" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E14" s="75" t="s">
-        <v>610</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="C15" s="103" t="s">
-        <v>612</v>
-      </c>
-      <c r="D15" s="106" t="s">
-        <v>609</v>
+        <v>660</v>
+      </c>
+      <c r="C15" s="106" t="s">
+        <v>661</v>
+      </c>
+      <c r="D15" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E15" s="75" t="s">
-        <v>613</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="C16" s="103" t="s">
-        <v>615</v>
-      </c>
-      <c r="D16" s="106" t="s">
-        <v>609</v>
+        <v>663</v>
+      </c>
+      <c r="C16" s="106" t="s">
+        <v>664</v>
+      </c>
+      <c r="D16" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E16" s="75" t="s">
-        <v>616</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="C17" s="103" t="s">
-        <v>618</v>
-      </c>
-      <c r="D17" s="106" t="s">
-        <v>609</v>
+        <v>666</v>
+      </c>
+      <c r="C17" s="106" t="s">
+        <v>667</v>
+      </c>
+      <c r="D17" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E17" s="75" t="s">
-        <v>619</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="C18" s="103" t="s">
-        <v>621</v>
-      </c>
-      <c r="D18" s="106" t="s">
-        <v>609</v>
+        <v>669</v>
+      </c>
+      <c r="C18" s="106" t="s">
+        <v>670</v>
+      </c>
+      <c r="D18" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E18" s="75" t="s">
-        <v>616</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="C19" s="103" t="s">
-        <v>623</v>
-      </c>
-      <c r="D19" s="106" t="s">
-        <v>609</v>
+        <v>671</v>
+      </c>
+      <c r="C19" s="106" t="s">
+        <v>672</v>
+      </c>
+      <c r="D19" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E19" s="75" t="s">
-        <v>624</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="C20" s="103" t="s">
-        <v>626</v>
-      </c>
-      <c r="D20" s="106" t="s">
-        <v>609</v>
+        <v>674</v>
+      </c>
+      <c r="C20" s="106" t="s">
+        <v>675</v>
+      </c>
+      <c r="D20" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E20" s="75" t="s">
-        <v>627</v>
+        <v>676</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="C21" s="103" t="s">
-        <v>629</v>
-      </c>
-      <c r="D21" s="106" t="s">
-        <v>609</v>
+        <v>677</v>
+      </c>
+      <c r="C21" s="106" t="s">
+        <v>678</v>
+      </c>
+      <c r="D21" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E21" s="75" t="s">
-        <v>630</v>
+        <v>679</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="C22" s="103" t="s">
-        <v>632</v>
-      </c>
-      <c r="D22" s="106" t="s">
-        <v>609</v>
+        <v>680</v>
+      </c>
+      <c r="C22" s="106" t="s">
+        <v>681</v>
+      </c>
+      <c r="D22" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E22" s="75" t="s">
-        <v>633</v>
+        <v>682</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="C23" s="103" t="s">
-        <v>635</v>
-      </c>
-      <c r="D23" s="106" t="s">
-        <v>609</v>
+        <v>683</v>
+      </c>
+      <c r="C23" s="106" t="s">
+        <v>684</v>
+      </c>
+      <c r="D23" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E23" s="75" t="s">
-        <v>636</v>
+        <v>685</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="C24" s="103" t="s">
-        <v>638</v>
-      </c>
-      <c r="D24" s="106" t="s">
-        <v>609</v>
+        <v>686</v>
+      </c>
+      <c r="C24" s="106" t="s">
+        <v>687</v>
+      </c>
+      <c r="D24" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E24" s="75" t="s">
-        <v>639</v>
+        <v>688</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="C25" s="103" t="s">
-        <v>641</v>
-      </c>
-      <c r="D25" s="106" t="s">
-        <v>609</v>
+        <v>689</v>
+      </c>
+      <c r="C25" s="106" t="s">
+        <v>690</v>
+      </c>
+      <c r="D25" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E25" s="75" t="s">
-        <v>642</v>
+        <v>691</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="C26" s="103" t="s">
-        <v>644</v>
-      </c>
-      <c r="D26" s="106" t="s">
-        <v>645</v>
+        <v>692</v>
+      </c>
+      <c r="C26" s="106" t="s">
+        <v>693</v>
+      </c>
+      <c r="D26" s="109" t="s">
+        <v>694</v>
       </c>
       <c r="E26" s="75" t="s">
-        <v>646</v>
+        <v>695</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="C27" s="103" t="s">
-        <v>648</v>
-      </c>
-      <c r="D27" s="106" t="s">
-        <v>645</v>
+        <v>696</v>
+      </c>
+      <c r="C27" s="106" t="s">
+        <v>697</v>
+      </c>
+      <c r="D27" s="109" t="s">
+        <v>694</v>
       </c>
       <c r="E27" s="75" t="s">
-        <v>649</v>
+        <v>698</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>650</v>
-      </c>
-      <c r="C28" s="103" t="s">
-        <v>651</v>
-      </c>
-      <c r="D28" s="106" t="s">
-        <v>645</v>
+        <v>699</v>
+      </c>
+      <c r="C28" s="106" t="s">
+        <v>700</v>
+      </c>
+      <c r="D28" s="109" t="s">
+        <v>694</v>
       </c>
       <c r="E28" s="75" t="s">
-        <v>652</v>
+        <v>701</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="C29" s="103" t="s">
-        <v>654</v>
-      </c>
-      <c r="D29" s="106" t="s">
-        <v>645</v>
+        <v>702</v>
+      </c>
+      <c r="C29" s="106" t="s">
+        <v>703</v>
+      </c>
+      <c r="D29" s="109" t="s">
+        <v>694</v>
       </c>
       <c r="E29" s="75" t="s">
-        <v>655</v>
+        <v>704</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="C30" s="103" t="s">
-        <v>657</v>
-      </c>
-      <c r="D30" s="106" t="s">
-        <v>609</v>
+        <v>705</v>
+      </c>
+      <c r="C30" s="106" t="s">
+        <v>706</v>
+      </c>
+      <c r="D30" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E30" s="75" t="s">
-        <v>658</v>
+        <v>707</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="C31" s="103" t="s">
-        <v>660</v>
-      </c>
-      <c r="D31" s="106" t="s">
-        <v>609</v>
+        <v>708</v>
+      </c>
+      <c r="C31" s="106" t="s">
+        <v>709</v>
+      </c>
+      <c r="D31" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E31" s="75" t="s">
-        <v>661</v>
+        <v>710</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="C32" s="103" t="s">
-        <v>663</v>
-      </c>
-      <c r="D32" s="106" t="s">
-        <v>609</v>
+        <v>711</v>
+      </c>
+      <c r="C32" s="106" t="s">
+        <v>712</v>
+      </c>
+      <c r="D32" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E32" s="75" t="s">
-        <v>664</v>
+        <v>713</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="C33" s="103" t="s">
-        <v>666</v>
-      </c>
-      <c r="D33" s="106" t="s">
-        <v>645</v>
+        <v>714</v>
+      </c>
+      <c r="C33" s="106" t="s">
+        <v>715</v>
+      </c>
+      <c r="D33" s="109" t="s">
+        <v>694</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>667</v>
+        <v>716</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="C34" s="103" t="s">
-        <v>669</v>
-      </c>
-      <c r="D34" s="106" t="s">
-        <v>609</v>
+        <v>717</v>
+      </c>
+      <c r="C34" s="106" t="s">
+        <v>718</v>
+      </c>
+      <c r="D34" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E34" s="75" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="C35" s="103" t="s">
-        <v>672</v>
-      </c>
-      <c r="D35" s="106" t="s">
-        <v>609</v>
+        <v>720</v>
+      </c>
+      <c r="C35" s="106" t="s">
+        <v>721</v>
+      </c>
+      <c r="D35" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E35" s="75" t="s">
-        <v>673</v>
+        <v>722</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="C36" s="103" t="s">
-        <v>675</v>
-      </c>
-      <c r="D36" s="106" t="s">
-        <v>609</v>
+        <v>723</v>
+      </c>
+      <c r="C36" s="106" t="s">
+        <v>724</v>
+      </c>
+      <c r="D36" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E36" s="75" t="s">
-        <v>676</v>
+        <v>725</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="C37" s="103" t="s">
-        <v>678</v>
-      </c>
-      <c r="D37" s="106" t="s">
-        <v>609</v>
+        <v>726</v>
+      </c>
+      <c r="C37" s="106" t="s">
+        <v>727</v>
+      </c>
+      <c r="D37" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E37" s="75" t="s">
-        <v>679</v>
+        <v>728</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="C38" s="103" t="s">
-        <v>681</v>
-      </c>
-      <c r="D38" s="106" t="s">
-        <v>609</v>
+        <v>729</v>
+      </c>
+      <c r="C38" s="106" t="s">
+        <v>730</v>
+      </c>
+      <c r="D38" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E38" s="75" t="s">
-        <v>682</v>
+        <v>731</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="C39" s="103" t="s">
-        <v>684</v>
-      </c>
-      <c r="D39" s="106" t="s">
-        <v>609</v>
+        <v>732</v>
+      </c>
+      <c r="C39" s="106" t="s">
+        <v>733</v>
+      </c>
+      <c r="D39" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E39" s="75" t="s">
-        <v>685</v>
+        <v>734</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>686</v>
-      </c>
-      <c r="C40" s="103" t="s">
-        <v>687</v>
-      </c>
-      <c r="D40" s="106" t="s">
-        <v>609</v>
+        <v>735</v>
+      </c>
+      <c r="C40" s="106" t="s">
+        <v>736</v>
+      </c>
+      <c r="D40" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E40" s="75" t="s">
-        <v>688</v>
+        <v>737</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>689</v>
-      </c>
-      <c r="C41" s="103" t="s">
-        <v>690</v>
-      </c>
-      <c r="D41" s="106" t="s">
-        <v>609</v>
+        <v>738</v>
+      </c>
+      <c r="C41" s="106" t="s">
+        <v>739</v>
+      </c>
+      <c r="D41" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E41" s="75" t="s">
-        <v>691</v>
+        <v>740</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="C42" s="103" t="s">
-        <v>693</v>
-      </c>
-      <c r="D42" s="105" t="s">
-        <v>599</v>
+        <v>741</v>
+      </c>
+      <c r="C42" s="106" t="s">
+        <v>742</v>
+      </c>
+      <c r="D42" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E42" s="75" t="s">
-        <v>694</v>
+        <v>743</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="C43" s="103" t="s">
-        <v>696</v>
-      </c>
-      <c r="D43" s="105" t="s">
-        <v>599</v>
+        <v>744</v>
+      </c>
+      <c r="C43" s="106" t="s">
+        <v>745</v>
+      </c>
+      <c r="D43" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E43" s="75" t="s">
-        <v>697</v>
+        <v>746</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="C44" s="103" t="s">
-        <v>699</v>
-      </c>
-      <c r="D44" s="105" t="s">
-        <v>599</v>
+        <v>747</v>
+      </c>
+      <c r="C44" s="106" t="s">
+        <v>748</v>
+      </c>
+      <c r="D44" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E44" s="75" t="s">
-        <v>700</v>
+        <v>749</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="C45" s="103" t="s">
-        <v>702</v>
-      </c>
-      <c r="D45" s="105" t="s">
-        <v>599</v>
+        <v>750</v>
+      </c>
+      <c r="C45" s="106" t="s">
+        <v>751</v>
+      </c>
+      <c r="D45" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E45" s="75" t="s">
-        <v>703</v>
+        <v>752</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="C46" s="103" t="s">
-        <v>705</v>
-      </c>
-      <c r="D46" s="105" t="s">
-        <v>599</v>
+        <v>753</v>
+      </c>
+      <c r="C46" s="106" t="s">
+        <v>754</v>
+      </c>
+      <c r="D46" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E46" s="75" t="s">
-        <v>706</v>
+        <v>755</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="C47" s="103" t="s">
-        <v>708</v>
-      </c>
-      <c r="D47" s="105" t="s">
-        <v>599</v>
+        <v>756</v>
+      </c>
+      <c r="C47" s="106" t="s">
+        <v>757</v>
+      </c>
+      <c r="D47" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E47" s="75" t="s">
-        <v>709</v>
+        <v>758</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="C48" s="103" t="s">
-        <v>711</v>
-      </c>
-      <c r="D48" s="105" t="s">
-        <v>599</v>
+        <v>759</v>
+      </c>
+      <c r="C48" s="106" t="s">
+        <v>760</v>
+      </c>
+      <c r="D48" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E48" s="75" t="s">
-        <v>712</v>
+        <v>761</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="C49" s="103" t="s">
-        <v>714</v>
-      </c>
-      <c r="D49" s="105" t="s">
-        <v>599</v>
+        <v>762</v>
+      </c>
+      <c r="C49" s="106" t="s">
+        <v>763</v>
+      </c>
+      <c r="D49" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E49" s="75" t="s">
-        <v>715</v>
+        <v>764</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="C50" s="103" t="s">
-        <v>717</v>
-      </c>
-      <c r="D50" s="105" t="s">
-        <v>599</v>
+        <v>765</v>
+      </c>
+      <c r="C50" s="106" t="s">
+        <v>766</v>
+      </c>
+      <c r="D50" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E50" s="75" t="s">
-        <v>718</v>
+        <v>767</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="C51" s="103" t="s">
-        <v>720</v>
-      </c>
-      <c r="D51" s="105" t="s">
-        <v>599</v>
+        <v>768</v>
+      </c>
+      <c r="C51" s="106" t="s">
+        <v>769</v>
+      </c>
+      <c r="D51" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E51" s="75" t="s">
-        <v>721</v>
+        <v>770</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="C52" s="103" t="s">
-        <v>723</v>
-      </c>
-      <c r="D52" s="105" t="s">
-        <v>599</v>
+        <v>771</v>
+      </c>
+      <c r="C52" s="106" t="s">
+        <v>772</v>
+      </c>
+      <c r="D52" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E52" s="75" t="s">
-        <v>724</v>
+        <v>773</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="C53" s="103" t="s">
-        <v>726</v>
-      </c>
-      <c r="D53" s="105" t="s">
-        <v>599</v>
+        <v>774</v>
+      </c>
+      <c r="C53" s="106" t="s">
+        <v>775</v>
+      </c>
+      <c r="D53" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E53" s="75" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="C54" s="103" t="s">
-        <v>728</v>
-      </c>
-      <c r="D54" s="105" t="s">
-        <v>599</v>
+        <v>776</v>
+      </c>
+      <c r="C54" s="106" t="s">
+        <v>777</v>
+      </c>
+      <c r="D54" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E54" s="75" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="11" t="s">
-        <v>729</v>
+        <v>778</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="11" t="s">
-        <v>730</v>
+        <v>779</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="11" t="s">
-        <v>731</v>
+        <v>780</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="11" t="s">
-        <v>732</v>
+        <v>781</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="11" t="s">
-        <v>733</v>
+        <v>782</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="11" t="s">
-        <v>734</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -7333,33 +7969,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S5" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -7368,30 +8004,30 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">MATCH($C$7,$S$3:$S$5,0)</f>
         <v>2</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -7400,29 +8036,29 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" s="21" t="n">
         <v>5.48</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>3220</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13" s="23" t="n">
         <f aca="false">C11*C12</f>
@@ -7431,7 +8067,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>6.81</v>
@@ -7439,7 +8075,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15" s="21" t="n">
         <v>1.91</v>
@@ -7447,19 +8083,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" s="24" t="n">
         <f aca="false">C11/C15-1</f>
         <v>1.86910994764398</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -7468,29 +8104,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>2290</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" s="25" t="n">
         <v>828</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C21" s="23" t="n">
         <f aca="false">C19-C20</f>
@@ -7499,7 +8135,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C22" s="23" t="n">
         <f aca="false">C13-C21</f>
@@ -7508,18 +8144,18 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C23" s="26" t="n">
         <v>0.1</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -7528,40 +8164,40 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C26" s="27" t="n">
         <v>0.05</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C27" s="27" t="n">
         <v>0.06</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28" s="28" t="n">
         <v>0.73</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C29" s="29" t="n">
         <f aca="false">C26+C28*C27</f>
@@ -7570,29 +8206,29 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C30" s="27" t="n">
         <v>0.0625</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C31" s="27" t="n">
         <v>0.3</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C32" s="30" t="n">
         <f aca="false">C30*(1-C31)</f>
@@ -7601,7 +8237,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">(1-C23)*C29+C23*C32</f>
@@ -7610,7 +8246,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
@@ -7619,27 +8255,27 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C36" s="29" t="n">
         <f aca="false">CHOOSE($C$8,0.015,0.025,0.03)</f>
         <v>0.025</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
@@ -7648,62 +8284,62 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C40" s="25" t="n">
         <v>95</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C41" s="26" t="n">
         <v>0.025</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C42" s="26" t="n">
         <v>0.05</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C43" s="26" t="n">
         <v>0.85</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C44" s="26" t="n">
         <v>0.08</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
@@ -7712,40 +8348,40 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C47" s="32" t="n">
         <v>446</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C48" s="32" t="n">
         <v>214.2</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C49" s="33" t="n">
         <v>0.75</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C50" s="34" t="n">
         <f aca="false">C47*C49</f>
@@ -7754,40 +8390,40 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C51" s="27" t="n">
         <v>0.0119</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C52" s="26" t="n">
         <v>0.765</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C53" s="27" t="n">
         <v>0.052</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C54" s="35" t="n">
         <f aca="false">C51*C52/C53</f>
@@ -7796,18 +8432,18 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C55" s="36" t="n">
         <v>25</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
@@ -7816,29 +8452,29 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C58" s="26" t="n">
         <v>0.059</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C59" s="26" t="n">
         <v>0.079</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C60" s="24" t="n">
         <f aca="false">C59-C58</f>
@@ -7847,7 +8483,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7883,66 +8519,66 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -7960,7 +8596,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F8" s="22" t="n">
         <v>880</v>
@@ -7995,7 +8631,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F9" s="22" t="n">
         <v>150</v>
@@ -8030,7 +8666,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F10" s="22" t="n">
         <v>0</v>
@@ -8065,7 +8701,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F11" s="22" t="n">
         <v>0</v>
@@ -8100,7 +8736,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F12" s="39" t="n">
         <f aca="false">SUM(F8:F11)</f>
@@ -8145,7 +8781,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -8163,7 +8799,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F15" s="22" t="n">
         <v>900</v>
@@ -8198,7 +8834,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F16" s="22" t="n">
         <v>165</v>
@@ -8233,7 +8869,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F17" s="22" t="n">
         <v>0</v>
@@ -8268,7 +8904,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F18" s="22" t="n">
         <v>0</v>
@@ -8303,7 +8939,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F19" s="39" t="n">
         <f aca="false">SUM(F15:F18)</f>
@@ -8348,7 +8984,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
@@ -8366,7 +9002,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F22" s="22" t="n">
         <v>920</v>
@@ -8401,7 +9037,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F23" s="22" t="n">
         <v>180</v>
@@ -8436,7 +9072,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F24" s="22" t="n">
         <v>0</v>
@@ -8471,7 +9107,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F25" s="22" t="n">
         <v>0</v>
@@ -8506,7 +9142,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F26" s="39" t="n">
         <f aca="false">SUM(F22:F25)</f>
@@ -8551,7 +9187,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -8569,7 +9205,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F29" s="40" t="n">
         <f aca="false">CHOOSE(Assumptions!$C$8,F8,F15,F22)</f>
@@ -8614,7 +9250,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F30" s="40" t="n">
         <f aca="false">CHOOSE(Assumptions!$C$8,F9,F16,F23)</f>
@@ -8659,7 +9295,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F31" s="40" t="n">
         <f aca="false">CHOOSE(Assumptions!$C$8,F10,F17,F24)</f>
@@ -8704,7 +9340,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F32" s="40" t="n">
         <f aca="false">CHOOSE(Assumptions!$C$8,F11,F18,F25)</f>
@@ -8749,7 +9385,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C33" s="41" t="n">
         <v>725.3</v>
@@ -8803,7 +9439,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C34" s="41" t="n">
         <v>707</v>
@@ -8855,12 +9491,12 @@
         <v>2500</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="42" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D35" s="24" t="n">
         <f aca="false">D33/C33-1</f>
@@ -8913,51 +9549,51 @@
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H37" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I37" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L37" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M37" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N37" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O37" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F38" s="25" t="n">
         <v>1350</v>
@@ -8992,7 +9628,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F39" s="25" t="n">
         <v>1700</v>
@@ -9027,7 +9663,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F40" s="25" t="n">
         <v>2050</v>
@@ -9062,7 +9698,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="43" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41" s="44" t="n">
         <v>1116</v>
@@ -9116,7 +9752,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C42" s="45" t="n">
         <v>0.657</v>
@@ -9160,7 +9796,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C43" s="23" t="n">
         <f aca="false">C41/C42</f>
@@ -9217,51 +9853,51 @@
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I45" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N45" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O45" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F46" s="25" t="n">
         <v>625</v>
@@ -9296,7 +9932,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F47" s="25" t="n">
         <v>600</v>
@@ -9331,7 +9967,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F48" s="25" t="n">
         <v>585</v>
@@ -9366,7 +10002,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="43" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C49" s="44" t="n">
         <v>655</v>
@@ -9420,7 +10056,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C50" s="23" t="n">
         <f aca="false">C43-C49</f>
@@ -9477,7 +10113,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C51" s="24" t="n">
         <f aca="false">IFERROR(C50/C43,0)</f>
@@ -9534,51 +10170,51 @@
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="37" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G53" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H53" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I53" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L53" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M53" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N53" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O53" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F54" s="25" t="n">
         <v>620</v>
@@ -9613,7 +10249,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F55" s="25" t="n">
         <v>652</v>
@@ -9648,7 +10284,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F56" s="25" t="n">
         <v>685</v>
@@ -9683,7 +10319,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C57" s="44" t="n">
         <v>820</v>
@@ -9737,12 +10373,12 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -9772,66 +10408,66 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F7" s="46" t="n">
         <f aca="false">Deck!F29</f>
@@ -9876,7 +10512,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F8" s="46" t="n">
         <f aca="false">Deck!F30</f>
@@ -9921,7 +10557,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F9" s="46" t="n">
         <f aca="false">Deck!F31</f>
@@ -9966,7 +10602,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F10" s="46" t="n">
         <f aca="false">Deck!F32</f>
@@ -10011,7 +10647,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C11" s="47" t="n">
         <f aca="false">Deck!C34</f>
@@ -10068,51 +10704,51 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="37" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L13" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M13" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N13" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O13" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C14" s="48" t="n">
         <f aca="false">Deck!C41</f>
@@ -10169,7 +10805,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C15" s="49" t="n">
         <f aca="false">Deck!C42</f>
@@ -10226,7 +10862,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="50" t="n">
         <f aca="false">C14/C15</f>
@@ -10283,51 +10919,51 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="37" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L18" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M18" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N18" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O18" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" s="23" t="n">
         <f aca="false">C11*C16/1000</f>
@@ -10384,7 +11020,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C20" s="26" t="n">
         <v>0</v>
@@ -10426,12 +11062,12 @@
         <v>0.054</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C21" s="23" t="n">
         <f aca="false">C19*(1-C20)</f>
@@ -10488,7 +11124,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="42" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C22" s="25" t="n">
         <v>1254</v>
@@ -10502,7 +11138,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="42" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">IFERROR(C21/C22-1,"")</f>
@@ -10519,7 +11155,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -10549,66 +11185,66 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C7" s="51" t="n">
         <f aca="false">'Revenue Build'!C21</f>
@@ -10665,7 +11301,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C8" s="50" t="n">
         <f aca="false">-Deck!C34*Deck!C49/1000</f>
@@ -10722,7 +11358,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C9" s="50" t="n">
         <f aca="false">-C7*Assumptions!$C$42</f>
@@ -10779,7 +11415,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C10" s="50" t="n">
         <f aca="false">C27-C7-C8-C9</f>
@@ -10834,12 +11470,12 @@
         <v>-118.641982145028</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="52" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C11" s="23" t="n">
         <f aca="false">SUM(C7:C10)</f>
@@ -10896,7 +11532,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="42" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C12" s="24" t="n">
         <f aca="false">IFERROR(C11/C7,0)</f>
@@ -10953,7 +11589,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>-300</v>
@@ -11007,7 +11643,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C14" s="23" t="n">
         <f aca="false">C11+C13</f>
@@ -11064,7 +11700,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>-10</v>
@@ -11118,7 +11754,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C16" s="50" t="n">
         <f aca="false">C14+C15</f>
@@ -11175,7 +11811,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C17" s="50" t="n">
         <f aca="false">-MAX(0,C16)*Assumptions!$C$31</f>
@@ -11232,7 +11868,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="52" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C18" s="23" t="n">
         <f aca="false">C16+C17</f>
@@ -11289,51 +11925,51 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L20" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M20" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N20" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O20" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C21" s="53" t="n">
         <f aca="false">C18/Assumptions!$C$12</f>
@@ -11390,7 +12026,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F22" s="26" t="n">
         <v>0.3</v>
@@ -11423,12 +12059,12 @@
         <v>0.5</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F23" s="53" t="n">
         <f aca="false">MAX(0,F21)*F22</f>
@@ -11473,7 +12109,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F24" s="50" t="n">
         <f aca="false">F23*Assumptions!$C$12</f>
@@ -11518,7 +12154,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="42" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F25" s="24" t="n">
         <f aca="false">F23/Assumptions!$C$11</f>
@@ -11563,7 +12199,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="42" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C27" s="25" t="n">
         <v>538</v>
@@ -11577,7 +12213,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="42" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C28" s="25" t="n">
         <v>257.8</v>
@@ -11616,66 +12252,66 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -11693,7 +12329,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F8" s="26" t="n">
         <v>0.115</v>
@@ -11726,12 +12362,12 @@
         <v>0.115</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>0.04</v>
@@ -11764,12 +12400,12 @@
         <v>0.04</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F10" s="24" t="n">
         <f aca="false">Assumptions!$C$29*0+0.0625</f>
@@ -11814,7 +12450,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -11832,7 +12468,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E13" s="48" t="n">
         <f aca="false">Assumptions!$C$19</f>
@@ -11881,7 +12517,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E14" s="50" t="n">
         <f aca="false">'Income Statement'!E7*Assumptions!$C$44</f>
@@ -11930,7 +12566,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E15" s="25" t="n">
         <v>3200</v>
@@ -11976,12 +12612,12 @@
         <v>4214.28621392166</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E16" s="23" t="n">
         <f aca="false">SUM(E13:E15)</f>
@@ -12030,7 +12666,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -12048,7 +12684,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E19" s="48" t="n">
         <f aca="false">Assumptions!$C$20</f>
@@ -12097,7 +12733,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E20" s="50" t="n">
         <f aca="false">E16-E19</f>
@@ -12146,7 +12782,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E21" s="23" t="n">
         <f aca="false">E19+E20</f>
@@ -12195,7 +12831,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E22" s="54" t="n">
         <f aca="false">E16-E21</f>
@@ -12244,7 +12880,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="19" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -12262,7 +12898,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F25" s="50" t="n">
         <f aca="false">E15*F8</f>
@@ -12307,7 +12943,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F26" s="50" t="n">
         <f aca="false">E13*F9-E19*F10</f>
@@ -12352,7 +12988,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E27" s="50" t="n">
         <f aca="false">E13-E19</f>
@@ -12401,7 +13037,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!F18/E20,0)</f>
@@ -12446,7 +13082,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="42" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!F14*(1-Assumptions!$C$31)/(E15+E14),0)</f>
@@ -12491,7 +13127,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -12521,66 +13157,66 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -12598,7 +13234,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E8" s="48" t="n">
         <f aca="false">'Income Statement'!E11</f>
@@ -12647,7 +13283,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F9" s="48" t="n">
         <f aca="false">'Balance Sheet'!F26</f>
@@ -12692,7 +13328,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F10" s="48" t="n">
         <f aca="false">'Income Statement'!F17</f>
@@ -12737,7 +13373,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F11" s="50" t="n">
         <f aca="false">-('Balance Sheet'!F14-'Balance Sheet'!E14)</f>
@@ -12782,7 +13418,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F12" s="23" t="n">
         <f aca="false">SUM(F8:F11)</f>
@@ -12827,7 +13463,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -12845,7 +13481,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E15" s="50" t="n">
         <f aca="false">-Deck!E57</f>
@@ -12894,7 +13530,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F16" s="23" t="n">
         <f aca="false">F12+F15</f>
@@ -12939,7 +13575,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -12957,7 +13593,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F19" s="48" t="n">
         <f aca="false">-'Income Statement'!F24</f>
@@ -13002,7 +13638,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F20" s="25" t="n">
         <v>0</v>
@@ -13035,12 +13671,12 @@
         <v>0</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F21" s="23" t="n">
         <f aca="false">F16+F19+F20</f>
@@ -13085,7 +13721,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F22" s="48" t="n">
         <f aca="false">'Balance Sheet'!E13</f>
@@ -13130,7 +13766,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F23" s="23" t="n">
         <f aca="false">F22+F21</f>
@@ -13175,7 +13811,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -13205,66 +13841,66 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F7" s="48" t="n">
         <f aca="false">'Income Statement'!F14</f>
@@ -13309,7 +13945,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F8" s="50" t="n">
         <f aca="false">-MAX(0,F7)*Assumptions!$C$31</f>
@@ -13354,7 +13990,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F9" s="23" t="n">
         <f aca="false">F7+F8</f>
@@ -13399,7 +14035,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F10" s="48" t="n">
         <f aca="false">'Balance Sheet'!F25</f>
@@ -13444,7 +14080,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F11" s="50" t="n">
         <f aca="false">-Deck!F57</f>
@@ -13489,7 +14125,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F12" s="48" t="n">
         <f aca="false">'Cash Flow'!F11</f>
@@ -13534,7 +14170,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="52" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F13" s="23" t="n">
         <f aca="false">F9+F10+F11+F12</f>
@@ -13579,7 +14215,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="42" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F14" s="36" t="n">
         <v>0.5</v>
@@ -13614,7 +14250,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F15" s="55" t="n">
         <f aca="false">1/(1+Assumptions!$C$33)^F14</f>
@@ -13659,7 +14295,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F16" s="50" t="n">
         <f aca="false">F13*F15</f>
@@ -13704,7 +14340,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -13713,7 +14349,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">SUM(F16:O16)</f>
@@ -13722,7 +14358,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C20" s="30" t="n">
         <f aca="false">Assumptions!$C$36</f>
@@ -13731,7 +14367,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C21" s="50" t="n">
         <f aca="false">O13</f>
@@ -13740,7 +14376,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C22" s="56" t="n">
         <f aca="false">SUM(Deck!F34:O34)/1000/Assumptions!$C$54</f>
@@ -13749,7 +14385,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C23" s="56" t="n">
         <f aca="false">MAX(0,Assumptions!$C$50-C22)</f>
@@ -13758,7 +14394,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C24" s="56" t="n">
         <f aca="false">Deck!O34/1000/Assumptions!$C$54</f>
@@ -13767,19 +14403,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C25" s="57" t="n">
         <f aca="false">MIN(Assumptions!$C$55,IFERROR(C23/C24,0))</f>
         <v>16.1440057692308</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C26" s="58" t="n">
         <f aca="false">(1-(1+Assumptions!$C$33)^-C25)/Assumptions!$C$33</f>
@@ -13788,7 +14424,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C27" s="50" t="n">
         <f aca="false">C21*C26</f>
@@ -13797,7 +14433,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C28" s="50" t="n">
         <f aca="false">C27*O15</f>
@@ -13806,7 +14442,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C29" s="23" t="n">
         <f aca="false">C19+C28</f>
@@ -13815,19 +14451,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C30" s="24" t="n">
         <f aca="false">C28/C29</f>
         <v>0.508437249833287</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C31" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
@@ -13836,7 +14472,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C32" s="23" t="n">
         <f aca="false">C29+C31</f>
@@ -13845,7 +14481,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C33" s="40" t="n">
         <f aca="false">Assumptions!$C$12</f>
@@ -13854,7 +14490,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C34" s="59" t="n">
         <f aca="false">C32/C33</f>
@@ -13863,7 +14499,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C35" s="53" t="n">
         <f aca="false">Assumptions!$C$11</f>
@@ -13872,7 +14508,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C36" s="60" t="n">
         <f aca="false">C34/C35-1</f>
@@ -13881,7 +14517,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -13911,66 +14547,66 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F7" s="46" t="n">
         <f aca="false">Deck!F12</f>
@@ -14015,7 +14651,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F8" s="48" t="n">
         <f aca="false">Deck!F38</f>
@@ -14060,7 +14696,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F9" s="50" t="n">
         <f aca="false">F8/Deck!F42</f>
@@ -14105,7 +14741,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F10" s="48" t="n">
         <f aca="false">Deck!F46</f>
@@ -14150,7 +14786,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F11" s="23" t="n">
         <f aca="false">F7*F9/1000*(1-'Revenue Build'!F20)</f>
@@ -14195,7 +14831,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F12" s="50" t="n">
         <f aca="false">-F7*F10/1000</f>
@@ -14240,7 +14876,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F13" s="50" t="n">
         <f aca="false">-F11*Assumptions!$C$42</f>
@@ -14285,7 +14921,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F14" s="50" t="n">
         <f aca="false">-Assumptions!$C$40*(1+Assumptions!$C$41)^(0)</f>
@@ -14330,7 +14966,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F15" s="23" t="n">
         <f aca="false">SUM(F11:F14)</f>
@@ -14375,7 +15011,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F16" s="48" t="n">
         <f aca="false">Deck!F54</f>
@@ -14420,7 +15056,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F17" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15+F16-F18</f>
@@ -14465,7 +15101,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F18" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15*'Balance Sheet'!F8</f>
@@ -14510,7 +15146,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F19" s="50" t="n">
         <f aca="false">F15-F18</f>
@@ -14555,7 +15191,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F20" s="50" t="n">
         <f aca="false">F19*(1-Assumptions!$C$31)</f>
@@ -14600,7 +15236,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F21" s="50" t="n">
         <f aca="false">-(F11*Assumptions!$C$44-'Balance Sheet'!E14)</f>
@@ -14645,7 +15281,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F22" s="23" t="n">
         <f aca="false">F20+F18-F16+F21</f>
@@ -14690,7 +15326,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F23" s="55" t="n">
         <f aca="false">1/(1+Assumptions!$C$33)^(DCF!F14)</f>
@@ -14735,7 +15371,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F24" s="50" t="n">
         <f aca="false">F22*F23</f>
@@ -14780,7 +15416,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">SUM(F24:O24)</f>
@@ -14789,7 +15425,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C26" s="27" t="n">
         <v>0.015</v>
@@ -14797,7 +15433,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C27" s="56" t="n">
         <f aca="false">SUM(F7:O7)/1000/Assumptions!$C$54</f>
@@ -14806,7 +15442,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C28" s="56" t="n">
         <f aca="false">MAX(0,Assumptions!$C$50-C27)</f>
@@ -14815,7 +15451,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C29" s="56" t="n">
         <f aca="false">O7/1000/Assumptions!$C$54</f>
@@ -14824,7 +15460,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C30" s="57" t="n">
         <f aca="false">MIN(Assumptions!$C$55,IFERROR(C28/C29,0))</f>
@@ -14833,7 +15469,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C31" s="58" t="n">
         <f aca="false">(1-(1+Assumptions!$C$33)^-C30)/Assumptions!$C$33</f>
@@ -14842,7 +15478,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C32" s="50" t="n">
         <f aca="false">O22*C31*O23</f>
@@ -14851,7 +15487,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C33" s="50" t="n">
         <f aca="false">O22*(1+C26)/(Assumptions!$C$33-C26)*O23</f>
@@ -14860,7 +15496,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C34" s="23" t="n">
         <f aca="false">C25+C32</f>
@@ -14869,7 +15505,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C35" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
@@ -14878,7 +15514,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C36" s="23" t="n">
         <f aca="false">C34+C35</f>
@@ -14887,7 +15523,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C37" s="59" t="n">
         <f aca="false">C36/Assumptions!$C$12</f>
@@ -14896,7 +15532,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C38" s="35" t="n">
         <f aca="false">C37/Assumptions!$C$11-1</f>
@@ -14905,51 +15541,51 @@
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I41" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L41" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M41" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N41" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O41" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F42" s="46" t="n">
         <f aca="false">Deck!F19</f>
@@ -14994,7 +15630,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F43" s="48" t="n">
         <f aca="false">Deck!F39</f>
@@ -15039,7 +15675,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F44" s="50" t="n">
         <f aca="false">F43/Deck!F42</f>
@@ -15084,7 +15720,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F45" s="48" t="n">
         <f aca="false">Deck!F47</f>
@@ -15129,7 +15765,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F46" s="23" t="n">
         <f aca="false">F42*F44/1000*(1-'Revenue Build'!F20)</f>
@@ -15174,7 +15810,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F47" s="50" t="n">
         <f aca="false">-F42*F45/1000</f>
@@ -15219,7 +15855,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F48" s="50" t="n">
         <f aca="false">-F46*Assumptions!$C$42</f>
@@ -15264,7 +15900,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F49" s="50" t="n">
         <f aca="false">-Assumptions!$C$40*(1+Assumptions!$C$41)^(0)</f>
@@ -15309,7 +15945,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F50" s="23" t="n">
         <f aca="false">SUM(F46:F49)</f>
@@ -15354,7 +15990,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F51" s="48" t="n">
         <f aca="false">Deck!F55</f>
@@ -15399,7 +16035,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F52" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15+F51-F53</f>
@@ -15444,7 +16080,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F53" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15*'Balance Sheet'!F8</f>
@@ -15489,7 +16125,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F54" s="50" t="n">
         <f aca="false">F50-F53</f>
@@ -15534,7 +16170,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F55" s="50" t="n">
         <f aca="false">F54*(1-Assumptions!$C$31)</f>
@@ -15579,7 +16215,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F56" s="50" t="n">
         <f aca="false">-(F46*Assumptions!$C$44-'Balance Sheet'!E14)</f>
@@ -15624,7 +16260,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F57" s="23" t="n">
         <f aca="false">F55+F53-F51+F56</f>
@@ -15669,7 +16305,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F58" s="55" t="n">
         <f aca="false">1/(1+Assumptions!$C$33)^(DCF!F14)</f>
@@ -15714,7 +16350,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F59" s="50" t="n">
         <f aca="false">F57*F58</f>
@@ -15759,7 +16395,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C60" s="50" t="n">
         <f aca="false">SUM(F59:O59)</f>
@@ -15768,7 +16404,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C61" s="27" t="n">
         <v>0.025</v>
@@ -15776,7 +16412,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C62" s="56" t="n">
         <f aca="false">SUM(F42:O42)/1000/Assumptions!$C$54</f>
@@ -15785,7 +16421,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C63" s="56" t="n">
         <f aca="false">MAX(0,Assumptions!$C$50-C62)</f>
@@ -15794,7 +16430,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C64" s="56" t="n">
         <f aca="false">O42/1000/Assumptions!$C$54</f>
@@ -15803,7 +16439,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C65" s="57" t="n">
         <f aca="false">MIN(Assumptions!$C$55,IFERROR(C63/C64,0))</f>
@@ -15812,7 +16448,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C66" s="58" t="n">
         <f aca="false">(1-(1+Assumptions!$C$33)^-C65)/Assumptions!$C$33</f>
@@ -15821,7 +16457,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C67" s="50" t="n">
         <f aca="false">O57*C66*O58</f>
@@ -15830,7 +16466,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C68" s="50" t="n">
         <f aca="false">O57*(1+C61)/(Assumptions!$C$33-C61)*O58</f>
@@ -15839,7 +16475,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C69" s="23" t="n">
         <f aca="false">C60+C67</f>
@@ -15848,7 +16484,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C70" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
@@ -15857,7 +16493,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C71" s="23" t="n">
         <f aca="false">C69+C70</f>
@@ -15866,7 +16502,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C72" s="59" t="n">
         <f aca="false">C71/Assumptions!$C$12</f>
@@ -15875,7 +16511,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C73" s="35" t="n">
         <f aca="false">C72/Assumptions!$C$11-1</f>
@@ -15884,51 +16520,51 @@
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="37" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F76" s="38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H76" s="38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I76" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J76" s="38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L76" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M76" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N76" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O76" s="38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F77" s="46" t="n">
         <f aca="false">Deck!F26</f>
@@ -15973,7 +16609,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F78" s="48" t="n">
         <f aca="false">Deck!F40</f>
@@ -16018,7 +16654,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F79" s="50" t="n">
         <f aca="false">F78/Deck!F42</f>
@@ -16063,7 +16699,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F80" s="48" t="n">
         <f aca="false">Deck!F48</f>
@@ -16108,7 +16744,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F81" s="23" t="n">
         <f aca="false">F77*F79/1000*(1-'Revenue Build'!F20)</f>
@@ -16153,7 +16789,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F82" s="50" t="n">
         <f aca="false">-F77*F80/1000</f>
@@ -16198,7 +16834,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F83" s="50" t="n">
         <f aca="false">-F81*Assumptions!$C$42</f>
@@ -16243,7 +16879,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F84" s="50" t="n">
         <f aca="false">-Assumptions!$C$40*(1+Assumptions!$C$41)^(0)</f>
@@ -16288,7 +16924,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F85" s="23" t="n">
         <f aca="false">SUM(F81:F84)</f>
@@ -16333,7 +16969,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F86" s="48" t="n">
         <f aca="false">Deck!F56</f>
@@ -16378,7 +17014,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F87" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15+F86-F88</f>
@@ -16423,7 +17059,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F88" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15*'Balance Sheet'!F8</f>
@@ -16468,7 +17104,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F89" s="50" t="n">
         <f aca="false">F85-F88</f>
@@ -16513,7 +17149,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F90" s="50" t="n">
         <f aca="false">F89*(1-Assumptions!$C$31)</f>
@@ -16558,7 +17194,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F91" s="50" t="n">
         <f aca="false">-(F81*Assumptions!$C$44-'Balance Sheet'!E14)</f>
@@ -16603,7 +17239,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F92" s="23" t="n">
         <f aca="false">F90+F88-F86+F91</f>
@@ -16648,7 +17284,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F93" s="55" t="n">
         <f aca="false">1/(1+Assumptions!$C$33)^(DCF!F14)</f>
@@ -16693,7 +17329,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F94" s="50" t="n">
         <f aca="false">F92*F93</f>
@@ -16738,7 +17374,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C95" s="50" t="n">
         <f aca="false">SUM(F94:O94)</f>
@@ -16747,7 +17383,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C96" s="27" t="n">
         <v>0.03</v>
@@ -16755,7 +17391,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C97" s="56" t="n">
         <f aca="false">SUM(F77:O77)/1000/Assumptions!$C$54</f>
@@ -16764,7 +17400,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C98" s="56" t="n">
         <f aca="false">MAX(0,Assumptions!$C$50-C97)</f>
@@ -16773,7 +17409,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C99" s="56" t="n">
         <f aca="false">O77/1000/Assumptions!$C$54</f>
@@ -16782,7 +17418,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C100" s="57" t="n">
         <f aca="false">MIN(Assumptions!$C$55,IFERROR(C98/C99,0))</f>
@@ -16791,7 +17427,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C101" s="58" t="n">
         <f aca="false">(1-(1+Assumptions!$C$33)^-C100)/Assumptions!$C$33</f>
@@ -16800,7 +17436,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C102" s="50" t="n">
         <f aca="false">O92*C101*O93</f>
@@ -16809,7 +17445,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C103" s="50" t="n">
         <f aca="false">O92*(1+C96)/(Assumptions!$C$33-C96)*O93</f>
@@ -16818,7 +17454,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C104" s="23" t="n">
         <f aca="false">C95+C102</f>
@@ -16827,7 +17463,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C105" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
@@ -16836,7 +17472,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C106" s="23" t="n">
         <f aca="false">C104+C105</f>
@@ -16845,7 +17481,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C107" s="59" t="n">
         <f aca="false">C106/Assumptions!$C$12</f>
@@ -16854,7 +17490,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C108" s="35" t="n">
         <f aca="false">C107/Assumptions!$C$11-1</f>

--- a/model/PLS_Valuation_Model_FMAA_2026.xlsx
+++ b/model/PLS_Valuation_Model_FMAA_2026.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="798">
   <si>
     <t xml:space="preserve">PLS GROUP LIMITED</t>
   </si>
@@ -298,7 +298,7 @@
     <t xml:space="preserve">Borrowings, FY26A (A$m)</t>
   </si>
   <si>
-    <t xml:space="preserve">E  US$600m senior notes translated at spot - VERIFY</t>
+    <t xml:space="preserve">A  reported at 30-Jun-26 after the US$600m notes issue</t>
   </si>
   <si>
     <t xml:space="preserve">Net cash / (net debt) (A$m)</t>
@@ -748,10 +748,10 @@
     <t xml:space="preserve">   Net working capital</t>
   </si>
   <si>
-    <t xml:space="preserve">   Property, plant and equipment (net)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E  FY26A net book value - VERIFY against the annual report</t>
+    <t xml:space="preserve">   Property, plant and equipment and other non-current assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D  reported FY26 total assets of A$6,258m less cash and net working capital</t>
   </si>
   <si>
     <t xml:space="preserve">Total assets</t>
@@ -2101,10 +2101,52 @@
     <t xml:space="preserve">Borrowings</t>
   </si>
   <si>
-    <t xml:space="preserve">US$600m senior unsecured notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inaugural international bond issued April 2026</t>
+    <t xml:space="preserve">A$853m at 30-Jun-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the US$600m senior notes issue, net of revolving facility repayments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A$6,258m at 30-Jun-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up 34% on FY25; used to derive the opening PP&amp;E and other non-current assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26 emissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Scope 1 and 2 down 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26 results; follows a 7.1% reduction in FY25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26 safety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group TRIFR 2.77, an 11% improvement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26 female participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26 environmental incidents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero major environmental, water or waste incidents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short interest, current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.09% of shares at 4-Aug-26, up 0.75pp week on week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASIC short position reports - REBUILT above the 10% level we named as a warning</t>
   </si>
   <si>
     <t xml:space="preserve">FY26 final dividend</t>
@@ -2335,10 +2377,10 @@
     <t xml:space="preserve">Industry data via Benchmark and Rho Motion</t>
   </si>
   <si>
-    <t xml:space="preserve">Short interest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~20% of shares (Sep-2024, most shorted on ASX) falling to ~6.8% (26-May-2026)</t>
+    <t xml:space="preserve">Short interest, history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~20% of shares (Sep-2024, most shorted on ASX), ~6.8% (26-May-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">ASIC short position reports via shortman.com.au</t>
@@ -2386,10 +2428,10 @@
     <t xml:space="preserve">consistent across sources. Figures tagged E are our own estimates and are identified as such wherever they appear.</t>
   </si>
   <si>
-    <t xml:space="preserve">Known unresolved items: total borrowings at 30-Jun-26 (only the US$600m notes issue is confirmed); FY24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparatives; the Ore Reserve has not been restated since August 2023; and PLS's Scope 3 emissions are not disclosed.</t>
+    <t xml:space="preserve">Known unresolved items: FY24 comparatives; the Ore Reserve has not been restated since August 2023;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLS's Scope 3 emissions and emissions intensity per tonne are not disclosed; and the tailings method is not disclosed.</t>
   </si>
 </sst>
 </file>
@@ -3850,19 +3892,19 @@
       </c>
       <c r="C8" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$34</f>
-        <v>5830.37408323384</v>
+        <v>5956.161503641</v>
       </c>
       <c r="D8" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$69</f>
-        <v>19460.198458088</v>
+        <v>19581.2480263643</v>
       </c>
       <c r="E8" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$104</f>
-        <v>27306.5983776793</v>
+        <v>27426.0222223156</v>
       </c>
       <c r="F8" s="23" t="n">
         <f aca="false">SUMPRODUCT(C8:E8,C$7:E$7)</f>
-        <v>18014.3423442723</v>
+        <v>18136.1699446713</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3871,19 +3913,19 @@
       </c>
       <c r="C9" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$36</f>
-        <v>7292.37408323384</v>
+        <v>7393.161503641</v>
       </c>
       <c r="D9" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$71</f>
-        <v>20922.198458088</v>
+        <v>21018.2480263643</v>
       </c>
       <c r="E9" s="50" t="n">
         <f aca="false">'Scenario Engine'!$C$106</f>
-        <v>28768.5983776793</v>
+        <v>28863.0222223156</v>
       </c>
       <c r="F9" s="23" t="n">
         <f aca="false">SUMPRODUCT(C9:E9,C$7:E$7)</f>
-        <v>19476.3423442723</v>
+        <v>19573.1699446713</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3892,19 +3934,19 @@
       </c>
       <c r="C10" s="63" t="n">
         <f aca="false">'Scenario Engine'!$C$37</f>
-        <v>2.26471244820927</v>
+        <v>2.2960128893295</v>
       </c>
       <c r="D10" s="63" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
       <c r="E10" s="63" t="n">
         <f aca="false">'Scenario Engine'!$C$107</f>
-        <v>8.93434732226067</v>
+        <v>8.96367149761355</v>
       </c>
       <c r="F10" s="64" t="n">
         <f aca="false">SUMPRODUCT(C10:E10,C$7:E$7)</f>
-        <v>6.04855352306593</v>
+        <v>6.07862420641966</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3913,19 +3955,19 @@
       </c>
       <c r="C11" s="35" t="n">
         <f aca="false">'Scenario Engine'!$C$38</f>
-        <v>-0.586731305071302</v>
+        <v>-0.581019545742792</v>
       </c>
       <c r="D11" s="35" t="n">
         <f aca="false">'Scenario Engine'!$C$73</f>
-        <v>0.18568926293739</v>
+        <v>0.191132521782442</v>
       </c>
       <c r="E11" s="35" t="n">
         <f aca="false">'Scenario Engine'!$C$108</f>
-        <v>0.630355350777494</v>
+        <v>0.635706477666707</v>
       </c>
       <c r="F11" s="65" t="n">
         <f aca="false">SUMPRODUCT(C11:E11,C$7:E$7)</f>
-        <v>0.103750642895243</v>
+        <v>0.1092379938722</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,23 +4171,23 @@
       </c>
       <c r="C8" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+C$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+C$7)^-$B8)/C$7/(1+C$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.2833438786021</v>
+        <v>6.3130994017947</v>
       </c>
       <c r="D8" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+D$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+D$7)^-$B8)/D$7/(1+D$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.0249514090978</v>
+        <v>6.05376559069775</v>
       </c>
       <c r="E8" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+E$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+E$7)^-$B8)/E$7/(1+E$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>5.78192379000033</v>
+        <v>5.80984324258334</v>
       </c>
       <c r="F8" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+F$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+F$7)^-$B8)/F$7/(1+F$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>5.55318479193557</v>
+        <v>5.58025308679672</v>
       </c>
       <c r="G8" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+G$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+G$7)^-$B8)/G$7/(1+G$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>5.33774274688339</v>
+        <v>5.36400064593976</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4154,23 +4196,23 @@
       </c>
       <c r="C9" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+C$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+C$7)^-$B9)/C$7/(1+C$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.03155103054887</v>
+        <v>7.06330276949487</v>
       </c>
       <c r="D9" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+D$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+D$7)^-$B9)/D$7/(1+D$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.69971284682114</v>
+        <v>6.73032729110004</v>
       </c>
       <c r="E9" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+E$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+E$7)^-$B9)/E$7/(1+E$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.39076421339548</v>
+        <v>6.42030805147297</v>
       </c>
       <c r="F9" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+F$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+F$7)^-$B9)/F$7/(1+F$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.10282610282252</v>
+        <v>6.13136084001941</v>
       </c>
       <c r="G9" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+G$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+G$7)^-$B9)/G$7/(1+G$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>5.83419305573031</v>
+        <v>5.86177548359495</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4179,23 +4221,23 @@
       </c>
       <c r="C10" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+C$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+C$7)^-$B10)/C$7/(1+C$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.54360668504584</v>
+        <v>7.57672458784296</v>
       </c>
       <c r="D10" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+D$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+D$7)^-$B10)/D$7/(1+D$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.15094965806454</v>
+        <v>7.18276800159619</v>
       </c>
       <c r="E10" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+E$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+E$7)^-$B10)/E$7/(1+E$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.78865411626023</v>
+        <v>6.81925952410508</v>
       </c>
       <c r="F10" s="72" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+F$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+F$7)^-$B10)/F$7/(1+F$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.45389291161712</v>
+        <v>6.48336429462445</v>
       </c>
       <c r="G10" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+G$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+G$7)^-$B10)/G$7/(1+G$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.14413655467392</v>
+        <v>6.17254591140932</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4204,23 +4246,23 @@
       </c>
       <c r="C11" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+C$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+C$7)^-$B11)/C$7/(1+C$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.89404572137436</v>
+        <v>7.92809859508576</v>
       </c>
       <c r="D11" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+D$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+D$7)^-$B11)/D$7/(1+D$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.45270765494729</v>
+        <v>7.48533108844035</v>
       </c>
       <c r="E11" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+E$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+E$7)^-$B11)/E$7/(1+E$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.04868345846272</v>
+        <v>7.07998262427005</v>
       </c>
       <c r="F11" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+F$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+F$7)^-$B11)/F$7/(1+F$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.67812624669585</v>
+        <v>6.70819588396306</v>
       </c>
       <c r="G11" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+G$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+G$7)^-$B11)/G$7/(1+G$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.33764025650569</v>
+        <v>6.36656588087759</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4229,23 +4271,23 @@
       </c>
       <c r="C12" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+C$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+C$7)^-$B12)/C$7/(1+C$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>8.13387808550185</v>
+        <v>8.16857083166328</v>
       </c>
       <c r="D12" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+D$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+D$7)^-$B12)/D$7/(1+D$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.65450388790926</v>
+        <v>7.68766571350158</v>
       </c>
       <c r="E12" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+E$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+E$7)^-$B12)/E$7/(1+E$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>7.21861805172441</v>
+        <v>7.2503706028158</v>
       </c>
       <c r="F12" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+F$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+F$7)^-$B12)/F$7/(1+F$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.82134852604823</v>
+        <v>6.85180028017911</v>
       </c>
       <c r="G12" s="71" t="n">
         <f aca="false">(SUMPRODUCT('Scenario Engine'!F57:O57,1/(1+G$7)^DCF!F14:O14)+'Scenario Engine'!O57*(1-(1+G$7)^-$B12)/G$7/(1+G$7)^DCF!O14+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.45844834814246</v>
+        <v>6.48769628835301</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4637,23 +4679,23 @@
       </c>
       <c r="C30" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*C$29-$C$26*$B30)/Assumptions!$C$12</f>
-        <v>3.98266524443733</v>
+        <v>4.01249430290822</v>
       </c>
       <c r="D30" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*D$29-$C$26*$B30)/Assumptions!$C$12</f>
-        <v>5.42068477710447</v>
+        <v>5.45051383557535</v>
       </c>
       <c r="E30" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*E$29-$C$26*$B30)/Assumptions!$C$12</f>
-        <v>6.8587043097716</v>
+        <v>6.88853336824248</v>
       </c>
       <c r="F30" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*F$29-$C$26*$B30)/Assumptions!$C$12</f>
-        <v>8.29672384243873</v>
+        <v>8.32655290090961</v>
       </c>
       <c r="G30" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*G$29-$C$26*$B30)/Assumptions!$C$12</f>
-        <v>9.73474337510586</v>
+        <v>9.76457243357675</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4662,23 +4704,23 @@
       </c>
       <c r="C31" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*C$29-$C$26*$B31)/Assumptions!$C$12</f>
-        <v>3.80210166999998</v>
+        <v>3.83193072847087</v>
       </c>
       <c r="D31" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*D$29-$C$26*$B31)/Assumptions!$C$12</f>
-        <v>5.24012120266712</v>
+        <v>5.269950261138</v>
       </c>
       <c r="E31" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*E$29-$C$26*$B31)/Assumptions!$C$12</f>
-        <v>6.67814073533425</v>
+        <v>6.70796979380513</v>
       </c>
       <c r="F31" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*F$29-$C$26*$B31)/Assumptions!$C$12</f>
-        <v>8.11616026800138</v>
+        <v>8.14598932647226</v>
       </c>
       <c r="G31" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*G$29-$C$26*$B31)/Assumptions!$C$12</f>
-        <v>9.55417980066851</v>
+        <v>9.5840088591394</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4687,23 +4729,23 @@
       </c>
       <c r="C32" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*C$29-$C$26*$B32)/Assumptions!$C$12</f>
-        <v>3.62153809556264</v>
+        <v>3.65136715403352</v>
       </c>
       <c r="D32" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*D$29-$C$26*$B32)/Assumptions!$C$12</f>
-        <v>5.05955762822977</v>
+        <v>5.08938668670065</v>
       </c>
       <c r="E32" s="72" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*E$29-$C$26*$B32)/Assumptions!$C$12</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
       <c r="F32" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*F$29-$C$26*$B32)/Assumptions!$C$12</f>
-        <v>7.93559669356403</v>
+        <v>7.96542575203492</v>
       </c>
       <c r="G32" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*G$29-$C$26*$B32)/Assumptions!$C$12</f>
-        <v>9.37361622623116</v>
+        <v>9.40344528470205</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4712,23 +4754,23 @@
       </c>
       <c r="C33" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*C$29-$C$26*$B33)/Assumptions!$C$12</f>
-        <v>3.44097452112529</v>
+        <v>3.47080357959617</v>
       </c>
       <c r="D33" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*D$29-$C$26*$B33)/Assumptions!$C$12</f>
-        <v>4.87899405379242</v>
+        <v>4.9088231122633</v>
       </c>
       <c r="E33" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*E$29-$C$26*$B33)/Assumptions!$C$12</f>
-        <v>6.31701358645955</v>
+        <v>6.34684264493044</v>
       </c>
       <c r="F33" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*F$29-$C$26*$B33)/Assumptions!$C$12</f>
-        <v>7.75503311912668</v>
+        <v>7.78486217759757</v>
       </c>
       <c r="G33" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*G$29-$C$26*$B33)/Assumptions!$C$12</f>
-        <v>9.19305265179381</v>
+        <v>9.2228817102647</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4737,23 +4779,23 @@
       </c>
       <c r="C34" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*C$29-$C$26*$B34)/Assumptions!$C$12</f>
-        <v>3.26041094668794</v>
+        <v>3.29024000515882</v>
       </c>
       <c r="D34" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*D$29-$C$26*$B34)/Assumptions!$C$12</f>
-        <v>4.69843047935507</v>
+        <v>4.72825953782596</v>
       </c>
       <c r="E34" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*E$29-$C$26*$B34)/Assumptions!$C$12</f>
-        <v>6.1364500120222</v>
+        <v>6.16627907049309</v>
       </c>
       <c r="F34" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*F$29-$C$26*$B34)/Assumptions!$C$12</f>
-        <v>7.57446954468933</v>
+        <v>7.60429860316022</v>
       </c>
       <c r="G34" s="71" t="n">
         <f aca="false">'Scenario Engine'!$C$72+($C$25*G$29-$C$26*$B34)/Assumptions!$C$12</f>
-        <v>9.01248907735647</v>
+        <v>9.04231813582735</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5026,11 +5068,11 @@
       </c>
       <c r="E16" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
-        <v>1462</v>
+        <v>1437</v>
       </c>
       <c r="F16" s="53" t="n">
         <f aca="false">E16/Assumptions!$C$12</f>
-        <v>0.454037267080745</v>
+        <v>0.446273291925466</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5039,11 +5081,11 @@
       </c>
       <c r="E17" s="78" t="n">
         <f aca="false">E15+E16</f>
-        <v>14411.5</v>
+        <v>14386.5</v>
       </c>
       <c r="F17" s="79" t="n">
         <f aca="false">E17/Assumptions!$C$12</f>
-        <v>4.47562111801242</v>
+        <v>4.46785714285714</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5052,7 +5094,7 @@
       </c>
       <c r="F18" s="80" t="n">
         <f aca="false">Assumptions!$C$11/F17-1</f>
-        <v>0.224411060611317</v>
+        <v>0.226538768984812</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5368,7 +5410,7 @@
       </c>
       <c r="D19" s="87" t="n">
         <f aca="false">(D16*D17+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>4.75539751552795</v>
+        <v>4.74763354037267</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5377,7 +5419,7 @@
       </c>
       <c r="D20" s="87" t="n">
         <f aca="false">(D16*D18+Assumptions!$C$21)/Assumptions!$C$12</f>
-        <v>6.36840760869565</v>
+        <v>6.36064363354037</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5386,7 +5428,7 @@
       </c>
       <c r="D21" s="88" t="n">
         <f aca="false">AVERAGE(D19,D20)</f>
-        <v>5.5619025621118</v>
+        <v>5.55413858695652</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5658,7 +5700,7 @@
       </c>
       <c r="E17" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5678,7 +5720,7 @@
       </c>
       <c r="E19" s="88" t="n">
         <f aca="false">E17*(1+E18)</f>
-        <v>8.22593268569547</v>
+        <v>8.26369627371962</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5780,15 +5822,15 @@
       </c>
       <c r="C7" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
       <c r="D7" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
       <c r="E7" s="87" t="n">
         <f aca="false">AVERAGE(C7:D7)</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>0.6</v>
@@ -5803,15 +5845,15 @@
       </c>
       <c r="C8" s="53" t="n">
         <f aca="false">'Scenario Summary'!$F$10</f>
-        <v>6.04855352306593</v>
+        <v>6.07862420641966</v>
       </c>
       <c r="D8" s="53" t="n">
         <f aca="false">'Scenario Summary'!$F$10</f>
-        <v>6.04855352306593</v>
+        <v>6.07862420641966</v>
       </c>
       <c r="E8" s="87" t="n">
         <f aca="false">AVERAGE(C8:D8)</f>
-        <v>6.04855352306593</v>
+        <v>6.07862420641966</v>
       </c>
       <c r="F8" s="26" t="n">
         <v>0</v>
@@ -5826,15 +5868,15 @@
       </c>
       <c r="C9" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$37</f>
-        <v>2.26471244820927</v>
+        <v>2.2960128893295</v>
       </c>
       <c r="D9" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$107</f>
-        <v>8.93434732226067</v>
+        <v>8.96367149761355</v>
       </c>
       <c r="E9" s="87" t="n">
         <f aca="false">AVERAGE(C9:D9)</f>
-        <v>5.59952988523497</v>
+        <v>5.62984219347153</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>0</v>
@@ -5849,15 +5891,15 @@
       </c>
       <c r="C10" s="53" t="n">
         <f aca="false">'Trading Comps'!$D$19</f>
-        <v>4.75539751552795</v>
+        <v>4.74763354037267</v>
       </c>
       <c r="D10" s="53" t="n">
         <f aca="false">'Trading Comps'!$D$20</f>
-        <v>6.36840760869565</v>
+        <v>6.36064363354037</v>
       </c>
       <c r="E10" s="87" t="n">
         <f aca="false">AVERAGE(C10:D10)</f>
-        <v>5.5619025621118</v>
+        <v>5.55413858695652</v>
       </c>
       <c r="F10" s="26" t="n">
         <v>0.4</v>
@@ -5872,15 +5914,15 @@
       </c>
       <c r="C11" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
       <c r="D11" s="53" t="n">
         <f aca="false">Precedents!$E$19</f>
-        <v>8.22593268569547</v>
+        <v>8.26369627371962</v>
       </c>
       <c r="E11" s="87" t="n">
         <f aca="false">AVERAGE(C11:D11)</f>
-        <v>7.36175492329619</v>
+        <v>7.3955512465437</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>0</v>
@@ -5946,7 +5988,7 @@
       </c>
       <c r="C16" s="90" t="n">
         <f aca="false">SUMPRODUCT(E7:E13,F7:F13)/SUM(F7:F13)</f>
-        <v>6.12330732138286</v>
+        <v>6.13809916640328</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5964,7 +6006,7 @@
       </c>
       <c r="C18" s="91" t="n">
         <f aca="false">C16/C17-1</f>
-        <v>0.117391846967675</v>
+        <v>0.120091088759722</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5973,7 +6015,7 @@
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">'Income Statement'!F25</f>
-        <v>0.0166988356870835</v>
+        <v>0.0158412805458585</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5982,7 +6024,7 @@
       </c>
       <c r="C20" s="92" t="n">
         <f aca="false">C18+C19</f>
-        <v>0.134090682654759</v>
+        <v>0.135932369305581</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6000,7 +6042,7 @@
       </c>
       <c r="C22" s="92" t="n">
         <f aca="false">C20-C21</f>
-        <v>0.0750906826547586</v>
+        <v>0.0769323693055809</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6454,7 +6496,7 @@
       </c>
       <c r="D31" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6463,7 +6505,7 @@
       </c>
       <c r="D32" s="80" t="n">
         <f aca="false">D30/D31</f>
-        <v>0.0663782389063311</v>
+        <v>0.0660749024349994</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6829,7 +6871,7 @@
       </c>
       <c r="D25" s="53" t="n">
         <f aca="false">'Football Field'!$C$16</f>
-        <v>6.12330732138286</v>
+        <v>6.13809916640328</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6847,7 +6889,7 @@
       </c>
       <c r="D27" s="87" t="n">
         <f aca="false">D25-D26</f>
-        <v>0.64330732138286</v>
+        <v>0.658099166403279</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6865,7 +6907,7 @@
       </c>
       <c r="D29" s="103" t="n">
         <f aca="false">D28/D27</f>
-        <v>0.670438085752254</v>
+        <v>0.655368903527889</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6883,7 +6925,7 @@
       </c>
       <c r="D31" s="104" t="n">
         <f aca="false">D25+F22</f>
-        <v>6.44108520958162</v>
+        <v>6.45587705460204</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7012,7 +7054,7 @@
       </c>
       <c r="C13" s="53" t="n">
         <f aca="false">'Football Field'!$C$16</f>
-        <v>6.12330732138286</v>
+        <v>6.13809916640328</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7021,7 +7063,7 @@
       </c>
       <c r="C14" s="24" t="n">
         <f aca="false">'Football Field'!$C$18</f>
-        <v>0.117391846967675</v>
+        <v>0.120091088759722</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7030,7 +7072,7 @@
       </c>
       <c r="C15" s="24" t="n">
         <f aca="false">'Income Statement'!F25</f>
-        <v>0.0166988356870835</v>
+        <v>0.0158412805458585</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7039,7 +7081,7 @@
       </c>
       <c r="C16" s="35" t="n">
         <f aca="false">'Football Field'!$C$20</f>
-        <v>0.134090682654759</v>
+        <v>0.135932369305581</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7048,7 +7090,7 @@
       </c>
       <c r="C17" s="35" t="n">
         <f aca="false">C16-C7</f>
-        <v>0.0750906826547586</v>
+        <v>0.0769323693055809</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7066,7 +7108,7 @@
       </c>
       <c r="C20" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$37</f>
-        <v>2.26471244820927</v>
+        <v>2.2960128893295</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7075,7 +7117,7 @@
       </c>
       <c r="C21" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7084,7 +7126,7 @@
       </c>
       <c r="C22" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$107</f>
-        <v>8.93434732226067</v>
+        <v>8.96367149761355</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7093,7 +7135,7 @@
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">C20/Assumptions!$C$11-1</f>
-        <v>-0.586731305071302</v>
+        <v>-0.581019545742792</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7102,7 +7144,7 @@
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">C22/Assumptions!$C$11-1</f>
-        <v>0.630355350777494</v>
+        <v>0.635706477666707</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7111,7 +7153,7 @@
       </c>
       <c r="C25" s="105" t="n">
         <f aca="false">IFERROR(ABS(C24/C23),0)</f>
-        <v>1.07435097689374</v>
+        <v>1.09412236184585</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>620</v>
@@ -7143,7 +7185,7 @@
       </c>
       <c r="C29" s="53" t="n">
         <f aca="false">C20</f>
-        <v>2.26471244820927</v>
+        <v>2.2960128893295</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7152,7 +7194,7 @@
       </c>
       <c r="C30" s="35" t="n">
         <f aca="false">C29/C28-1</f>
-        <v>0.185713323669774</v>
+        <v>0.202100989177749</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7197,7 +7239,7 @@
     <tabColor rgb="FF5A6472"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:E61"/>
+  <dimension ref="B2:E67"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -7491,452 +7533,536 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="106" t="s">
         <v>689</v>
-      </c>
-      <c r="C25" s="106" t="s">
-        <v>690</v>
       </c>
       <c r="D25" s="109" t="s">
         <v>658</v>
       </c>
       <c r="E25" s="75" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="C26" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="C26" s="106" t="s">
+      <c r="D26" s="109" t="s">
+        <v>658</v>
+      </c>
+      <c r="E26" s="75" t="s">
         <v>693</v>
-      </c>
-      <c r="D26" s="109" t="s">
-        <v>694</v>
-      </c>
-      <c r="E26" s="75" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C27" s="106" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D27" s="109" t="s">
-        <v>694</v>
+        <v>658</v>
       </c>
       <c r="E27" s="75" t="s">
-        <v>698</v>
+        <v>665</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C28" s="106" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D28" s="109" t="s">
-        <v>694</v>
+        <v>658</v>
       </c>
       <c r="E28" s="75" t="s">
-        <v>701</v>
+        <v>665</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C29" s="106" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D29" s="109" t="s">
-        <v>694</v>
+        <v>658</v>
       </c>
       <c r="E29" s="75" t="s">
-        <v>704</v>
+        <v>665</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C30" s="106" t="s">
-        <v>706</v>
-      </c>
-      <c r="D30" s="109" t="s">
-        <v>658</v>
+        <v>701</v>
+      </c>
+      <c r="D30" s="108" t="s">
+        <v>648</v>
       </c>
       <c r="E30" s="75" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="C31" s="106" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="D31" s="109" t="s">
         <v>658</v>
       </c>
       <c r="E31" s="75" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C32" s="106" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="D32" s="109" t="s">
-        <v>658</v>
+        <v>708</v>
       </c>
       <c r="E32" s="75" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C33" s="106" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D33" s="109" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C34" s="106" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D34" s="109" t="s">
-        <v>658</v>
+        <v>708</v>
       </c>
       <c r="E34" s="75" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C35" s="106" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D35" s="109" t="s">
-        <v>658</v>
+        <v>708</v>
       </c>
       <c r="E35" s="75" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C36" s="106" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="D36" s="109" t="s">
         <v>658</v>
       </c>
       <c r="E36" s="75" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C37" s="106" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D37" s="109" t="s">
         <v>658</v>
       </c>
       <c r="E37" s="75" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C38" s="106" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="D38" s="109" t="s">
         <v>658</v>
       </c>
       <c r="E38" s="75" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C39" s="106" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D39" s="109" t="s">
-        <v>658</v>
+        <v>708</v>
       </c>
       <c r="E39" s="75" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C40" s="106" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D40" s="109" t="s">
         <v>658</v>
       </c>
       <c r="E40" s="75" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C41" s="106" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="D41" s="109" t="s">
         <v>658</v>
       </c>
       <c r="E41" s="75" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C42" s="106" t="s">
-        <v>742</v>
-      </c>
-      <c r="D42" s="108" t="s">
-        <v>648</v>
+        <v>738</v>
+      </c>
+      <c r="D42" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E42" s="75" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C43" s="106" t="s">
-        <v>745</v>
-      </c>
-      <c r="D43" s="108" t="s">
-        <v>648</v>
+        <v>741</v>
+      </c>
+      <c r="D43" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E43" s="75" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="C44" s="106" t="s">
-        <v>748</v>
-      </c>
-      <c r="D44" s="108" t="s">
-        <v>648</v>
+        <v>744</v>
+      </c>
+      <c r="D44" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E44" s="75" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C45" s="106" t="s">
-        <v>751</v>
-      </c>
-      <c r="D45" s="108" t="s">
-        <v>648</v>
+        <v>747</v>
+      </c>
+      <c r="D45" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E45" s="75" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C46" s="106" t="s">
-        <v>754</v>
-      </c>
-      <c r="D46" s="108" t="s">
-        <v>648</v>
+        <v>750</v>
+      </c>
+      <c r="D46" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E46" s="75" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C47" s="106" t="s">
-        <v>757</v>
-      </c>
-      <c r="D47" s="108" t="s">
-        <v>648</v>
+        <v>753</v>
+      </c>
+      <c r="D47" s="109" t="s">
+        <v>658</v>
       </c>
       <c r="E47" s="75" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="5" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C48" s="106" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D48" s="108" t="s">
         <v>648</v>
       </c>
       <c r="E48" s="75" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="C49" s="106" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="D49" s="108" t="s">
         <v>648</v>
       </c>
       <c r="E49" s="75" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C50" s="106" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D50" s="108" t="s">
         <v>648</v>
       </c>
       <c r="E50" s="75" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C51" s="106" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="D51" s="108" t="s">
         <v>648</v>
       </c>
       <c r="E51" s="75" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="5" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C52" s="106" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D52" s="108" t="s">
         <v>648</v>
       </c>
       <c r="E52" s="75" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C53" s="106" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D53" s="108" t="s">
         <v>648</v>
       </c>
       <c r="E53" s="75" t="s">
-        <v>719</v>
+        <v>772</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C54" s="106" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D54" s="108" t="s">
         <v>648</v>
       </c>
       <c r="E54" s="75" t="s">
-        <v>719</v>
+        <v>775</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C55" s="106" t="s">
+        <v>777</v>
+      </c>
+      <c r="D55" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="E55" s="75" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="11" t="s">
-        <v>778</v>
+      <c r="B56" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="C56" s="106" t="s">
+        <v>780</v>
+      </c>
+      <c r="D56" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="E56" s="75" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="11" t="s">
-        <v>779</v>
+      <c r="B57" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C57" s="106" t="s">
+        <v>783</v>
+      </c>
+      <c r="D57" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="E57" s="75" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="11" t="s">
-        <v>780</v>
+      <c r="B58" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C58" s="106" t="s">
+        <v>786</v>
+      </c>
+      <c r="D58" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="E58" s="75" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="11" t="s">
-        <v>781</v>
+      <c r="B59" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="C59" s="106" t="s">
+        <v>789</v>
+      </c>
+      <c r="D59" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="E59" s="75" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="11" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="11" t="s">
-        <v>783</v>
+      <c r="B60" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="C60" s="106" t="s">
+        <v>791</v>
+      </c>
+      <c r="D60" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="E60" s="75" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="11" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="11" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="11" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="11" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="11" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="11" t="s">
+        <v>797</v>
       </c>
     </row>
   </sheetData>
@@ -8118,7 +8244,7 @@
         <v>85</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>86</v>
@@ -8130,7 +8256,7 @@
       </c>
       <c r="C21" s="23" t="n">
         <f aca="false">C19-C20</f>
-        <v>1462</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8139,7 +8265,7 @@
       </c>
       <c r="C22" s="23" t="n">
         <f aca="false">C13-C21</f>
-        <v>16183.6</v>
+        <v>16208.6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11602,43 +11728,43 @@
       </c>
       <c r="F13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!F25</f>
-        <v>-368</v>
+        <v>-438.495</v>
       </c>
       <c r="G13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!G25</f>
-        <v>-400.66</v>
+        <v>-463.048075</v>
       </c>
       <c r="H13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!H25</f>
-        <v>-455.7841</v>
+        <v>-510.997546375</v>
       </c>
       <c r="I13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!I25</f>
-        <v>-520.6689285</v>
+        <v>-569.532828541875</v>
       </c>
       <c r="J13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!J25</f>
-        <v>-548.1920017225</v>
+        <v>-591.436553259559</v>
       </c>
       <c r="K13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!K25</f>
-        <v>-549.549921524413</v>
+        <v>-587.82134963471</v>
       </c>
       <c r="L13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!L25</f>
-        <v>-546.151680549105</v>
+        <v>-580.021894426719</v>
       </c>
       <c r="M13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!M25</f>
-        <v>-532.794237285958</v>
+        <v>-562.769376567646</v>
       </c>
       <c r="N13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!N25</f>
-        <v>-516.372899998073</v>
+        <v>-542.900898262367</v>
       </c>
       <c r="O13" s="50" t="n">
         <f aca="false">-'Balance Sheet'!O25</f>
-        <v>-499.540016498294</v>
+        <v>-523.017294962194</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11659,43 +11785,43 @@
       </c>
       <c r="F14" s="23" t="n">
         <f aca="false">F11+F13</f>
-        <v>1363.2975</v>
+        <v>1292.8025</v>
       </c>
       <c r="G14" s="23" t="n">
         <f aca="false">G11+G13</f>
-        <v>1506.27901492537</v>
+        <v>1443.89093992537</v>
       </c>
       <c r="H14" s="23" t="n">
         <f aca="false">H11+H13</f>
-        <v>1518.29832647059</v>
+        <v>1463.08488009559</v>
       </c>
       <c r="I14" s="23" t="n">
         <f aca="false">I11+I13</f>
-        <v>1785.47994038587</v>
+        <v>1736.61604034399</v>
       </c>
       <c r="J14" s="23" t="n">
         <f aca="false">J11+J13</f>
-        <v>2138.73452366813</v>
+        <v>2095.48997213107</v>
       </c>
       <c r="K14" s="23" t="n">
         <f aca="false">K11+K13</f>
-        <v>2815.78004825098</v>
+        <v>2777.50862014068</v>
       </c>
       <c r="L14" s="23" t="n">
         <f aca="false">L11+L13</f>
-        <v>3295.78994472067</v>
+        <v>3261.91973084306</v>
       </c>
       <c r="M14" s="23" t="n">
         <f aca="false">M11+M13</f>
-        <v>3491.38561611556</v>
+        <v>3461.41047683387</v>
       </c>
       <c r="N14" s="23" t="n">
         <f aca="false">N11+N13</f>
-        <v>3572.25382473848</v>
+        <v>3545.72582647419</v>
       </c>
       <c r="O14" s="23" t="n">
         <f aca="false">O11+O13</f>
-        <v>3586.19300135668</v>
+        <v>3562.71572289278</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11713,43 +11839,43 @@
       </c>
       <c r="F15" s="50" t="n">
         <f aca="false">'Balance Sheet'!F26</f>
-        <v>39.85</v>
+        <v>38.2875</v>
       </c>
       <c r="G15" s="50" t="n">
         <f aca="false">'Balance Sheet'!G26</f>
-        <v>53.8760799624615</v>
+        <v>53.7210529624615</v>
       </c>
       <c r="H15" s="50" t="n">
         <f aca="false">'Balance Sheet'!H26</f>
-        <v>64.6183905088303</v>
+        <v>65.7330417096303</v>
       </c>
       <c r="I15" s="50" t="n">
         <f aca="false">'Balance Sheet'!I26</f>
-        <v>72.8593338280009</v>
+        <v>75.1221864983866</v>
       </c>
       <c r="J15" s="50" t="n">
         <f aca="false">'Balance Sheet'!J26</f>
-        <v>87.7062541062278</v>
+        <v>91.2712481150876</v>
       </c>
       <c r="K15" s="50" t="n">
         <f aca="false">'Balance Sheet'!K26</f>
-        <v>116.582849411795</v>
+        <v>121.322111676742</v>
       </c>
       <c r="L15" s="50" t="n">
         <f aca="false">'Balance Sheet'!L26</f>
-        <v>155.79072684005</v>
+        <v>161.591395907575</v>
       </c>
       <c r="M15" s="50" t="n">
         <f aca="false">'Balance Sheet'!M26</f>
-        <v>206.602043463865</v>
+        <v>213.364547459152</v>
       </c>
       <c r="N15" s="50" t="n">
         <f aca="false">'Balance Sheet'!N26</f>
-        <v>263.253160189415</v>
+        <v>270.88969286196</v>
       </c>
       <c r="O15" s="50" t="n">
         <f aca="false">'Balance Sheet'!O26</f>
-        <v>322.502453978328</v>
+        <v>330.935626063161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11770,43 +11896,43 @@
       </c>
       <c r="F16" s="50" t="n">
         <f aca="false">F14+F15</f>
-        <v>1403.1475</v>
+        <v>1331.09</v>
       </c>
       <c r="G16" s="50" t="n">
         <f aca="false">G14+G15</f>
-        <v>1560.15509488783</v>
+        <v>1497.61199288783</v>
       </c>
       <c r="H16" s="50" t="n">
         <f aca="false">H14+H15</f>
-        <v>1582.91671697942</v>
+        <v>1528.81792180522</v>
       </c>
       <c r="I16" s="50" t="n">
         <f aca="false">I14+I15</f>
-        <v>1858.33927421387</v>
+        <v>1811.73822684238</v>
       </c>
       <c r="J16" s="50" t="n">
         <f aca="false">J14+J15</f>
-        <v>2226.44077777435</v>
+        <v>2186.76122024615</v>
       </c>
       <c r="K16" s="50" t="n">
         <f aca="false">K14+K15</f>
-        <v>2932.36289766277</v>
+        <v>2898.83073181742</v>
       </c>
       <c r="L16" s="50" t="n">
         <f aca="false">L14+L15</f>
-        <v>3451.58067156072</v>
+        <v>3423.51112675063</v>
       </c>
       <c r="M16" s="50" t="n">
         <f aca="false">M14+M15</f>
-        <v>3697.98765957943</v>
+        <v>3674.77502429303</v>
       </c>
       <c r="N16" s="50" t="n">
         <f aca="false">N14+N15</f>
-        <v>3835.5069849279</v>
+        <v>3816.61551933615</v>
       </c>
       <c r="O16" s="50" t="n">
         <f aca="false">O14+O15</f>
-        <v>3908.69545533501</v>
+        <v>3893.65134895594</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11827,43 +11953,43 @@
       </c>
       <c r="F17" s="50" t="n">
         <f aca="false">-MAX(0,F16)*Assumptions!$C$31</f>
-        <v>-420.94425</v>
+        <v>-399.327</v>
       </c>
       <c r="G17" s="50" t="n">
         <f aca="false">-MAX(0,G16)*Assumptions!$C$31</f>
-        <v>-468.04652846635</v>
+        <v>-449.28359786635</v>
       </c>
       <c r="H17" s="50" t="n">
         <f aca="false">-MAX(0,H16)*Assumptions!$C$31</f>
-        <v>-474.875015093826</v>
+        <v>-458.645376541566</v>
       </c>
       <c r="I17" s="50" t="n">
         <f aca="false">-MAX(0,I16)*Assumptions!$C$31</f>
-        <v>-557.501782264161</v>
+        <v>-543.521468052715</v>
       </c>
       <c r="J17" s="50" t="n">
         <f aca="false">-MAX(0,J16)*Assumptions!$C$31</f>
-        <v>-667.932233332306</v>
+        <v>-656.028366073846</v>
       </c>
       <c r="K17" s="50" t="n">
         <f aca="false">-MAX(0,K16)*Assumptions!$C$31</f>
-        <v>-879.708869298832</v>
+        <v>-869.649219545227</v>
       </c>
       <c r="L17" s="50" t="n">
         <f aca="false">-MAX(0,L16)*Assumptions!$C$31</f>
-        <v>-1035.47420146822</v>
+        <v>-1027.05333802519</v>
       </c>
       <c r="M17" s="50" t="n">
         <f aca="false">-MAX(0,M16)*Assumptions!$C$31</f>
-        <v>-1109.39629787383</v>
+        <v>-1102.43250728791</v>
       </c>
       <c r="N17" s="50" t="n">
         <f aca="false">-MAX(0,N16)*Assumptions!$C$31</f>
-        <v>-1150.65209547837</v>
+        <v>-1144.98465580085</v>
       </c>
       <c r="O17" s="50" t="n">
         <f aca="false">-MAX(0,O16)*Assumptions!$C$31</f>
-        <v>-1172.6086366005</v>
+        <v>-1168.09540468678</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11884,43 +12010,43 @@
       </c>
       <c r="F18" s="23" t="n">
         <f aca="false">F16+F17</f>
-        <v>982.20325</v>
+        <v>931.763</v>
       </c>
       <c r="G18" s="23" t="n">
         <f aca="false">G16+G17</f>
-        <v>1092.10856642148</v>
+        <v>1048.32839502148</v>
       </c>
       <c r="H18" s="23" t="n">
         <f aca="false">H16+H17</f>
-        <v>1108.04170188559</v>
+        <v>1070.17254526365</v>
       </c>
       <c r="I18" s="23" t="n">
         <f aca="false">I16+I17</f>
-        <v>1300.83749194971</v>
+        <v>1268.21675878967</v>
       </c>
       <c r="J18" s="23" t="n">
         <f aca="false">J16+J17</f>
-        <v>1558.50854444205</v>
+        <v>1530.73285417231</v>
       </c>
       <c r="K18" s="23" t="n">
         <f aca="false">K16+K17</f>
-        <v>2052.65402836394</v>
+        <v>2029.1815122722</v>
       </c>
       <c r="L18" s="23" t="n">
         <f aca="false">L16+L17</f>
-        <v>2416.1064700925</v>
+        <v>2396.45778872544</v>
       </c>
       <c r="M18" s="23" t="n">
         <f aca="false">M16+M17</f>
-        <v>2588.5913617056</v>
+        <v>2572.34251700512</v>
       </c>
       <c r="N18" s="23" t="n">
         <f aca="false">N16+N17</f>
-        <v>2684.85488944953</v>
+        <v>2671.63086353531</v>
       </c>
       <c r="O18" s="23" t="n">
         <f aca="false">O16+O17</f>
-        <v>2736.0868187345</v>
+        <v>2725.55594426916</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11985,43 +12111,43 @@
       </c>
       <c r="F21" s="53" t="n">
         <f aca="false">F18/Assumptions!$C$12</f>
-        <v>0.305032065217391</v>
+        <v>0.289367391304348</v>
       </c>
       <c r="G21" s="53" t="n">
         <f aca="false">G18/Assumptions!$C$12</f>
-        <v>0.339164151062573</v>
+        <v>0.325567824540834</v>
       </c>
       <c r="H21" s="53" t="n">
         <f aca="false">H18/Assumptions!$C$12</f>
-        <v>0.344112329778134</v>
+        <v>0.332351722131569</v>
       </c>
       <c r="I21" s="53" t="n">
         <f aca="false">I18/Assumptions!$C$12</f>
-        <v>0.403986798742146</v>
+        <v>0.393856136270083</v>
       </c>
       <c r="J21" s="53" t="n">
         <f aca="false">J18/Assumptions!$C$12</f>
-        <v>0.484008864733555</v>
+        <v>0.475382873966555</v>
       </c>
       <c r="K21" s="53" t="n">
         <f aca="false">K18/Assumptions!$C$12</f>
-        <v>0.637470195144081</v>
+        <v>0.630180593873353</v>
       </c>
       <c r="L21" s="53" t="n">
         <f aca="false">L18/Assumptions!$C$12</f>
-        <v>0.750343624252331</v>
+        <v>0.744241549293616</v>
       </c>
       <c r="M21" s="53" t="n">
         <f aca="false">M18/Assumptions!$C$12</f>
-        <v>0.803910360778136</v>
+        <v>0.798864135715875</v>
       </c>
       <c r="N21" s="53" t="n">
         <f aca="false">N18/Assumptions!$C$12</f>
-        <v>0.833805866288674</v>
+        <v>0.829699025942642</v>
       </c>
       <c r="O21" s="53" t="n">
         <f aca="false">O18/Assumptions!$C$12</f>
-        <v>0.849716403333697</v>
+        <v>0.846445945425204</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12068,43 +12194,43 @@
       </c>
       <c r="F23" s="53" t="n">
         <f aca="false">MAX(0,F21)*F22</f>
-        <v>0.0915096195652174</v>
+        <v>0.0868102173913043</v>
       </c>
       <c r="G23" s="53" t="n">
         <f aca="false">MAX(0,G21)*G22</f>
-        <v>0.101749245318772</v>
+        <v>0.0976703473622501</v>
       </c>
       <c r="H23" s="53" t="n">
         <f aca="false">MAX(0,H21)*H22</f>
-        <v>0.10323369893344</v>
+        <v>0.0997055166394708</v>
       </c>
       <c r="I23" s="53" t="n">
         <f aca="false">MAX(0,I21)*I22</f>
-        <v>0.201993399371073</v>
+        <v>0.196928068135041</v>
       </c>
       <c r="J23" s="53" t="n">
         <f aca="false">MAX(0,J21)*J22</f>
-        <v>0.242004432366778</v>
+        <v>0.237691436983277</v>
       </c>
       <c r="K23" s="53" t="n">
         <f aca="false">MAX(0,K21)*K22</f>
-        <v>0.31873509757204</v>
+        <v>0.315090296936676</v>
       </c>
       <c r="L23" s="53" t="n">
         <f aca="false">MAX(0,L21)*L22</f>
-        <v>0.375171812126165</v>
+        <v>0.372120774646808</v>
       </c>
       <c r="M23" s="53" t="n">
         <f aca="false">MAX(0,M21)*M22</f>
-        <v>0.401955180389068</v>
+        <v>0.399432067857938</v>
       </c>
       <c r="N23" s="53" t="n">
         <f aca="false">MAX(0,N21)*N22</f>
-        <v>0.416902933144337</v>
+        <v>0.414849512971321</v>
       </c>
       <c r="O23" s="53" t="n">
         <f aca="false">MAX(0,O21)*O22</f>
-        <v>0.424858201666848</v>
+        <v>0.423222972712602</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12113,43 +12239,43 @@
       </c>
       <c r="F24" s="50" t="n">
         <f aca="false">F23*Assumptions!$C$12</f>
-        <v>294.660975</v>
+        <v>279.5289</v>
       </c>
       <c r="G24" s="50" t="n">
         <f aca="false">G23*Assumptions!$C$12</f>
-        <v>327.632569926445</v>
+        <v>314.498518506445</v>
       </c>
       <c r="H24" s="50" t="n">
         <f aca="false">H23*Assumptions!$C$12</f>
-        <v>332.412510565678</v>
+        <v>321.051763579096</v>
       </c>
       <c r="I24" s="50" t="n">
         <f aca="false">I23*Assumptions!$C$12</f>
-        <v>650.418745974855</v>
+        <v>634.108379394834</v>
       </c>
       <c r="J24" s="50" t="n">
         <f aca="false">J23*Assumptions!$C$12</f>
-        <v>779.254272221024</v>
+        <v>765.366427086153</v>
       </c>
       <c r="K24" s="50" t="n">
         <f aca="false">K23*Assumptions!$C$12</f>
-        <v>1026.32701418197</v>
+        <v>1014.5907561361</v>
       </c>
       <c r="L24" s="50" t="n">
         <f aca="false">L23*Assumptions!$C$12</f>
-        <v>1208.05323504625</v>
+        <v>1198.22889436272</v>
       </c>
       <c r="M24" s="50" t="n">
         <f aca="false">M23*Assumptions!$C$12</f>
-        <v>1294.2956808528</v>
+        <v>1286.17125850256</v>
       </c>
       <c r="N24" s="50" t="n">
         <f aca="false">N23*Assumptions!$C$12</f>
-        <v>1342.42744472476</v>
+        <v>1335.81543176765</v>
       </c>
       <c r="O24" s="50" t="n">
         <f aca="false">O23*Assumptions!$C$12</f>
-        <v>1368.04340936725</v>
+        <v>1362.77797213458</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12158,43 +12284,43 @@
       </c>
       <c r="F25" s="24" t="n">
         <f aca="false">F23/Assumptions!$C$11</f>
-        <v>0.0166988356870835</v>
+        <v>0.0158412805458585</v>
       </c>
       <c r="G25" s="24" t="n">
         <f aca="false">G23/Assumptions!$C$11</f>
-        <v>0.0185673805326226</v>
+        <v>0.0178230560880018</v>
       </c>
       <c r="H25" s="24" t="n">
         <f aca="false">H23/Assumptions!$C$11</f>
-        <v>0.01883826622873</v>
+        <v>0.0181944373429691</v>
       </c>
       <c r="I25" s="24" t="n">
         <f aca="false">I23/Assumptions!$C$11</f>
-        <v>0.0368601093742834</v>
+        <v>0.0359357788567594</v>
       </c>
       <c r="J25" s="24" t="n">
         <f aca="false">J23/Assumptions!$C$11</f>
-        <v>0.0441613927676601</v>
+        <v>0.0433743498144667</v>
       </c>
       <c r="K25" s="24" t="n">
         <f aca="false">K23/Assumptions!$C$11</f>
-        <v>0.0581633389730001</v>
+        <v>0.0574982293680066</v>
       </c>
       <c r="L25" s="24" t="n">
         <f aca="false">L23/Assumptions!$C$11</f>
-        <v>0.068462009512074</v>
+        <v>0.0679052508479576</v>
       </c>
       <c r="M25" s="24" t="n">
         <f aca="false">M23/Assumptions!$C$11</f>
-        <v>0.0733494854724577</v>
+        <v>0.0728890634777258</v>
       </c>
       <c r="N25" s="24" t="n">
         <f aca="false">N23/Assumptions!$C$11</f>
-        <v>0.0760771775810834</v>
+        <v>0.075702465870679</v>
       </c>
       <c r="O25" s="24" t="n">
         <f aca="false">O23/Assumptions!$C$11</f>
-        <v>0.0775288689173081</v>
+        <v>0.0772304694731026</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12476,43 +12602,43 @@
       </c>
       <c r="F13" s="48" t="n">
         <f aca="false">'Cash Flow'!F23</f>
-        <v>2640.65199906154</v>
+        <v>2675.83882406154</v>
       </c>
       <c r="G13" s="48" t="n">
         <f aca="false">'Cash Flow'!G23</f>
-        <v>2909.20976272076</v>
+        <v>2976.13854274076</v>
       </c>
       <c r="H13" s="48" t="n">
         <f aca="false">'Cash Flow'!H23</f>
-        <v>3115.23334570002</v>
+        <v>3210.86716245966</v>
       </c>
       <c r="I13" s="48" t="n">
         <f aca="false">'Cash Flow'!I23</f>
-        <v>3486.4063526557</v>
+        <v>3614.59370287719</v>
       </c>
       <c r="J13" s="48" t="n">
         <f aca="false">'Cash Flow'!J23</f>
-        <v>4208.32123529487</v>
+        <v>4365.86529191856</v>
       </c>
       <c r="K13" s="48" t="n">
         <f aca="false">'Cash Flow'!K23</f>
-        <v>5188.51817100126</v>
+        <v>5372.59739768936</v>
       </c>
       <c r="L13" s="48" t="n">
         <f aca="false">'Cash Flow'!L23</f>
-        <v>6458.80108659661</v>
+        <v>6666.9261864788</v>
       </c>
       <c r="M13" s="48" t="n">
         <f aca="false">'Cash Flow'!M23</f>
-        <v>7875.07900473537</v>
+        <v>8105.05482154901</v>
       </c>
       <c r="N13" s="48" t="n">
         <f aca="false">'Cash Flow'!N23</f>
-        <v>9356.31134945821</v>
+        <v>9606.20315157903</v>
       </c>
       <c r="O13" s="48" t="n">
         <f aca="false">'Cash Flow'!O23</f>
-        <v>10853.8947753238</v>
+        <v>11121.9984186758</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12569,47 +12695,47 @@
         <v>236</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>3200</v>
+        <v>3813</v>
       </c>
       <c r="F15" s="50" t="n">
         <f aca="false">E15+Deck!F57-F25</f>
-        <v>3484</v>
+        <v>4026.505</v>
       </c>
       <c r="G15" s="50" t="n">
         <f aca="false">F15+Deck!G57-G25</f>
-        <v>3963.34</v>
+        <v>4443.456925</v>
       </c>
       <c r="H15" s="50" t="n">
         <f aca="false">G15+Deck!H57-H25</f>
-        <v>4527.5559</v>
+        <v>4952.459378625</v>
       </c>
       <c r="I15" s="50" t="n">
         <f aca="false">H15+Deck!I57-I25</f>
-        <v>4766.8869715</v>
+        <v>5142.92655008313</v>
       </c>
       <c r="J15" s="50" t="n">
         <f aca="false">I15+Deck!J57-J25</f>
-        <v>4778.6949697775</v>
+        <v>5111.48999682357</v>
       </c>
       <c r="K15" s="50" t="n">
         <f aca="false">J15+Deck!K57-K25</f>
-        <v>4749.14504825309</v>
+        <v>5043.66864718886</v>
       </c>
       <c r="L15" s="50" t="n">
         <f aca="false">K15+Deck!L57-L25</f>
-        <v>4632.99336770398</v>
+        <v>4893.64675276214</v>
       </c>
       <c r="M15" s="50" t="n">
         <f aca="false">L15+Deck!M57-M25</f>
-        <v>4490.19913041803</v>
+        <v>4720.87737619449</v>
       </c>
       <c r="N15" s="50" t="n">
         <f aca="false">M15+Deck!N57-N25</f>
-        <v>4343.82623041995</v>
+        <v>4547.97647793213</v>
       </c>
       <c r="O15" s="50" t="n">
         <f aca="false">N15+Deck!O57-O25</f>
-        <v>4214.28621392166</v>
+        <v>4394.95918296993</v>
       </c>
       <c r="Q15" s="11" t="s">
         <v>237</v>
@@ -12621,47 +12747,47 @@
       </c>
       <c r="E16" s="23" t="n">
         <f aca="false">SUM(E13:E15)</f>
-        <v>5644.71372406154</v>
+        <v>6257.71372406154</v>
       </c>
       <c r="F16" s="23" t="n">
         <f aca="false">SUM(F13:F15)</f>
-        <v>6332.25599906154</v>
+        <v>6909.94782406154</v>
       </c>
       <c r="G16" s="23" t="n">
         <f aca="false">SUM(G13:G15)</f>
-        <v>7096.73199555658</v>
+        <v>7643.77770057658</v>
       </c>
       <c r="H16" s="23" t="n">
         <f aca="false">SUM(H13:H15)</f>
-        <v>7872.36118687649</v>
+        <v>8392.89848226114</v>
       </c>
       <c r="I16" s="23" t="n">
         <f aca="false">SUM(I13:I15)</f>
-        <v>8522.77993285135</v>
+        <v>9027.00686165597</v>
       </c>
       <c r="J16" s="23" t="n">
         <f aca="false">SUM(J13:J15)</f>
-        <v>9302.03420507237</v>
+        <v>9792.37328874212</v>
       </c>
       <c r="K16" s="23" t="n">
         <f aca="false">SUM(K13:K15)</f>
-        <v>10328.3612192543</v>
+        <v>10806.9640448782</v>
       </c>
       <c r="L16" s="23" t="n">
         <f aca="false">SUM(L13:L15)</f>
-        <v>11536.4144543006</v>
+        <v>12005.1929392409</v>
       </c>
       <c r="M16" s="23" t="n">
         <f aca="false">SUM(M13:M15)</f>
-        <v>12830.7101351534</v>
+        <v>13291.3641977435</v>
       </c>
       <c r="N16" s="23" t="n">
         <f aca="false">SUM(N13:N15)</f>
-        <v>14173.1375798782</v>
+        <v>14627.1796295112</v>
       </c>
       <c r="O16" s="23" t="n">
         <f aca="false">SUM(O13:O15)</f>
-        <v>15541.1809892454</v>
+        <v>15989.9576016457</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12688,47 +12814,47 @@
       </c>
       <c r="E19" s="48" t="n">
         <f aca="false">Assumptions!$C$20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="F19" s="50" t="n">
         <f aca="false">E19+'Cash Flow'!F20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="G19" s="50" t="n">
         <f aca="false">F19+'Cash Flow'!G20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="H19" s="50" t="n">
         <f aca="false">G19+'Cash Flow'!H20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="I19" s="50" t="n">
         <f aca="false">H19+'Cash Flow'!I20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="J19" s="50" t="n">
         <f aca="false">I19+'Cash Flow'!J20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="K19" s="50" t="n">
         <f aca="false">J19+'Cash Flow'!K20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="L19" s="50" t="n">
         <f aca="false">K19+'Cash Flow'!L20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="M19" s="50" t="n">
         <f aca="false">L19+'Cash Flow'!M20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="N19" s="50" t="n">
         <f aca="false">M19+'Cash Flow'!N20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="O19" s="50" t="n">
         <f aca="false">N19+'Cash Flow'!O20</f>
-        <v>828</v>
+        <v>853</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12737,47 +12863,47 @@
       </c>
       <c r="E20" s="50" t="n">
         <f aca="false">E16-E19</f>
-        <v>4816.71372406154</v>
+        <v>5404.71372406154</v>
       </c>
       <c r="F20" s="50" t="n">
         <f aca="false">E20+'Income Statement'!F18-'Income Statement'!F24</f>
-        <v>5504.25599906154</v>
+        <v>6056.94782406154</v>
       </c>
       <c r="G20" s="50" t="n">
         <f aca="false">F20+'Income Statement'!G18-'Income Statement'!G24</f>
-        <v>6268.73199555658</v>
+        <v>6790.77770057658</v>
       </c>
       <c r="H20" s="50" t="n">
         <f aca="false">G20+'Income Statement'!H18-'Income Statement'!H24</f>
-        <v>7044.36118687649</v>
+        <v>7539.89848226113</v>
       </c>
       <c r="I20" s="50" t="n">
         <f aca="false">H20+'Income Statement'!I18-'Income Statement'!I24</f>
-        <v>7694.77993285135</v>
+        <v>8174.00686165597</v>
       </c>
       <c r="J20" s="50" t="n">
         <f aca="false">I20+'Income Statement'!J18-'Income Statement'!J24</f>
-        <v>8474.03420507237</v>
+        <v>8939.37328874212</v>
       </c>
       <c r="K20" s="50" t="n">
         <f aca="false">J20+'Income Statement'!K18-'Income Statement'!K24</f>
-        <v>9500.36121925434</v>
+        <v>9953.96404487822</v>
       </c>
       <c r="L20" s="50" t="n">
         <f aca="false">K20+'Income Statement'!L18-'Income Statement'!L24</f>
-        <v>10708.4144543006</v>
+        <v>11152.1929392409</v>
       </c>
       <c r="M20" s="50" t="n">
         <f aca="false">L20+'Income Statement'!M18-'Income Statement'!M24</f>
-        <v>12002.7101351534</v>
+        <v>12438.3641977435</v>
       </c>
       <c r="N20" s="50" t="n">
         <f aca="false">M20+'Income Statement'!N18-'Income Statement'!N24</f>
-        <v>13345.1375798782</v>
+        <v>13774.1796295111</v>
       </c>
       <c r="O20" s="50" t="n">
         <f aca="false">N20+'Income Statement'!O18-'Income Statement'!O24</f>
-        <v>14713.1809892454</v>
+        <v>15136.9576016457</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12786,47 +12912,47 @@
       </c>
       <c r="E21" s="23" t="n">
         <f aca="false">E19+E20</f>
-        <v>5644.71372406154</v>
+        <v>6257.71372406154</v>
       </c>
       <c r="F21" s="23" t="n">
         <f aca="false">F19+F20</f>
-        <v>6332.25599906154</v>
+        <v>6909.94782406154</v>
       </c>
       <c r="G21" s="23" t="n">
         <f aca="false">G19+G20</f>
-        <v>7096.73199555658</v>
+        <v>7643.77770057658</v>
       </c>
       <c r="H21" s="23" t="n">
         <f aca="false">H19+H20</f>
-        <v>7872.36118687649</v>
+        <v>8392.89848226114</v>
       </c>
       <c r="I21" s="23" t="n">
         <f aca="false">I19+I20</f>
-        <v>8522.77993285135</v>
+        <v>9027.00686165597</v>
       </c>
       <c r="J21" s="23" t="n">
         <f aca="false">J19+J20</f>
-        <v>9302.03420507237</v>
+        <v>9792.37328874212</v>
       </c>
       <c r="K21" s="23" t="n">
         <f aca="false">K19+K20</f>
-        <v>10328.3612192543</v>
+        <v>10806.9640448782</v>
       </c>
       <c r="L21" s="23" t="n">
         <f aca="false">L19+L20</f>
-        <v>11536.4144543006</v>
+        <v>12005.1929392409</v>
       </c>
       <c r="M21" s="23" t="n">
         <f aca="false">M19+M20</f>
-        <v>12830.7101351534</v>
+        <v>13291.3641977435</v>
       </c>
       <c r="N21" s="23" t="n">
         <f aca="false">N19+N20</f>
-        <v>14173.1375798782</v>
+        <v>14627.1796295111</v>
       </c>
       <c r="O21" s="23" t="n">
         <f aca="false">O19+O20</f>
-        <v>15541.1809892454</v>
+        <v>15989.9576016457</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12902,43 +13028,43 @@
       </c>
       <c r="F25" s="50" t="n">
         <f aca="false">E15*F8</f>
-        <v>368</v>
+        <v>438.495</v>
       </c>
       <c r="G25" s="50" t="n">
         <f aca="false">F15*G8</f>
-        <v>400.66</v>
+        <v>463.048075</v>
       </c>
       <c r="H25" s="50" t="n">
         <f aca="false">G15*H8</f>
-        <v>455.7841</v>
+        <v>510.997546375</v>
       </c>
       <c r="I25" s="50" t="n">
         <f aca="false">H15*I8</f>
-        <v>520.6689285</v>
+        <v>569.532828541875</v>
       </c>
       <c r="J25" s="50" t="n">
         <f aca="false">I15*J8</f>
-        <v>548.1920017225</v>
+        <v>591.436553259559</v>
       </c>
       <c r="K25" s="50" t="n">
         <f aca="false">J15*K8</f>
-        <v>549.549921524413</v>
+        <v>587.82134963471</v>
       </c>
       <c r="L25" s="50" t="n">
         <f aca="false">K15*L8</f>
-        <v>546.151680549105</v>
+        <v>580.021894426719</v>
       </c>
       <c r="M25" s="50" t="n">
         <f aca="false">L15*M8</f>
-        <v>532.794237285958</v>
+        <v>562.769376567646</v>
       </c>
       <c r="N25" s="50" t="n">
         <f aca="false">M15*N8</f>
-        <v>516.372899998073</v>
+        <v>542.900898262367</v>
       </c>
       <c r="O25" s="50" t="n">
         <f aca="false">N15*O8</f>
-        <v>499.540016498294</v>
+        <v>523.017294962194</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12947,43 +13073,43 @@
       </c>
       <c r="F26" s="50" t="n">
         <f aca="false">E13*F9-E19*F10</f>
-        <v>39.85</v>
+        <v>38.2875</v>
       </c>
       <c r="G26" s="50" t="n">
         <f aca="false">F13*G9-F19*G10</f>
-        <v>53.8760799624615</v>
+        <v>53.7210529624615</v>
       </c>
       <c r="H26" s="50" t="n">
         <f aca="false">G13*H9-G19*H10</f>
-        <v>64.6183905088303</v>
+        <v>65.7330417096303</v>
       </c>
       <c r="I26" s="50" t="n">
         <f aca="false">H13*I9-H19*I10</f>
-        <v>72.8593338280009</v>
+        <v>75.1221864983866</v>
       </c>
       <c r="J26" s="50" t="n">
         <f aca="false">I13*J9-I19*J10</f>
-        <v>87.7062541062278</v>
+        <v>91.2712481150876</v>
       </c>
       <c r="K26" s="50" t="n">
         <f aca="false">J13*K9-J19*K10</f>
-        <v>116.582849411795</v>
+        <v>121.322111676742</v>
       </c>
       <c r="L26" s="50" t="n">
         <f aca="false">K13*L9-K19*L10</f>
-        <v>155.79072684005</v>
+        <v>161.591395907575</v>
       </c>
       <c r="M26" s="50" t="n">
         <f aca="false">L13*M9-L19*M10</f>
-        <v>206.602043463865</v>
+        <v>213.364547459152</v>
       </c>
       <c r="N26" s="50" t="n">
         <f aca="false">M13*N9-M19*N10</f>
-        <v>263.253160189415</v>
+        <v>270.88969286196</v>
       </c>
       <c r="O26" s="50" t="n">
         <f aca="false">N13*O9-N19*O10</f>
-        <v>322.502453978328</v>
+        <v>330.935626063161</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12992,47 +13118,47 @@
       </c>
       <c r="E27" s="50" t="n">
         <f aca="false">E13-E19</f>
-        <v>1462</v>
+        <v>1437</v>
       </c>
       <c r="F27" s="50" t="n">
         <f aca="false">F13-F19</f>
-        <v>1812.65199906154</v>
+        <v>1822.83882406154</v>
       </c>
       <c r="G27" s="50" t="n">
         <f aca="false">G13-G19</f>
-        <v>2081.20976272076</v>
+        <v>2123.13854274076</v>
       </c>
       <c r="H27" s="50" t="n">
         <f aca="false">H13-H19</f>
-        <v>2287.23334570002</v>
+        <v>2357.86716245966</v>
       </c>
       <c r="I27" s="50" t="n">
         <f aca="false">I13-I19</f>
-        <v>2658.4063526557</v>
+        <v>2761.59370287719</v>
       </c>
       <c r="J27" s="50" t="n">
         <f aca="false">J13-J19</f>
-        <v>3380.32123529487</v>
+        <v>3512.86529191856</v>
       </c>
       <c r="K27" s="50" t="n">
         <f aca="false">K13-K19</f>
-        <v>4360.51817100126</v>
+        <v>4519.59739768936</v>
       </c>
       <c r="L27" s="50" t="n">
         <f aca="false">L13-L19</f>
-        <v>5630.80108659661</v>
+        <v>5813.9261864788</v>
       </c>
       <c r="M27" s="50" t="n">
         <f aca="false">M13-M19</f>
-        <v>7047.07900473537</v>
+        <v>7252.05482154901</v>
       </c>
       <c r="N27" s="50" t="n">
         <f aca="false">N13-N19</f>
-        <v>8528.31134945821</v>
+        <v>8753.20315157903</v>
       </c>
       <c r="O27" s="50" t="n">
         <f aca="false">O13-O19</f>
-        <v>10025.8947753238</v>
+        <v>10268.9984186758</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13041,43 +13167,43 @@
       </c>
       <c r="F28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!F18/E20,0)</f>
-        <v>0.203915637562904</v>
+        <v>0.172398215256404</v>
       </c>
       <c r="G28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!G18/F20,0)</f>
-        <v>0.198411659379158</v>
+        <v>0.173078657018795</v>
       </c>
       <c r="H28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!H18/G20,0)</f>
-        <v>0.176756910754998</v>
+        <v>0.157592045042616</v>
       </c>
       <c r="I28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!I18/H20,0)</f>
-        <v>0.184663656141474</v>
+        <v>0.168200773760198</v>
       </c>
       <c r="J28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!J18/I20,0)</f>
-        <v>0.202541015863014</v>
+        <v>0.187268359334628</v>
       </c>
       <c r="K28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!K18/J20,0)</f>
-        <v>0.242228669213451</v>
+        <v>0.226993710490607</v>
       </c>
       <c r="L28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!L18/K20,0)</f>
-        <v>0.254317326923927</v>
+        <v>0.240754113428663</v>
       </c>
       <c r="M28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!M18/L20,0)</f>
-        <v>0.241734327033448</v>
+        <v>0.230657999822966</v>
       </c>
       <c r="N28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!N18/M20,0)</f>
-        <v>0.223687388866133</v>
+        <v>0.214789567266408</v>
       </c>
       <c r="O28" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!O18/N20,0)</f>
-        <v>0.2050249989824</v>
+        <v>0.197874284899673</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13086,43 +13212,43 @@
       </c>
       <c r="F29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!F14*(1-Assumptions!$C$31)/(E15+E14),0)</f>
-        <v>0.284467864770477</v>
+        <v>0.228081412353923</v>
       </c>
       <c r="G29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!G14*(1-Assumptions!$C$31)/(F15+F14),0)</f>
-        <v>0.285619830959052</v>
+        <v>0.238709881570777</v>
       </c>
       <c r="H29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!H14*(1-Assumptions!$C$31)/(G15+G14),0)</f>
-        <v>0.253803745851319</v>
+        <v>0.219417007492449</v>
       </c>
       <c r="I29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!I14*(1-Assumptions!$C$31)/(H15+H14),0)</f>
-        <v>0.262729108823154</v>
+        <v>0.234585851227037</v>
       </c>
       <c r="J29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!J14*(1-Assumptions!$C$31)/(I15+I14),0)</f>
-        <v>0.297260348687146</v>
+        <v>0.271014598749279</v>
       </c>
       <c r="K29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!K14*(1-Assumptions!$C$31)/(J15+J14),0)</f>
-        <v>0.386956635654675</v>
+        <v>0.358288614931841</v>
       </c>
       <c r="L29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!L14*(1-Assumptions!$C$31)/(K15+K14),0)</f>
-        <v>0.448856694581089</v>
+        <v>0.420167419651615</v>
       </c>
       <c r="M29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!M14*(1-Assumptions!$C$31)/(L15+L14),0)</f>
-        <v>0.481322573086343</v>
+        <v>0.453890269258276</v>
       </c>
       <c r="N29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!N14*(1-Assumptions!$C$31)/(M15+M14),0)</f>
-        <v>0.504593181273766</v>
+        <v>0.478569228809318</v>
       </c>
       <c r="O29" s="24" t="n">
         <f aca="false">IFERROR('Income Statement'!O14*(1-Assumptions!$C$31)/(N15+N14),0)</f>
-        <v>0.521159572893875</v>
+        <v>0.496696412936005</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13287,43 +13413,43 @@
       </c>
       <c r="F9" s="48" t="n">
         <f aca="false">'Balance Sheet'!F26</f>
-        <v>39.85</v>
+        <v>38.2875</v>
       </c>
       <c r="G9" s="48" t="n">
         <f aca="false">'Balance Sheet'!G26</f>
-        <v>53.8760799624615</v>
+        <v>53.7210529624615</v>
       </c>
       <c r="H9" s="48" t="n">
         <f aca="false">'Balance Sheet'!H26</f>
-        <v>64.6183905088303</v>
+        <v>65.7330417096303</v>
       </c>
       <c r="I9" s="48" t="n">
         <f aca="false">'Balance Sheet'!I26</f>
-        <v>72.8593338280009</v>
+        <v>75.1221864983866</v>
       </c>
       <c r="J9" s="48" t="n">
         <f aca="false">'Balance Sheet'!J26</f>
-        <v>87.7062541062278</v>
+        <v>91.2712481150876</v>
       </c>
       <c r="K9" s="48" t="n">
         <f aca="false">'Balance Sheet'!K26</f>
-        <v>116.582849411795</v>
+        <v>121.322111676742</v>
       </c>
       <c r="L9" s="48" t="n">
         <f aca="false">'Balance Sheet'!L26</f>
-        <v>155.79072684005</v>
+        <v>161.591395907575</v>
       </c>
       <c r="M9" s="48" t="n">
         <f aca="false">'Balance Sheet'!M26</f>
-        <v>206.602043463865</v>
+        <v>213.364547459152</v>
       </c>
       <c r="N9" s="48" t="n">
         <f aca="false">'Balance Sheet'!N26</f>
-        <v>263.253160189415</v>
+        <v>270.88969286196</v>
       </c>
       <c r="O9" s="48" t="n">
         <f aca="false">'Balance Sheet'!O26</f>
-        <v>322.502453978328</v>
+        <v>330.935626063161</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13332,43 +13458,43 @@
       </c>
       <c r="F10" s="48" t="n">
         <f aca="false">'Income Statement'!F17</f>
-        <v>-420.94425</v>
+        <v>-399.327</v>
       </c>
       <c r="G10" s="48" t="n">
         <f aca="false">'Income Statement'!G17</f>
-        <v>-468.04652846635</v>
+        <v>-449.28359786635</v>
       </c>
       <c r="H10" s="48" t="n">
         <f aca="false">'Income Statement'!H17</f>
-        <v>-474.875015093826</v>
+        <v>-458.645376541566</v>
       </c>
       <c r="I10" s="48" t="n">
         <f aca="false">'Income Statement'!I17</f>
-        <v>-557.501782264161</v>
+        <v>-543.521468052715</v>
       </c>
       <c r="J10" s="48" t="n">
         <f aca="false">'Income Statement'!J17</f>
-        <v>-667.932233332306</v>
+        <v>-656.028366073846</v>
       </c>
       <c r="K10" s="48" t="n">
         <f aca="false">'Income Statement'!K17</f>
-        <v>-879.708869298832</v>
+        <v>-869.649219545227</v>
       </c>
       <c r="L10" s="48" t="n">
         <f aca="false">'Income Statement'!L17</f>
-        <v>-1035.47420146822</v>
+        <v>-1027.05333802519</v>
       </c>
       <c r="M10" s="48" t="n">
         <f aca="false">'Income Statement'!M17</f>
-        <v>-1109.39629787383</v>
+        <v>-1102.43250728791</v>
       </c>
       <c r="N10" s="48" t="n">
         <f aca="false">'Income Statement'!N17</f>
-        <v>-1150.65209547837</v>
+        <v>-1144.98465580085</v>
       </c>
       <c r="O10" s="48" t="n">
         <f aca="false">'Income Statement'!O17</f>
-        <v>-1172.6086366005</v>
+        <v>-1168.09540468678</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13422,43 +13548,43 @@
       </c>
       <c r="F12" s="23" t="n">
         <f aca="false">SUM(F8:F11)</f>
-        <v>1297.31297406154</v>
+        <v>1317.36772406154</v>
       </c>
       <c r="G12" s="23" t="n">
         <f aca="false">SUM(G8:G11)</f>
-        <v>1476.19033358566</v>
+        <v>1494.79823718566</v>
       </c>
       <c r="H12" s="23" t="n">
         <f aca="false">SUM(H8:H11)</f>
-        <v>1558.43609354494</v>
+        <v>1575.780383298</v>
       </c>
       <c r="I12" s="23" t="n">
         <f aca="false">SUM(I8:I11)</f>
-        <v>1781.59175293053</v>
+        <v>1797.83491981236</v>
       </c>
       <c r="J12" s="23" t="n">
         <f aca="false">SUM(J8:J11)</f>
-        <v>2061.1691548602</v>
+        <v>2076.63801612752</v>
       </c>
       <c r="K12" s="23" t="n">
         <f aca="false">SUM(K8:K11)</f>
-        <v>2526.52394988835</v>
+        <v>2541.32286190691</v>
       </c>
       <c r="L12" s="23" t="n">
         <f aca="false">SUM(L8:L11)</f>
-        <v>2908.33615064161</v>
+        <v>2922.55768315216</v>
       </c>
       <c r="M12" s="23" t="n">
         <f aca="false">SUM(M8:M11)</f>
-        <v>3100.57359899156</v>
+        <v>3114.29989357276</v>
       </c>
       <c r="N12" s="23" t="n">
         <f aca="false">SUM(N8:N11)</f>
-        <v>3193.6597894476</v>
+        <v>3206.96376179767</v>
       </c>
       <c r="O12" s="23" t="n">
         <f aca="false">SUM(O8:O11)</f>
-        <v>3235.6268352328</v>
+        <v>3248.57323923135</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13534,43 +13660,43 @@
       </c>
       <c r="F16" s="23" t="n">
         <f aca="false">F12+F15</f>
-        <v>645.312974061538</v>
+        <v>665.367724061538</v>
       </c>
       <c r="G16" s="23" t="n">
         <f aca="false">G12+G15</f>
-        <v>596.190333585663</v>
+        <v>614.798237185663</v>
       </c>
       <c r="H16" s="23" t="n">
         <f aca="false">H12+H15</f>
-        <v>538.436093544943</v>
+        <v>555.780383298003</v>
       </c>
       <c r="I16" s="23" t="n">
         <f aca="false">I12+I15</f>
-        <v>1021.59175293053</v>
+        <v>1037.83491981236</v>
       </c>
       <c r="J16" s="23" t="n">
         <f aca="false">J12+J15</f>
-        <v>1501.1691548602</v>
+        <v>1516.63801612752</v>
       </c>
       <c r="K16" s="23" t="n">
         <f aca="false">K12+K15</f>
-        <v>2006.52394988835</v>
+        <v>2021.32286190691</v>
       </c>
       <c r="L16" s="23" t="n">
         <f aca="false">L12+L15</f>
-        <v>2478.33615064161</v>
+        <v>2492.55768315216</v>
       </c>
       <c r="M16" s="23" t="n">
         <f aca="false">M12+M15</f>
-        <v>2710.57359899156</v>
+        <v>2724.29989357276</v>
       </c>
       <c r="N16" s="23" t="n">
         <f aca="false">N12+N15</f>
-        <v>2823.6597894476</v>
+        <v>2836.96376179767</v>
       </c>
       <c r="O16" s="23" t="n">
         <f aca="false">O12+O15</f>
-        <v>2865.6268352328</v>
+        <v>2878.57323923135</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13597,43 +13723,43 @@
       </c>
       <c r="F19" s="48" t="n">
         <f aca="false">-'Income Statement'!F24</f>
-        <v>-294.660975</v>
+        <v>-279.5289</v>
       </c>
       <c r="G19" s="48" t="n">
         <f aca="false">-'Income Statement'!G24</f>
-        <v>-327.632569926445</v>
+        <v>-314.498518506445</v>
       </c>
       <c r="H19" s="48" t="n">
         <f aca="false">-'Income Statement'!H24</f>
-        <v>-332.412510565678</v>
+        <v>-321.051763579096</v>
       </c>
       <c r="I19" s="48" t="n">
         <f aca="false">-'Income Statement'!I24</f>
-        <v>-650.418745974855</v>
+        <v>-634.108379394834</v>
       </c>
       <c r="J19" s="48" t="n">
         <f aca="false">-'Income Statement'!J24</f>
-        <v>-779.254272221024</v>
+        <v>-765.366427086153</v>
       </c>
       <c r="K19" s="48" t="n">
         <f aca="false">-'Income Statement'!K24</f>
-        <v>-1026.32701418197</v>
+        <v>-1014.5907561361</v>
       </c>
       <c r="L19" s="48" t="n">
         <f aca="false">-'Income Statement'!L24</f>
-        <v>-1208.05323504625</v>
+        <v>-1198.22889436272</v>
       </c>
       <c r="M19" s="48" t="n">
         <f aca="false">-'Income Statement'!M24</f>
-        <v>-1294.2956808528</v>
+        <v>-1286.17125850256</v>
       </c>
       <c r="N19" s="48" t="n">
         <f aca="false">-'Income Statement'!N24</f>
-        <v>-1342.42744472476</v>
+        <v>-1335.81543176765</v>
       </c>
       <c r="O19" s="48" t="n">
         <f aca="false">-'Income Statement'!O24</f>
-        <v>-1368.04340936725</v>
+        <v>-1362.77797213458</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13680,43 +13806,43 @@
       </c>
       <c r="F21" s="23" t="n">
         <f aca="false">F16+F19+F20</f>
-        <v>350.651999061538</v>
+        <v>385.838824061538</v>
       </c>
       <c r="G21" s="23" t="n">
         <f aca="false">G16+G19+G20</f>
-        <v>268.557763659218</v>
+        <v>300.299718679218</v>
       </c>
       <c r="H21" s="23" t="n">
         <f aca="false">H16+H19+H20</f>
-        <v>206.023582979265</v>
+        <v>234.728619718907</v>
       </c>
       <c r="I21" s="23" t="n">
         <f aca="false">I16+I19+I20</f>
-        <v>371.173006955673</v>
+        <v>403.726540417527</v>
       </c>
       <c r="J21" s="23" t="n">
         <f aca="false">J16+J19+J20</f>
-        <v>721.914882639175</v>
+        <v>751.271589041365</v>
       </c>
       <c r="K21" s="23" t="n">
         <f aca="false">K16+K19+K20</f>
-        <v>980.196935706383</v>
+        <v>1006.73210577081</v>
       </c>
       <c r="L21" s="23" t="n">
         <f aca="false">L16+L19+L20</f>
-        <v>1270.28291559536</v>
+        <v>1294.32878878944</v>
       </c>
       <c r="M21" s="23" t="n">
         <f aca="false">M16+M19+M20</f>
-        <v>1416.27791813876</v>
+        <v>1438.1286350702</v>
       </c>
       <c r="N21" s="23" t="n">
         <f aca="false">N16+N19+N20</f>
-        <v>1481.23234472284</v>
+        <v>1501.14833003002</v>
       </c>
       <c r="O21" s="23" t="n">
         <f aca="false">O16+O19+O20</f>
-        <v>1497.58342586555</v>
+        <v>1515.79526709677</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13729,39 +13855,39 @@
       </c>
       <c r="G22" s="48" t="n">
         <f aca="false">'Balance Sheet'!F13</f>
-        <v>2640.65199906154</v>
+        <v>2675.83882406154</v>
       </c>
       <c r="H22" s="48" t="n">
         <f aca="false">'Balance Sheet'!G13</f>
-        <v>2909.20976272076</v>
+        <v>2976.13854274076</v>
       </c>
       <c r="I22" s="48" t="n">
         <f aca="false">'Balance Sheet'!H13</f>
-        <v>3115.23334570002</v>
+        <v>3210.86716245966</v>
       </c>
       <c r="J22" s="48" t="n">
         <f aca="false">'Balance Sheet'!I13</f>
-        <v>3486.4063526557</v>
+        <v>3614.59370287719</v>
       </c>
       <c r="K22" s="48" t="n">
         <f aca="false">'Balance Sheet'!J13</f>
-        <v>4208.32123529487</v>
+        <v>4365.86529191856</v>
       </c>
       <c r="L22" s="48" t="n">
         <f aca="false">'Balance Sheet'!K13</f>
-        <v>5188.51817100126</v>
+        <v>5372.59739768936</v>
       </c>
       <c r="M22" s="48" t="n">
         <f aca="false">'Balance Sheet'!L13</f>
-        <v>6458.80108659661</v>
+        <v>6666.9261864788</v>
       </c>
       <c r="N22" s="48" t="n">
         <f aca="false">'Balance Sheet'!M13</f>
-        <v>7875.07900473537</v>
+        <v>8105.05482154901</v>
       </c>
       <c r="O22" s="48" t="n">
         <f aca="false">'Balance Sheet'!N13</f>
-        <v>9356.31134945821</v>
+        <v>9606.20315157903</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13770,43 +13896,43 @@
       </c>
       <c r="F23" s="23" t="n">
         <f aca="false">F22+F21</f>
-        <v>2640.65199906154</v>
+        <v>2675.83882406154</v>
       </c>
       <c r="G23" s="23" t="n">
         <f aca="false">G22+G21</f>
-        <v>2909.20976272076</v>
+        <v>2976.13854274076</v>
       </c>
       <c r="H23" s="23" t="n">
         <f aca="false">H22+H21</f>
-        <v>3115.23334570002</v>
+        <v>3210.86716245966</v>
       </c>
       <c r="I23" s="23" t="n">
         <f aca="false">I22+I21</f>
-        <v>3486.4063526557</v>
+        <v>3614.59370287719</v>
       </c>
       <c r="J23" s="23" t="n">
         <f aca="false">J22+J21</f>
-        <v>4208.32123529487</v>
+        <v>4365.86529191856</v>
       </c>
       <c r="K23" s="23" t="n">
         <f aca="false">K22+K21</f>
-        <v>5188.51817100126</v>
+        <v>5372.59739768936</v>
       </c>
       <c r="L23" s="23" t="n">
         <f aca="false">L22+L21</f>
-        <v>6458.80108659661</v>
+        <v>6666.9261864788</v>
       </c>
       <c r="M23" s="23" t="n">
         <f aca="false">M22+M21</f>
-        <v>7875.07900473537</v>
+        <v>8105.05482154901</v>
       </c>
       <c r="N23" s="23" t="n">
         <f aca="false">N22+N21</f>
-        <v>9356.31134945821</v>
+        <v>9606.20315157903</v>
       </c>
       <c r="O23" s="23" t="n">
         <f aca="false">O22+O21</f>
-        <v>10853.8947753238</v>
+        <v>11121.9984186758</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13904,43 +14030,43 @@
       </c>
       <c r="F7" s="48" t="n">
         <f aca="false">'Income Statement'!F14</f>
-        <v>1363.2975</v>
+        <v>1292.8025</v>
       </c>
       <c r="G7" s="48" t="n">
         <f aca="false">'Income Statement'!G14</f>
-        <v>1506.27901492537</v>
+        <v>1443.89093992537</v>
       </c>
       <c r="H7" s="48" t="n">
         <f aca="false">'Income Statement'!H14</f>
-        <v>1518.29832647059</v>
+        <v>1463.08488009559</v>
       </c>
       <c r="I7" s="48" t="n">
         <f aca="false">'Income Statement'!I14</f>
-        <v>1785.47994038587</v>
+        <v>1736.61604034399</v>
       </c>
       <c r="J7" s="48" t="n">
         <f aca="false">'Income Statement'!J14</f>
-        <v>2138.73452366813</v>
+        <v>2095.48997213107</v>
       </c>
       <c r="K7" s="48" t="n">
         <f aca="false">'Income Statement'!K14</f>
-        <v>2815.78004825098</v>
+        <v>2777.50862014068</v>
       </c>
       <c r="L7" s="48" t="n">
         <f aca="false">'Income Statement'!L14</f>
-        <v>3295.78994472067</v>
+        <v>3261.91973084306</v>
       </c>
       <c r="M7" s="48" t="n">
         <f aca="false">'Income Statement'!M14</f>
-        <v>3491.38561611556</v>
+        <v>3461.41047683387</v>
       </c>
       <c r="N7" s="48" t="n">
         <f aca="false">'Income Statement'!N14</f>
-        <v>3572.25382473848</v>
+        <v>3545.72582647419</v>
       </c>
       <c r="O7" s="48" t="n">
         <f aca="false">'Income Statement'!O14</f>
-        <v>3586.19300135668</v>
+        <v>3562.71572289278</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13949,43 +14075,43 @@
       </c>
       <c r="F8" s="50" t="n">
         <f aca="false">-MAX(0,F7)*Assumptions!$C$31</f>
-        <v>-408.98925</v>
+        <v>-387.84075</v>
       </c>
       <c r="G8" s="50" t="n">
         <f aca="false">-MAX(0,G7)*Assumptions!$C$31</f>
-        <v>-451.883704477612</v>
+        <v>-433.167281977612</v>
       </c>
       <c r="H8" s="50" t="n">
         <f aca="false">-MAX(0,H7)*Assumptions!$C$31</f>
-        <v>-455.489497941176</v>
+        <v>-438.925464028676</v>
       </c>
       <c r="I8" s="50" t="n">
         <f aca="false">-MAX(0,I7)*Assumptions!$C$31</f>
-        <v>-535.643982115761</v>
+        <v>-520.984812103199</v>
       </c>
       <c r="J8" s="50" t="n">
         <f aca="false">-MAX(0,J7)*Assumptions!$C$31</f>
-        <v>-641.620357100437</v>
+        <v>-628.64699163932</v>
       </c>
       <c r="K8" s="50" t="n">
         <f aca="false">-MAX(0,K7)*Assumptions!$C$31</f>
-        <v>-844.734014475293</v>
+        <v>-833.252586042204</v>
       </c>
       <c r="L8" s="50" t="n">
         <f aca="false">-MAX(0,L7)*Assumptions!$C$31</f>
-        <v>-988.736983416201</v>
+        <v>-978.575919252917</v>
       </c>
       <c r="M8" s="50" t="n">
         <f aca="false">-MAX(0,M7)*Assumptions!$C$31</f>
-        <v>-1047.41568483467</v>
+        <v>-1038.42314305016</v>
       </c>
       <c r="N8" s="50" t="n">
         <f aca="false">-MAX(0,N7)*Assumptions!$C$31</f>
-        <v>-1071.67614742155</v>
+        <v>-1063.71774794226</v>
       </c>
       <c r="O8" s="50" t="n">
         <f aca="false">-MAX(0,O7)*Assumptions!$C$31</f>
-        <v>-1075.857900407</v>
+        <v>-1068.81471686783</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13994,43 +14120,43 @@
       </c>
       <c r="F9" s="23" t="n">
         <f aca="false">F7+F8</f>
-        <v>954.30825</v>
+        <v>904.96175</v>
       </c>
       <c r="G9" s="23" t="n">
         <f aca="false">G7+G8</f>
-        <v>1054.39531044776</v>
+        <v>1010.72365794776</v>
       </c>
       <c r="H9" s="23" t="n">
         <f aca="false">H7+H8</f>
-        <v>1062.80882852941</v>
+        <v>1024.15941606691</v>
       </c>
       <c r="I9" s="23" t="n">
         <f aca="false">I7+I8</f>
-        <v>1249.83595827011</v>
+        <v>1215.6312282408</v>
       </c>
       <c r="J9" s="23" t="n">
         <f aca="false">J7+J8</f>
-        <v>1497.11416656769</v>
+        <v>1466.84298049175</v>
       </c>
       <c r="K9" s="23" t="n">
         <f aca="false">K7+K8</f>
-        <v>1971.04603377568</v>
+        <v>1944.25603409848</v>
       </c>
       <c r="L9" s="23" t="n">
         <f aca="false">L7+L8</f>
-        <v>2307.05296130447</v>
+        <v>2283.34381159014</v>
       </c>
       <c r="M9" s="23" t="n">
         <f aca="false">M7+M8</f>
-        <v>2443.96993128089</v>
+        <v>2422.98733378371</v>
       </c>
       <c r="N9" s="23" t="n">
         <f aca="false">N7+N8</f>
-        <v>2500.57767731694</v>
+        <v>2482.00807853193</v>
       </c>
       <c r="O9" s="23" t="n">
         <f aca="false">O7+O8</f>
-        <v>2510.33510094967</v>
+        <v>2493.90100602494</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14039,43 +14165,43 @@
       </c>
       <c r="F10" s="48" t="n">
         <f aca="false">'Balance Sheet'!F25</f>
-        <v>368</v>
+        <v>438.495</v>
       </c>
       <c r="G10" s="48" t="n">
         <f aca="false">'Balance Sheet'!G25</f>
-        <v>400.66</v>
+        <v>463.048075</v>
       </c>
       <c r="H10" s="48" t="n">
         <f aca="false">'Balance Sheet'!H25</f>
-        <v>455.7841</v>
+        <v>510.997546375</v>
       </c>
       <c r="I10" s="48" t="n">
         <f aca="false">'Balance Sheet'!I25</f>
-        <v>520.6689285</v>
+        <v>569.532828541875</v>
       </c>
       <c r="J10" s="48" t="n">
         <f aca="false">'Balance Sheet'!J25</f>
-        <v>548.1920017225</v>
+        <v>591.436553259559</v>
       </c>
       <c r="K10" s="48" t="n">
         <f aca="false">'Balance Sheet'!K25</f>
-        <v>549.549921524413</v>
+        <v>587.82134963471</v>
       </c>
       <c r="L10" s="48" t="n">
         <f aca="false">'Balance Sheet'!L25</f>
-        <v>546.151680549105</v>
+        <v>580.021894426719</v>
       </c>
       <c r="M10" s="48" t="n">
         <f aca="false">'Balance Sheet'!M25</f>
-        <v>532.794237285958</v>
+        <v>562.769376567646</v>
       </c>
       <c r="N10" s="48" t="n">
         <f aca="false">'Balance Sheet'!N25</f>
-        <v>516.372899998073</v>
+        <v>542.900898262367</v>
       </c>
       <c r="O10" s="48" t="n">
         <f aca="false">'Balance Sheet'!O25</f>
-        <v>499.540016498294</v>
+        <v>523.017294962194</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14174,43 +14300,43 @@
       </c>
       <c r="F13" s="23" t="n">
         <f aca="false">F9+F10+F11+F12</f>
-        <v>617.417974061538</v>
+        <v>638.566474061538</v>
       </c>
       <c r="G13" s="23" t="n">
         <f aca="false">G9+G10+G11+G12</f>
-        <v>558.47707761194</v>
+        <v>577.19350011194</v>
       </c>
       <c r="H13" s="23" t="n">
         <f aca="false">H9+H10+H11+H12</f>
-        <v>493.203220188762</v>
+        <v>509.767254101262</v>
       </c>
       <c r="I13" s="23" t="n">
         <f aca="false">I9+I10+I11+I12</f>
-        <v>970.590219250927</v>
+        <v>985.24938926349</v>
       </c>
       <c r="J13" s="23" t="n">
         <f aca="false">J9+J10+J11+J12</f>
-        <v>1439.77477698584</v>
+        <v>1452.74814244696</v>
       </c>
       <c r="K13" s="23" t="n">
         <f aca="false">K9+K10+K11+K12</f>
-        <v>1924.9159553001</v>
+        <v>1936.39738373319</v>
       </c>
       <c r="L13" s="23" t="n">
         <f aca="false">L9+L10+L11+L12</f>
-        <v>2369.28264185357</v>
+        <v>2379.44370601686</v>
       </c>
       <c r="M13" s="23" t="n">
         <f aca="false">M9+M10+M11+M12</f>
-        <v>2565.95216856685</v>
+        <v>2574.94471035136</v>
       </c>
       <c r="N13" s="23" t="n">
         <f aca="false">N9+N10+N11+N12</f>
-        <v>2639.38257731501</v>
+        <v>2647.3409767943</v>
       </c>
       <c r="O13" s="23" t="n">
         <f aca="false">O9+O10+O11+O12</f>
-        <v>2639.87511744797</v>
+        <v>2646.91830098714</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14299,43 +14425,43 @@
       </c>
       <c r="F16" s="50" t="n">
         <f aca="false">F13*F15</f>
-        <v>591.706321994264</v>
+        <v>611.974117355609</v>
       </c>
       <c r="G16" s="50" t="n">
         <f aca="false">G13*G15</f>
-        <v>491.570911415722</v>
+        <v>508.045085980071</v>
       </c>
       <c r="H16" s="50" t="n">
         <f aca="false">H13*H15</f>
-        <v>398.713195483293</v>
+        <v>412.103819512104</v>
       </c>
       <c r="I16" s="50" t="n">
         <f aca="false">I13*I15</f>
-        <v>720.650177937578</v>
+        <v>731.534414424242</v>
       </c>
       <c r="J16" s="50" t="n">
         <f aca="false">J13*J15</f>
-        <v>981.831656927598</v>
+        <v>990.678638490425</v>
       </c>
       <c r="K16" s="50" t="n">
         <f aca="false">K13*K15</f>
-        <v>1205.61356083483</v>
+        <v>1212.80461028225</v>
       </c>
       <c r="L16" s="50" t="n">
         <f aca="false">L13*L15</f>
-        <v>1362.90977645961</v>
+        <v>1368.75484257487</v>
       </c>
       <c r="M16" s="50" t="n">
         <f aca="false">M13*M15</f>
-        <v>1355.66590247826</v>
+        <v>1360.41691943922</v>
       </c>
       <c r="N16" s="50" t="n">
         <f aca="false">N13*N15</f>
-        <v>1280.73814365174</v>
+        <v>1284.59988990375</v>
       </c>
       <c r="O16" s="50" t="n">
         <f aca="false">O13*O15</f>
-        <v>1176.50902566487</v>
+        <v>1179.64795028614</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14353,7 +14479,7 @@
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">SUM(F16:O16)</f>
-        <v>9565.90867284777</v>
+        <v>9660.56028824868</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14371,7 +14497,7 @@
       </c>
       <c r="C21" s="50" t="n">
         <f aca="false">O13</f>
-        <v>2639.87511744797</v>
+        <v>2646.91830098714</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14428,7 +14554,7 @@
       </c>
       <c r="C27" s="50" t="n">
         <f aca="false">C21*C26</f>
-        <v>22201.0106502283</v>
+        <v>22260.2429191076</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14437,7 +14563,7 @@
       </c>
       <c r="C28" s="50" t="n">
         <f aca="false">C27*O15</f>
-        <v>9894.28978524025</v>
+        <v>9920.68773811559</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14446,7 +14572,7 @@
       </c>
       <c r="C29" s="23" t="n">
         <f aca="false">C19+C28</f>
-        <v>19460.198458088</v>
+        <v>19581.2480263643</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14455,7 +14581,7 @@
       </c>
       <c r="C30" s="24" t="n">
         <f aca="false">C28/C29</f>
-        <v>0.508437249833287</v>
+        <v>0.506642259204231</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>294</v>
@@ -14467,7 +14593,7 @@
       </c>
       <c r="C31" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
-        <v>1462</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14476,7 +14602,7 @@
       </c>
       <c r="C32" s="23" t="n">
         <f aca="false">C29+C31</f>
-        <v>20922.198458088</v>
+        <v>21018.2480263643</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14494,7 +14620,7 @@
       </c>
       <c r="C34" s="59" t="n">
         <f aca="false">C32/C33</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936779</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14512,7 +14638,7 @@
       </c>
       <c r="C36" s="60" t="n">
         <f aca="false">C34/C35-1</f>
-        <v>0.18568926293739</v>
+        <v>0.191132521782442</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15060,43 +15186,43 @@
       </c>
       <c r="F17" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15+F16-F18</f>
-        <v>3452</v>
+        <v>3994.505</v>
       </c>
       <c r="G17" s="50" t="n">
         <f aca="false">F17+G16-G18</f>
-        <v>3455.02</v>
+        <v>3935.136925</v>
       </c>
       <c r="H17" s="50" t="n">
         <f aca="false">G17+H16-H18</f>
-        <v>3397.6927</v>
+        <v>3822.596178625</v>
       </c>
       <c r="I17" s="50" t="n">
         <f aca="false">H17+I16-I18</f>
-        <v>3326.9580395</v>
+        <v>3702.99761808313</v>
       </c>
       <c r="J17" s="50" t="n">
         <f aca="false">I17+J16-J18</f>
-        <v>3244.3578649575</v>
+        <v>3577.15289200357</v>
       </c>
       <c r="K17" s="50" t="n">
         <f aca="false">J17+K16-K18</f>
-        <v>3166.25671048739</v>
+        <v>3460.78030942316</v>
       </c>
       <c r="L17" s="50" t="n">
         <f aca="false">K17+L16-L18</f>
-        <v>3092.13718878134</v>
+        <v>3352.79057383949</v>
       </c>
       <c r="M17" s="50" t="n">
         <f aca="false">L17+M16-M18</f>
-        <v>3026.54141207148</v>
+        <v>3257.21965784795</v>
       </c>
       <c r="N17" s="50" t="n">
         <f aca="false">M17+N16-N18</f>
-        <v>2968.48914968326</v>
+        <v>3172.63939719544</v>
       </c>
       <c r="O17" s="50" t="n">
         <f aca="false">N17+O16-O18</f>
-        <v>2917.11289746969</v>
+        <v>3097.78586651796</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15105,43 +15231,43 @@
       </c>
       <c r="F18" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15*'Balance Sheet'!F8</f>
-        <v>368</v>
+        <v>438.495</v>
       </c>
       <c r="G18" s="50" t="n">
         <f aca="false">F17*'Balance Sheet'!F8</f>
-        <v>396.98</v>
+        <v>459.368075</v>
       </c>
       <c r="H18" s="50" t="n">
         <f aca="false">G17*'Balance Sheet'!F8</f>
-        <v>397.3273</v>
+        <v>452.540746375</v>
       </c>
       <c r="I18" s="50" t="n">
         <f aca="false">H17*'Balance Sheet'!F8</f>
-        <v>390.7346605</v>
+        <v>439.598560541875</v>
       </c>
       <c r="J18" s="50" t="n">
         <f aca="false">I17*'Balance Sheet'!F8</f>
-        <v>382.6001745425</v>
+        <v>425.84472607956</v>
       </c>
       <c r="K18" s="50" t="n">
         <f aca="false">J17*'Balance Sheet'!F8</f>
-        <v>373.101154470113</v>
+        <v>411.37258258041</v>
       </c>
       <c r="L18" s="50" t="n">
         <f aca="false">K17*'Balance Sheet'!F8</f>
-        <v>364.11952170605</v>
+        <v>397.989735583663</v>
       </c>
       <c r="M18" s="50" t="n">
         <f aca="false">L17*'Balance Sheet'!F8</f>
-        <v>355.595776709854</v>
+        <v>385.570915991542</v>
       </c>
       <c r="N18" s="50" t="n">
         <f aca="false">M17*'Balance Sheet'!F8</f>
-        <v>348.052262388221</v>
+        <v>374.580260652514</v>
       </c>
       <c r="O18" s="50" t="n">
         <f aca="false">N17*'Balance Sheet'!F8</f>
-        <v>341.376252213575</v>
+        <v>364.853530677475</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15150,43 +15276,43 @@
       </c>
       <c r="F19" s="50" t="n">
         <f aca="false">F15-F18</f>
-        <v>786.6475</v>
+        <v>716.1525</v>
       </c>
       <c r="G19" s="50" t="n">
         <f aca="false">G15-G18</f>
-        <v>448.067014925373</v>
+        <v>385.678939925373</v>
       </c>
       <c r="H19" s="50" t="n">
         <f aca="false">H15-H18</f>
-        <v>257.542810294118</v>
+        <v>202.329363919118</v>
       </c>
       <c r="I19" s="50" t="n">
         <f aca="false">I15-I18</f>
-        <v>227.271817081522</v>
+        <v>178.407917039647</v>
       </c>
       <c r="J19" s="50" t="n">
         <f aca="false">J15-J18</f>
-        <v>346.944600848125</v>
+        <v>303.700049311065</v>
       </c>
       <c r="K19" s="50" t="n">
         <f aca="false">K15-K18</f>
-        <v>509.236493876707</v>
+        <v>470.965065766409</v>
       </c>
       <c r="L19" s="50" t="n">
         <f aca="false">L15-L18</f>
-        <v>648.916746420869</v>
+        <v>615.046532543255</v>
       </c>
       <c r="M19" s="50" t="n">
         <f aca="false">M15-M18</f>
-        <v>795.587862405952</v>
+        <v>765.612723124264</v>
       </c>
       <c r="N19" s="50" t="n">
         <f aca="false">N15-N18</f>
-        <v>878.300890919766</v>
+        <v>851.772892655472</v>
       </c>
       <c r="O19" s="50" t="n">
         <f aca="false">O15-O18</f>
-        <v>947.559908498539</v>
+        <v>924.082630034639</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15195,43 +15321,43 @@
       </c>
       <c r="F20" s="50" t="n">
         <f aca="false">F19*(1-Assumptions!$C$31)</f>
-        <v>550.65325</v>
+        <v>501.30675</v>
       </c>
       <c r="G20" s="50" t="n">
         <f aca="false">G19*(1-Assumptions!$C$31)</f>
-        <v>313.646910447761</v>
+        <v>269.975257947761</v>
       </c>
       <c r="H20" s="50" t="n">
         <f aca="false">H19*(1-Assumptions!$C$31)</f>
-        <v>180.279967205882</v>
+        <v>141.630554743382</v>
       </c>
       <c r="I20" s="50" t="n">
         <f aca="false">I19*(1-Assumptions!$C$31)</f>
-        <v>159.090271957065</v>
+        <v>124.885541927753</v>
       </c>
       <c r="J20" s="50" t="n">
         <f aca="false">J19*(1-Assumptions!$C$31)</f>
-        <v>242.861220593687</v>
+        <v>212.590034517746</v>
       </c>
       <c r="K20" s="50" t="n">
         <f aca="false">K19*(1-Assumptions!$C$31)</f>
-        <v>356.465545713695</v>
+        <v>329.675546036486</v>
       </c>
       <c r="L20" s="50" t="n">
         <f aca="false">L19*(1-Assumptions!$C$31)</f>
-        <v>454.241722494608</v>
+        <v>430.532572780279</v>
       </c>
       <c r="M20" s="50" t="n">
         <f aca="false">M19*(1-Assumptions!$C$31)</f>
-        <v>556.911503684166</v>
+        <v>535.928906186985</v>
       </c>
       <c r="N20" s="50" t="n">
         <f aca="false">N19*(1-Assumptions!$C$31)</f>
-        <v>614.810623643836</v>
+        <v>596.24102485883</v>
       </c>
       <c r="O20" s="50" t="n">
         <f aca="false">O19*(1-Assumptions!$C$31)</f>
-        <v>663.291935948977</v>
+        <v>646.857841024248</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15285,43 +15411,43 @@
       </c>
       <c r="F22" s="23" t="n">
         <f aca="false">F20+F18-F16+F21</f>
-        <v>293.922974061538</v>
+        <v>315.071474061538</v>
       </c>
       <c r="G22" s="23" t="n">
         <f aca="false">G20+G18-G16+G21</f>
-        <v>333.67747761194</v>
+        <v>352.39390011194</v>
       </c>
       <c r="H22" s="23" t="n">
         <f aca="false">H20+H18-H16+H21</f>
-        <v>253.636111806409</v>
+        <v>270.200145718909</v>
       </c>
       <c r="I22" s="23" t="n">
         <f aca="false">I20+I18-I16+I21</f>
-        <v>236.175955474968</v>
+        <v>250.835125487531</v>
       </c>
       <c r="J22" s="23" t="n">
         <f aca="false">J20+J18-J16+J21</f>
-        <v>317.630160353579</v>
+        <v>330.603525814697</v>
       </c>
       <c r="K22" s="23" t="n">
         <f aca="false">K20+K18-K16+K21</f>
-        <v>421.26864304095</v>
+        <v>432.750071474039</v>
       </c>
       <c r="L22" s="23" t="n">
         <f aca="false">L20+L18-L16+L21</f>
-        <v>517.549815629229</v>
+        <v>527.710879792513</v>
       </c>
       <c r="M22" s="23" t="n">
         <f aca="false">M20+M18-M16+M21</f>
-        <v>610.128194679734</v>
+        <v>619.120736464241</v>
       </c>
       <c r="N22" s="23" t="n">
         <f aca="false">N20+N18-N16+N21</f>
-        <v>665.781400317771</v>
+        <v>673.739799797059</v>
       </c>
       <c r="O22" s="23" t="n">
         <f aca="false">O20+O18-O16+O21</f>
-        <v>709.154359591124</v>
+        <v>716.197543130294</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15375,43 +15501,43 @@
       </c>
       <c r="F24" s="50" t="n">
         <f aca="false">F22*F23</f>
-        <v>281.682894308215</v>
+        <v>301.95068966956</v>
       </c>
       <c r="G24" s="50" t="n">
         <f aca="false">G22*G23</f>
-        <v>293.702549959579</v>
+        <v>310.176724523928</v>
       </c>
       <c r="H24" s="50" t="n">
         <f aca="false">H22*H23</f>
-        <v>205.043398925066</v>
+        <v>218.434022953876</v>
       </c>
       <c r="I24" s="50" t="n">
         <f aca="false">I22*I23</f>
-        <v>175.35746905524</v>
+        <v>186.241705541904</v>
       </c>
       <c r="J24" s="50" t="n">
         <f aca="false">J22*J23</f>
-        <v>216.602868459058</v>
+        <v>225.449850021884</v>
       </c>
       <c r="K24" s="50" t="n">
         <f aca="false">K22*K23</f>
-        <v>263.849020216302</v>
+        <v>271.04006966372</v>
       </c>
       <c r="L24" s="50" t="n">
         <f aca="false">L22*L23</f>
-        <v>297.716148789283</v>
+        <v>303.561214904543</v>
       </c>
       <c r="M24" s="50" t="n">
         <f aca="false">M22*M23</f>
-        <v>322.348171489849</v>
+        <v>327.099188450806</v>
       </c>
       <c r="N24" s="50" t="n">
         <f aca="false">N22*N23</f>
-        <v>323.064811463697</v>
+        <v>326.926557715698</v>
       </c>
       <c r="O24" s="50" t="n">
         <f aca="false">O22*O23</f>
-        <v>316.04771723259</v>
+        <v>319.186641853864</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15420,7 +15546,7 @@
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">SUM(F24:O24)</f>
-        <v>2695.41504989888</v>
+        <v>2790.06666529978</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15482,7 +15608,7 @@
       </c>
       <c r="C32" s="50" t="n">
         <f aca="false">O22*C31*O23</f>
-        <v>3134.95903333497</v>
+        <v>3166.09483834121</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15491,7 +15617,7 @@
       </c>
       <c r="C33" s="50" t="n">
         <f aca="false">O22*(1+C26)/(Assumptions!$C$33-C26)*O23</f>
-        <v>4347.02124793114</v>
+        <v>4390.19501973944</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15500,7 +15626,7 @@
       </c>
       <c r="C34" s="23" t="n">
         <f aca="false">C25+C32</f>
-        <v>5830.37408323384</v>
+        <v>5956.161503641</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15509,7 +15635,7 @@
       </c>
       <c r="C35" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
-        <v>1462</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15518,7 +15644,7 @@
       </c>
       <c r="C36" s="23" t="n">
         <f aca="false">C34+C35</f>
-        <v>7292.37408323384</v>
+        <v>7393.161503641</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15527,7 +15653,7 @@
       </c>
       <c r="C37" s="59" t="n">
         <f aca="false">C36/Assumptions!$C$12</f>
-        <v>2.26471244820927</v>
+        <v>2.2960128893295</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15536,7 +15662,7 @@
       </c>
       <c r="C38" s="35" t="n">
         <f aca="false">C37/Assumptions!$C$11-1</f>
-        <v>-0.586731305071302</v>
+        <v>-0.581019545742792</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16039,43 +16165,43 @@
       </c>
       <c r="F52" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15+F51-F53</f>
-        <v>3484</v>
+        <v>4026.505</v>
       </c>
       <c r="G52" s="50" t="n">
         <f aca="false">F52+G51-G53</f>
-        <v>3963.34</v>
+        <v>4443.456925</v>
       </c>
       <c r="H52" s="50" t="n">
         <f aca="false">G52+H51-H53</f>
-        <v>4527.5559</v>
+        <v>4952.459378625</v>
       </c>
       <c r="I52" s="50" t="n">
         <f aca="false">H52+I51-I53</f>
-        <v>4766.8869715</v>
+        <v>5142.92655008313</v>
       </c>
       <c r="J52" s="50" t="n">
         <f aca="false">I52+J51-J53</f>
-        <v>4778.6949697775</v>
+        <v>5111.48999682357</v>
       </c>
       <c r="K52" s="50" t="n">
         <f aca="false">J52+K51-K53</f>
-        <v>4749.14504825309</v>
+        <v>5043.66864718886</v>
       </c>
       <c r="L52" s="50" t="n">
         <f aca="false">K52+L51-L53</f>
-        <v>4632.99336770398</v>
+        <v>4893.64675276214</v>
       </c>
       <c r="M52" s="50" t="n">
         <f aca="false">L52+M51-M53</f>
-        <v>4490.19913041803</v>
+        <v>4720.87737619449</v>
       </c>
       <c r="N52" s="50" t="n">
         <f aca="false">M52+N51-N53</f>
-        <v>4343.82623041995</v>
+        <v>4547.97647793213</v>
       </c>
       <c r="O52" s="50" t="n">
         <f aca="false">N52+O51-O53</f>
-        <v>4214.28621392166</v>
+        <v>4394.95918296993</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16084,43 +16210,43 @@
       </c>
       <c r="F53" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15*'Balance Sheet'!F8</f>
-        <v>368</v>
+        <v>438.495</v>
       </c>
       <c r="G53" s="50" t="n">
         <f aca="false">F52*'Balance Sheet'!F8</f>
-        <v>400.66</v>
+        <v>463.048075</v>
       </c>
       <c r="H53" s="50" t="n">
         <f aca="false">G52*'Balance Sheet'!F8</f>
-        <v>455.7841</v>
+        <v>510.997546375</v>
       </c>
       <c r="I53" s="50" t="n">
         <f aca="false">H52*'Balance Sheet'!F8</f>
-        <v>520.6689285</v>
+        <v>569.532828541875</v>
       </c>
       <c r="J53" s="50" t="n">
         <f aca="false">I52*'Balance Sheet'!F8</f>
-        <v>548.1920017225</v>
+        <v>591.436553259559</v>
       </c>
       <c r="K53" s="50" t="n">
         <f aca="false">J52*'Balance Sheet'!F8</f>
-        <v>549.549921524413</v>
+        <v>587.82134963471</v>
       </c>
       <c r="L53" s="50" t="n">
         <f aca="false">K52*'Balance Sheet'!F8</f>
-        <v>546.151680549105</v>
+        <v>580.021894426719</v>
       </c>
       <c r="M53" s="50" t="n">
         <f aca="false">L52*'Balance Sheet'!F8</f>
-        <v>532.794237285958</v>
+        <v>562.769376567646</v>
       </c>
       <c r="N53" s="50" t="n">
         <f aca="false">M52*'Balance Sheet'!F8</f>
-        <v>516.372899998073</v>
+        <v>542.900898262367</v>
       </c>
       <c r="O53" s="50" t="n">
         <f aca="false">N52*'Balance Sheet'!F8</f>
-        <v>499.540016498294</v>
+        <v>523.017294962194</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16129,43 +16255,43 @@
       </c>
       <c r="F54" s="50" t="n">
         <f aca="false">F50-F53</f>
-        <v>1363.2975</v>
+        <v>1292.8025</v>
       </c>
       <c r="G54" s="50" t="n">
         <f aca="false">G50-G53</f>
-        <v>1506.27901492537</v>
+        <v>1443.89093992537</v>
       </c>
       <c r="H54" s="50" t="n">
         <f aca="false">H50-H53</f>
-        <v>1518.29832647059</v>
+        <v>1463.08488009559</v>
       </c>
       <c r="I54" s="50" t="n">
         <f aca="false">I50-I53</f>
-        <v>1785.47994038587</v>
+        <v>1736.61604034399</v>
       </c>
       <c r="J54" s="50" t="n">
         <f aca="false">J50-J53</f>
-        <v>2138.73452366813</v>
+        <v>2095.48997213107</v>
       </c>
       <c r="K54" s="50" t="n">
         <f aca="false">K50-K53</f>
-        <v>2815.78004825098</v>
+        <v>2777.50862014068</v>
       </c>
       <c r="L54" s="50" t="n">
         <f aca="false">L50-L53</f>
-        <v>3295.78994472067</v>
+        <v>3261.91973084306</v>
       </c>
       <c r="M54" s="50" t="n">
         <f aca="false">M50-M53</f>
-        <v>3491.38561611556</v>
+        <v>3461.41047683387</v>
       </c>
       <c r="N54" s="50" t="n">
         <f aca="false">N50-N53</f>
-        <v>3572.25382473848</v>
+        <v>3545.72582647419</v>
       </c>
       <c r="O54" s="50" t="n">
         <f aca="false">O50-O53</f>
-        <v>3586.19300135668</v>
+        <v>3562.71572289278</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16174,43 +16300,43 @@
       </c>
       <c r="F55" s="50" t="n">
         <f aca="false">F54*(1-Assumptions!$C$31)</f>
-        <v>954.30825</v>
+        <v>904.96175</v>
       </c>
       <c r="G55" s="50" t="n">
         <f aca="false">G54*(1-Assumptions!$C$31)</f>
-        <v>1054.39531044776</v>
+        <v>1010.72365794776</v>
       </c>
       <c r="H55" s="50" t="n">
         <f aca="false">H54*(1-Assumptions!$C$31)</f>
-        <v>1062.80882852941</v>
+        <v>1024.15941606691</v>
       </c>
       <c r="I55" s="50" t="n">
         <f aca="false">I54*(1-Assumptions!$C$31)</f>
-        <v>1249.83595827011</v>
+        <v>1215.6312282408</v>
       </c>
       <c r="J55" s="50" t="n">
         <f aca="false">J54*(1-Assumptions!$C$31)</f>
-        <v>1497.11416656769</v>
+        <v>1466.84298049175</v>
       </c>
       <c r="K55" s="50" t="n">
         <f aca="false">K54*(1-Assumptions!$C$31)</f>
-        <v>1971.04603377568</v>
+        <v>1944.25603409848</v>
       </c>
       <c r="L55" s="50" t="n">
         <f aca="false">L54*(1-Assumptions!$C$31)</f>
-        <v>2307.05296130447</v>
+        <v>2283.34381159014</v>
       </c>
       <c r="M55" s="50" t="n">
         <f aca="false">M54*(1-Assumptions!$C$31)</f>
-        <v>2443.96993128089</v>
+        <v>2422.98733378371</v>
       </c>
       <c r="N55" s="50" t="n">
         <f aca="false">N54*(1-Assumptions!$C$31)</f>
-        <v>2500.57767731694</v>
+        <v>2482.00807853193</v>
       </c>
       <c r="O55" s="50" t="n">
         <f aca="false">O54*(1-Assumptions!$C$31)</f>
-        <v>2510.33510094967</v>
+        <v>2493.90100602494</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16264,43 +16390,43 @@
       </c>
       <c r="F57" s="23" t="n">
         <f aca="false">F55+F53-F51+F56</f>
-        <v>617.417974061538</v>
+        <v>638.566474061538</v>
       </c>
       <c r="G57" s="23" t="n">
         <f aca="false">G55+G53-G51+G56</f>
-        <v>558.47707761194</v>
+        <v>577.19350011194</v>
       </c>
       <c r="H57" s="23" t="n">
         <f aca="false">H55+H53-H51+H56</f>
-        <v>493.203220188762</v>
+        <v>509.767254101262</v>
       </c>
       <c r="I57" s="23" t="n">
         <f aca="false">I55+I53-I51+I56</f>
-        <v>970.590219250927</v>
+        <v>985.24938926349</v>
       </c>
       <c r="J57" s="23" t="n">
         <f aca="false">J55+J53-J51+J56</f>
-        <v>1439.77477698584</v>
+        <v>1452.74814244696</v>
       </c>
       <c r="K57" s="23" t="n">
         <f aca="false">K55+K53-K51+K56</f>
-        <v>1924.9159553001</v>
+        <v>1936.39738373319</v>
       </c>
       <c r="L57" s="23" t="n">
         <f aca="false">L55+L53-L51+L56</f>
-        <v>2369.28264185357</v>
+        <v>2379.44370601686</v>
       </c>
       <c r="M57" s="23" t="n">
         <f aca="false">M55+M53-M51+M56</f>
-        <v>2565.95216856685</v>
+        <v>2574.94471035136</v>
       </c>
       <c r="N57" s="23" t="n">
         <f aca="false">N55+N53-N51+N56</f>
-        <v>2639.38257731501</v>
+        <v>2647.3409767943</v>
       </c>
       <c r="O57" s="23" t="n">
         <f aca="false">O55+O53-O51+O56</f>
-        <v>2639.87511744797</v>
+        <v>2646.91830098714</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16354,43 +16480,43 @@
       </c>
       <c r="F59" s="50" t="n">
         <f aca="false">F57*F58</f>
-        <v>591.706321994264</v>
+        <v>611.974117355609</v>
       </c>
       <c r="G59" s="50" t="n">
         <f aca="false">G57*G58</f>
-        <v>491.570911415722</v>
+        <v>508.045085980071</v>
       </c>
       <c r="H59" s="50" t="n">
         <f aca="false">H57*H58</f>
-        <v>398.713195483293</v>
+        <v>412.103819512104</v>
       </c>
       <c r="I59" s="50" t="n">
         <f aca="false">I57*I58</f>
-        <v>720.650177937578</v>
+        <v>731.534414424242</v>
       </c>
       <c r="J59" s="50" t="n">
         <f aca="false">J57*J58</f>
-        <v>981.831656927598</v>
+        <v>990.678638490425</v>
       </c>
       <c r="K59" s="50" t="n">
         <f aca="false">K57*K58</f>
-        <v>1205.61356083483</v>
+        <v>1212.80461028225</v>
       </c>
       <c r="L59" s="50" t="n">
         <f aca="false">L57*L58</f>
-        <v>1362.90977645961</v>
+        <v>1368.75484257487</v>
       </c>
       <c r="M59" s="50" t="n">
         <f aca="false">M57*M58</f>
-        <v>1355.66590247826</v>
+        <v>1360.41691943922</v>
       </c>
       <c r="N59" s="50" t="n">
         <f aca="false">N57*N58</f>
-        <v>1280.73814365174</v>
+        <v>1284.59988990375</v>
       </c>
       <c r="O59" s="50" t="n">
         <f aca="false">O57*O58</f>
-        <v>1176.50902566486</v>
+        <v>1179.64795028614</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16399,7 +16525,7 @@
       </c>
       <c r="C60" s="50" t="n">
         <f aca="false">SUM(F59:O59)</f>
-        <v>9565.90867284777</v>
+        <v>9660.56028824868</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16461,7 +16587,7 @@
       </c>
       <c r="C67" s="50" t="n">
         <f aca="false">O57*C66*O58</f>
-        <v>9894.28978524025</v>
+        <v>9920.68773811559</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16470,7 +16596,7 @@
       </c>
       <c r="C68" s="50" t="n">
         <f aca="false">O57*(1+C61)/(Assumptions!$C$33-C61)*O58</f>
-        <v>18903.0762803744</v>
+        <v>18953.5096644454</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16479,7 +16605,7 @@
       </c>
       <c r="C69" s="23" t="n">
         <f aca="false">C60+C67</f>
-        <v>19460.198458088</v>
+        <v>19581.2480263643</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16488,7 +16614,7 @@
       </c>
       <c r="C70" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
-        <v>1462</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16497,7 +16623,7 @@
       </c>
       <c r="C71" s="23" t="n">
         <f aca="false">C69+C70</f>
-        <v>20922.198458088</v>
+        <v>21018.2480263643</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16506,7 +16632,7 @@
       </c>
       <c r="C72" s="59" t="n">
         <f aca="false">C71/Assumptions!$C$12</f>
-        <v>6.4975771608969</v>
+        <v>6.52740621936778</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16515,7 +16641,7 @@
       </c>
       <c r="C73" s="35" t="n">
         <f aca="false">C72/Assumptions!$C$11-1</f>
-        <v>0.18568926293739</v>
+        <v>0.191132521782442</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17018,43 +17144,43 @@
       </c>
       <c r="F87" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15+F86-F88</f>
-        <v>3517</v>
+        <v>4059.505</v>
       </c>
       <c r="G87" s="50" t="n">
         <f aca="false">F87+G86-G88</f>
-        <v>4132.545</v>
+        <v>4612.661925</v>
       </c>
       <c r="H87" s="50" t="n">
         <f aca="false">G87+H86-H88</f>
-        <v>4787.302325</v>
+        <v>5212.205803625</v>
       </c>
       <c r="I87" s="50" t="n">
         <f aca="false">H87+I86-I88</f>
-        <v>5136.762557625</v>
+        <v>5512.80213620813</v>
       </c>
       <c r="J87" s="50" t="n">
         <f aca="false">I87+J86-J88</f>
-        <v>5266.03486349813</v>
+        <v>5598.82989054419</v>
       </c>
       <c r="K87" s="50" t="n">
         <f aca="false">J87+K86-K88</f>
-        <v>5260.44085419584</v>
+        <v>5554.96445313161</v>
       </c>
       <c r="L87" s="50" t="n">
         <f aca="false">K87+L86-L88</f>
-        <v>5135.49015596332</v>
+        <v>5396.14354102147</v>
       </c>
       <c r="M87" s="50" t="n">
         <f aca="false">L87+M86-M88</f>
-        <v>4974.90878802754</v>
+        <v>5205.587033804</v>
       </c>
       <c r="N87" s="50" t="n">
         <f aca="false">M87+N86-N88</f>
-        <v>4812.79427740437</v>
+        <v>5016.94452491654</v>
       </c>
       <c r="O87" s="50" t="n">
         <f aca="false">N87+O86-O88</f>
-        <v>4669.32293550287</v>
+        <v>4849.99590455114</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17063,43 +17189,43 @@
       </c>
       <c r="F88" s="50" t="n">
         <f aca="false">'Balance Sheet'!E15*'Balance Sheet'!F8</f>
-        <v>368</v>
+        <v>438.495</v>
       </c>
       <c r="G88" s="50" t="n">
         <f aca="false">F87*'Balance Sheet'!F8</f>
-        <v>404.455</v>
+        <v>466.843075</v>
       </c>
       <c r="H88" s="50" t="n">
         <f aca="false">G87*'Balance Sheet'!F8</f>
-        <v>475.242675</v>
+        <v>530.456121375</v>
       </c>
       <c r="I88" s="50" t="n">
         <f aca="false">H87*'Balance Sheet'!F8</f>
-        <v>550.539767375</v>
+        <v>599.403667416875</v>
       </c>
       <c r="J88" s="50" t="n">
         <f aca="false">I87*'Balance Sheet'!F8</f>
-        <v>590.727694126875</v>
+        <v>633.972245663935</v>
       </c>
       <c r="K88" s="50" t="n">
         <f aca="false">J87*'Balance Sheet'!F8</f>
-        <v>605.594009302284</v>
+        <v>643.865437412582</v>
       </c>
       <c r="L88" s="50" t="n">
         <f aca="false">K87*'Balance Sheet'!F8</f>
-        <v>604.950698232522</v>
+        <v>638.820912110135</v>
       </c>
       <c r="M88" s="50" t="n">
         <f aca="false">L87*'Balance Sheet'!F8</f>
-        <v>590.581367935782</v>
+        <v>620.55650721747</v>
       </c>
       <c r="N88" s="50" t="n">
         <f aca="false">M87*'Balance Sheet'!F8</f>
-        <v>572.114510623167</v>
+        <v>598.642508887461</v>
       </c>
       <c r="O88" s="50" t="n">
         <f aca="false">N87*'Balance Sheet'!F8</f>
-        <v>553.471341901503</v>
+        <v>576.948620365403</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17108,43 +17234,43 @@
       </c>
       <c r="F89" s="50" t="n">
         <f aca="false">F85-F88</f>
-        <v>1964.05833333333</v>
+        <v>1893.56333333333</v>
       </c>
       <c r="G89" s="50" t="n">
         <f aca="false">G85-G88</f>
-        <v>2590.34082089552</v>
+        <v>2527.95274589552</v>
       </c>
       <c r="H89" s="50" t="n">
         <f aca="false">H85-H88</f>
-        <v>3162.58456764706</v>
+        <v>3107.37112127206</v>
       </c>
       <c r="I89" s="50" t="n">
         <f aca="false">I85-I88</f>
-        <v>3655.08950006159</v>
+        <v>3606.22560001972</v>
       </c>
       <c r="J89" s="50" t="n">
         <f aca="false">J85-J88</f>
-        <v>4477.24058126375</v>
+        <v>4433.99602972669</v>
       </c>
       <c r="K89" s="50" t="n">
         <f aca="false">K85-K88</f>
-        <v>4830.44849618739</v>
+        <v>4792.17706807709</v>
       </c>
       <c r="L89" s="50" t="n">
         <f aca="false">L85-L88</f>
-        <v>4828.63467703725</v>
+        <v>4794.76446315964</v>
       </c>
       <c r="M89" s="50" t="n">
         <f aca="false">M85-M88</f>
-        <v>4708.42743189431</v>
+        <v>4678.45229261262</v>
       </c>
       <c r="N89" s="50" t="n">
         <f aca="false">N85-N88</f>
-        <v>4551.71333911339</v>
+        <v>4525.1853408491</v>
       </c>
       <c r="O89" s="50" t="n">
         <f aca="false">O85-O88</f>
-        <v>4481.28389023918</v>
+        <v>4457.80661177528</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17153,43 +17279,43 @@
       </c>
       <c r="F90" s="50" t="n">
         <f aca="false">F89*(1-Assumptions!$C$31)</f>
-        <v>1374.84083333333</v>
+        <v>1325.49433333333</v>
       </c>
       <c r="G90" s="50" t="n">
         <f aca="false">G89*(1-Assumptions!$C$31)</f>
-        <v>1813.23857462687</v>
+        <v>1769.56692212687</v>
       </c>
       <c r="H90" s="50" t="n">
         <f aca="false">H89*(1-Assumptions!$C$31)</f>
-        <v>2213.80919735294</v>
+        <v>2175.15978489044</v>
       </c>
       <c r="I90" s="50" t="n">
         <f aca="false">I89*(1-Assumptions!$C$31)</f>
-        <v>2558.56265004312</v>
+        <v>2524.3579200138</v>
       </c>
       <c r="J90" s="50" t="n">
         <f aca="false">J89*(1-Assumptions!$C$31)</f>
-        <v>3134.06840688463</v>
+        <v>3103.79722080868</v>
       </c>
       <c r="K90" s="50" t="n">
         <f aca="false">K89*(1-Assumptions!$C$31)</f>
-        <v>3381.31394733117</v>
+        <v>3354.52394765397</v>
       </c>
       <c r="L90" s="50" t="n">
         <f aca="false">L89*(1-Assumptions!$C$31)</f>
-        <v>3380.04427392608</v>
+        <v>3356.33512421175</v>
       </c>
       <c r="M90" s="50" t="n">
         <f aca="false">M89*(1-Assumptions!$C$31)</f>
-        <v>3295.89920232602</v>
+        <v>3274.91660482884</v>
       </c>
       <c r="N90" s="50" t="n">
         <f aca="false">N89*(1-Assumptions!$C$31)</f>
-        <v>3186.19933737937</v>
+        <v>3167.62973859437</v>
       </c>
       <c r="O90" s="50" t="n">
         <f aca="false">O89*(1-Assumptions!$C$31)</f>
-        <v>3136.89872316743</v>
+        <v>3120.4646282427</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17243,43 +17369,43 @@
       </c>
       <c r="F92" s="23" t="n">
         <f aca="false">F90+F88-F86+F91</f>
-        <v>953.981224061538</v>
+        <v>975.129724061539</v>
       </c>
       <c r="G92" s="23" t="n">
         <f aca="false">G90+G88-G86+G91</f>
-        <v>1140.44410199005</v>
+        <v>1159.16052449005</v>
       </c>
       <c r="H92" s="23" t="n">
         <f aca="false">H90+H88-H86+H91</f>
-        <v>1500.14738420544</v>
+        <v>1516.71141811794</v>
       </c>
       <c r="I92" s="23" t="n">
         <f aca="false">I90+I88-I86+I91</f>
-        <v>2147.16159559373</v>
+        <v>2161.8207656063</v>
       </c>
       <c r="J92" s="23" t="n">
         <f aca="false">J90+J88-J86+J91</f>
-        <v>2910.56901695353</v>
+        <v>2923.54238241465</v>
       </c>
       <c r="K92" s="23" t="n">
         <f aca="false">K90+K88-K86+K91</f>
-        <v>3341.33778520489</v>
+        <v>3352.81921363798</v>
       </c>
       <c r="L92" s="23" t="n">
         <f aca="false">L90+L88-L86+L91</f>
-        <v>3499.67034358717</v>
+        <v>3509.83140775045</v>
       </c>
       <c r="M92" s="23" t="n">
         <f aca="false">M90+M88-M86+M91</f>
-        <v>3464.95402740466</v>
+        <v>3473.94656918916</v>
       </c>
       <c r="N92" s="23" t="n">
         <f aca="false">N90+N88-N86+N91</f>
-        <v>3362.82819085968</v>
+        <v>3370.78659033897</v>
       </c>
       <c r="O92" s="23" t="n">
         <f aca="false">O90+O88-O86+O91</f>
-        <v>3287.6272364975</v>
+        <v>3294.67042003667</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17333,43 +17459,43 @@
       </c>
       <c r="F94" s="50" t="n">
         <f aca="false">F92*F93</f>
-        <v>914.253787637185</v>
+        <v>934.52158299853</v>
       </c>
       <c r="G94" s="50" t="n">
         <f aca="false">G92*G93</f>
-        <v>1003.81764822132</v>
+        <v>1020.29182278567</v>
       </c>
       <c r="H94" s="50" t="n">
         <f aca="false">H92*H93</f>
-        <v>1212.74260339082</v>
+        <v>1226.13322741963</v>
       </c>
       <c r="I94" s="50" t="n">
         <f aca="false">I92*I93</f>
-        <v>1594.23859341954</v>
+        <v>1605.1228299062</v>
       </c>
       <c r="J94" s="50" t="n">
         <f aca="false">J92*J93</f>
-        <v>1984.81654644636</v>
+        <v>1993.66352800919</v>
       </c>
       <c r="K94" s="50" t="n">
         <f aca="false">K92*K93</f>
-        <v>2092.74702829548</v>
+        <v>2099.9380777429</v>
       </c>
       <c r="L94" s="50" t="n">
         <f aca="false">L92*L93</f>
-        <v>2013.15572967232</v>
+        <v>2019.00079578759</v>
       </c>
       <c r="M94" s="50" t="n">
         <f aca="false">M92*M93</f>
-        <v>1830.63429090761</v>
+        <v>1835.38530786857</v>
       </c>
       <c r="N94" s="50" t="n">
         <f aca="false">N92*N93</f>
-        <v>1631.78402843089</v>
+        <v>1635.64577468289</v>
       </c>
       <c r="O94" s="50" t="n">
         <f aca="false">O92*O93</f>
-        <v>1465.19170213634</v>
+        <v>1468.33062675761</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17378,7 +17504,7 @@
       </c>
       <c r="C95" s="50" t="n">
         <f aca="false">SUM(F94:O94)</f>
-        <v>15743.3819585579</v>
+        <v>15838.0335739588</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17440,7 +17566,7 @@
       </c>
       <c r="C102" s="50" t="n">
         <f aca="false">O92*C101*O93</f>
-        <v>11563.2164191215</v>
+        <v>11587.9886483569</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17449,7 +17575,7 @@
       </c>
       <c r="C103" s="50" t="n">
         <f aca="false">O92*(1+C96)/(Assumptions!$C$33-C96)*O93</f>
-        <v>25667.9556629038</v>
+        <v>25722.9449028036</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17458,7 +17584,7 @@
       </c>
       <c r="C104" s="23" t="n">
         <f aca="false">C95+C102</f>
-        <v>27306.5983776793</v>
+        <v>27426.0222223156</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17467,7 +17593,7 @@
       </c>
       <c r="C105" s="50" t="n">
         <f aca="false">Assumptions!$C$21</f>
-        <v>1462</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17476,7 +17602,7 @@
       </c>
       <c r="C106" s="23" t="n">
         <f aca="false">C104+C105</f>
-        <v>28768.5983776793</v>
+        <v>28863.0222223156</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17485,7 +17611,7 @@
       </c>
       <c r="C107" s="59" t="n">
         <f aca="false">C106/Assumptions!$C$12</f>
-        <v>8.93434732226067</v>
+        <v>8.96367149761355</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17494,7 +17620,7 @@
       </c>
       <c r="C108" s="35" t="n">
         <f aca="false">C107/Assumptions!$C$11-1</f>
-        <v>0.630355350777494</v>
+        <v>0.635706477666707</v>
       </c>
     </row>
   </sheetData>

--- a/model/PLS_Valuation_Model_FMAA_2026.xlsx
+++ b/model/PLS_Valuation_Model_FMAA_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,8 +25,9 @@
     <sheet name="Football Field" sheetId="15" state="visible" r:id="rId17"/>
     <sheet name="ESG Value Bridge" sheetId="16" state="visible" r:id="rId18"/>
     <sheet name="Downstream Option" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="Returns" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="Sources" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="Monte Carlo" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Returns" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="Sources" sheetId="20" state="visible" r:id="rId22"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="855">
   <si>
     <t xml:space="preserve">PLS GROUP LIMITED</t>
   </si>
@@ -1843,6 +1844,180 @@
     <t xml:space="preserve">carbon position and downstream reach let it sell tonnes the others cannot. That gap is the recommendation.</t>
   </si>
   <si>
+    <t xml:space="preserve">Monte Carlo simulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,000 trials over the same FCFF mechanics as the Scenario Engine sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These results are produced by model/monte_carlo.py, which is committed alongside this workbook. They are imported values, not live formulas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed 20260906, 20,000 trials. Re-running the script with the same seed reproduces every figure on this sheet exactly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is randomised, and how</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why it is drawn that way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lognormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A commodity price forecast is wrong by a multiple, and the error persists across years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual price noise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-to-year variation around that level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disclosed and guided within an A$50/t band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2000 proceeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernoulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditioned on the price draw, not independent of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina proceeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same treatment, lower unconditional rate, only reachable after P2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60bp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CAPM inputs are prescribed by the case; the gearing weight is not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve conversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets the life of the terminal annuity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution of intrinsic value per share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs last close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilities the simulation reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intrinsic value above the A$5.48 last close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intrinsic value above our A$6.14 target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More than 20% below the last close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More than doubles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the mean and the median together. The mean at A$5.69 sits above the last close; the median at A$5.19 sits below it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The gap between them is the shape of the distribution: a long right tail from the growth options against a fat left tail from price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This does not move the target, which is a base-case point estimate. It is why the position is built over several prints.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The P2000 and Colina decisions are deliberately correlated with the price draw. Drawing them independently would fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">those projects in exactly the states where they are worth most, and it understates the answer by about four percentage points.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histogram (bin centre, share of trials)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of trials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: model/monte_carlo.py, run against the same FCFF mechanics as the Scenario Engine sheet. Percentiles are of modelled intrinsic value per share, not of a traded price.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Against the fund's benchmark and mandate</t>
   </si>
   <si>
@@ -1937,9 +2112,6 @@
   </si>
   <si>
     <t xml:space="preserve">Provenance for every input. Tags: A actual, G guidance, M market, D derived, E our estimate, C prescribed by the case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input</t>
   </si>
   <si>
     <t xml:space="preserve">Tag</t>
@@ -2438,7 +2610,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
@@ -2453,8 +2625,9 @@
     <numFmt numFmtId="175" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="176" formatCode="0.00\x"/>
     <numFmt numFmtId="177" formatCode="0.0\x;\(0.0&quot;x)&quot;;\-"/>
+    <numFmt numFmtId="178" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2751,6 +2924,22 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
+      <color rgb="FFB3261E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC77D02"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
       <color rgb="FF5A6472"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -2847,7 +3036,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="116">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3268,6 +3457,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3280,7 +3493,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6962,6 +7175,731 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF0B2545"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E79"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="6" style="0" width="11.5"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="12" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="13" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="105" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="19" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="68" t="s">
+        <v>606</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>607</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>608</v>
+      </c>
+      <c r="E10" s="68" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="19" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="68" t="s">
+        <v>634</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>356</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C21" s="106" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D21" s="35" t="n">
+        <f aca="false">C21/Assumptions!$C$11-1</f>
+        <v>0.0383211678832116</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C22" s="106" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <f aca="false">C22/Assumptions!$C$11-1</f>
+        <v>-0.0529197080291971</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <f aca="false">C24/Assumptions!$C$11-1</f>
+        <v>-0.728102189781022</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <f aca="false">C25/Assumptions!$C$11-1</f>
+        <v>-0.636861313868613</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C26" s="21" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <f aca="false">C26/Assumptions!$C$11-1</f>
+        <v>-0.428832116788321</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D27" s="24" t="n">
+        <f aca="false">C27/Assumptions!$C$11-1</f>
+        <v>0.395985401459854</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <f aca="false">C28/Assumptions!$C$11-1</f>
+        <v>0.841240875912409</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="D29" s="24" t="n">
+        <f aca="false">C29/Assumptions!$C$11-1</f>
+        <v>1.13138686131387</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="19" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="C32" s="107" t="n">
+        <v>0.4662</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C33" s="107" t="n">
+        <v>0.3931</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="C34" s="108" t="n">
+        <v>0.409</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="C35" s="109" t="n">
+        <v>0.0681</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="11" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="11" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="11" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="11" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="19" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="C45" s="68" t="s">
+        <v>656</v>
+      </c>
+      <c r="D45" s="68" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="D46" s="110" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="D47" s="110" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="D48" s="110" t="n">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="D49" s="110" t="n">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>0.0656</v>
+      </c>
+      <c r="D50" s="110" t="n">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="D51" s="110" t="n">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C52" s="26" t="n">
+        <v>0.0671</v>
+      </c>
+      <c r="D52" s="110" t="n">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C53" s="26" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="D53" s="110" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C54" s="26" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="D54" s="110" t="n">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="D55" s="110" t="n">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C56" s="26" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="D56" s="110" t="n">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C57" s="26" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="D57" s="110" t="n">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C58" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D58" s="110" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="D59" s="110" t="n">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="21" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="D60" s="110" t="n">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="21" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="D61" s="110" t="n">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="21" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="D62" s="110" t="n">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="21" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="D63" s="110" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="21" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="D64" s="110" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="21" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="C65" s="26" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="D65" s="110" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="21" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="C66" s="26" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="D66" s="110" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="21" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="C67" s="26" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="D67" s="110" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="21" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="C68" s="26" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D68" s="110" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="21" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="C69" s="26" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="D69" s="110" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="21" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="C70" s="26" t="n">
+        <v>0.0084</v>
+      </c>
+      <c r="D70" s="110" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="21" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="C71" s="26" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="D71" s="110" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="21" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C72" s="26" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="D72" s="110" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="21" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="C73" s="26" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="D73" s="110" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="21" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="C74" s="26" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="D74" s="110" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="21" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="C75" s="26" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="D75" s="110" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="21" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="C76" s="26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="D76" s="110" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="21" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="C77" s="26" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="D77" s="110" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="11" t="s">
+        <v>658</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FF8FBF3F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -6982,7 +7920,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>601</v>
+        <v>659</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6992,7 +7930,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>602</v>
+        <v>660</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -7008,7 +7946,7 @@
         <v>0.059</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>603</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7019,12 +7957,12 @@
         <v>0.079</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>605</v>
+        <v>663</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>0.02</v>
@@ -7032,7 +7970,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="19" t="s">
-        <v>606</v>
+        <v>664</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -7041,7 +7979,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>607</v>
+        <v>665</v>
       </c>
       <c r="C12" s="53" t="n">
         <f aca="false">Assumptions!$C$11</f>
@@ -7050,7 +7988,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>608</v>
+        <v>666</v>
       </c>
       <c r="C13" s="53" t="n">
         <f aca="false">'Football Field'!$C$16</f>
@@ -7059,7 +7997,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>609</v>
+        <v>667</v>
       </c>
       <c r="C14" s="24" t="n">
         <f aca="false">'Football Field'!$C$18</f>
@@ -7068,7 +8006,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>610</v>
+        <v>668</v>
       </c>
       <c r="C15" s="24" t="n">
         <f aca="false">'Income Statement'!F25</f>
@@ -7077,7 +8015,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>611</v>
+        <v>669</v>
       </c>
       <c r="C16" s="35" t="n">
         <f aca="false">'Football Field'!$C$20</f>
@@ -7086,7 +8024,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>612</v>
+        <v>670</v>
       </c>
       <c r="C17" s="35" t="n">
         <f aca="false">C16-C7</f>
@@ -7095,7 +8033,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="19" t="s">
-        <v>613</v>
+        <v>671</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
@@ -7104,7 +8042,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>614</v>
+        <v>672</v>
       </c>
       <c r="C20" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$37</f>
@@ -7113,7 +8051,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>615</v>
+        <v>673</v>
       </c>
       <c r="C21" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$72</f>
@@ -7122,7 +8060,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>616</v>
+        <v>674</v>
       </c>
       <c r="C22" s="53" t="n">
         <f aca="false">'Scenario Engine'!$C$107</f>
@@ -7131,7 +8069,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>617</v>
+        <v>675</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">C20/Assumptions!$C$11-1</f>
@@ -7140,7 +8078,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>618</v>
+        <v>676</v>
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">C22/Assumptions!$C$11-1</f>
@@ -7149,19 +8087,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="C25" s="105" t="n">
+        <v>677</v>
+      </c>
+      <c r="C25" s="111" t="n">
         <f aca="false">IFERROR(ABS(C24/C23),0)</f>
         <v>1.09412236184585</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>620</v>
+        <v>678</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="19" t="s">
-        <v>621</v>
+        <v>679</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -7170,18 +8108,18 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>622</v>
+        <v>680</v>
       </c>
       <c r="C28" s="21" t="n">
         <v>1.91</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>623</v>
+        <v>681</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>624</v>
+        <v>682</v>
       </c>
       <c r="C29" s="53" t="n">
         <f aca="false">C20</f>
@@ -7190,7 +8128,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>625</v>
+        <v>683</v>
       </c>
       <c r="C30" s="35" t="n">
         <f aca="false">C29/C28-1</f>
@@ -7199,870 +8137,27 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="11" t="s">
-        <v>626</v>
+        <v>684</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="11" t="s">
-        <v>627</v>
+        <v>685</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="11" t="s">
-        <v>628</v>
+        <v>686</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="11" t="s">
-        <v>629</v>
+        <v>687</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>630</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF5A6472"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:E67"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="6" style="0" width="11.5"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="12" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="68" t="s">
-        <v>633</v>
-      </c>
-      <c r="C6" s="68" t="s">
-        <v>426</v>
-      </c>
-      <c r="D6" s="68" t="s">
-        <v>634</v>
-      </c>
-      <c r="E6" s="68" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="106" t="s">
-        <v>636</v>
-      </c>
-      <c r="D7" s="107" t="s">
-        <v>637</v>
-      </c>
-      <c r="E7" s="75" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="106" t="s">
-        <v>639</v>
-      </c>
-      <c r="D8" s="107" t="s">
-        <v>637</v>
-      </c>
-      <c r="E8" s="75" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="106" t="s">
-        <v>641</v>
-      </c>
-      <c r="D9" s="107" t="s">
-        <v>637</v>
-      </c>
-      <c r="E9" s="75" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="C10" s="106" t="s">
-        <v>644</v>
-      </c>
-      <c r="D10" s="107" t="s">
-        <v>637</v>
-      </c>
-      <c r="E10" s="75" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="C11" s="106" t="s">
-        <v>647</v>
-      </c>
-      <c r="D11" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>650</v>
-      </c>
-      <c r="C12" s="106" t="s">
-        <v>651</v>
-      </c>
-      <c r="D12" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E12" s="75" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="C13" s="106" t="s">
-        <v>654</v>
-      </c>
-      <c r="D13" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E13" s="75" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="C14" s="106" t="s">
-        <v>657</v>
-      </c>
-      <c r="D14" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E14" s="75" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="C15" s="106" t="s">
-        <v>661</v>
-      </c>
-      <c r="D15" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E15" s="75" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="C16" s="106" t="s">
-        <v>664</v>
-      </c>
-      <c r="D16" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E16" s="75" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="C17" s="106" t="s">
-        <v>667</v>
-      </c>
-      <c r="D17" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E17" s="75" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="C18" s="106" t="s">
-        <v>670</v>
-      </c>
-      <c r="D18" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E18" s="75" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="C19" s="106" t="s">
-        <v>672</v>
-      </c>
-      <c r="D19" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E19" s="75" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="C20" s="106" t="s">
-        <v>675</v>
-      </c>
-      <c r="D20" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="C21" s="106" t="s">
-        <v>678</v>
-      </c>
-      <c r="D21" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E21" s="75" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="C22" s="106" t="s">
-        <v>681</v>
-      </c>
-      <c r="D22" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E22" s="75" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="C23" s="106" t="s">
-        <v>684</v>
-      </c>
-      <c r="D23" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E23" s="75" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="s">
-        <v>686</v>
-      </c>
-      <c r="C24" s="106" t="s">
-        <v>687</v>
-      </c>
-      <c r="D24" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E24" s="75" t="s">
         <v>688</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C25" s="106" t="s">
-        <v>689</v>
-      </c>
-      <c r="D25" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
-        <v>691</v>
-      </c>
-      <c r="C26" s="106" t="s">
-        <v>692</v>
-      </c>
-      <c r="D26" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E26" s="75" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
-        <v>694</v>
-      </c>
-      <c r="C27" s="106" t="s">
-        <v>695</v>
-      </c>
-      <c r="D27" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E27" s="75" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="C28" s="106" t="s">
-        <v>697</v>
-      </c>
-      <c r="D28" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E28" s="75" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="C29" s="106" t="s">
-        <v>699</v>
-      </c>
-      <c r="D29" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E29" s="75" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="C30" s="106" t="s">
-        <v>701</v>
-      </c>
-      <c r="D30" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E30" s="75" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5" t="s">
-        <v>703</v>
-      </c>
-      <c r="C31" s="106" t="s">
-        <v>704</v>
-      </c>
-      <c r="D31" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E31" s="75" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="C32" s="106" t="s">
-        <v>707</v>
-      </c>
-      <c r="D32" s="109" t="s">
-        <v>708</v>
-      </c>
-      <c r="E32" s="75" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="C33" s="106" t="s">
-        <v>711</v>
-      </c>
-      <c r="D33" s="109" t="s">
-        <v>708</v>
-      </c>
-      <c r="E33" s="75" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="C34" s="106" t="s">
-        <v>714</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>708</v>
-      </c>
-      <c r="E34" s="75" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="C35" s="106" t="s">
-        <v>717</v>
-      </c>
-      <c r="D35" s="109" t="s">
-        <v>708</v>
-      </c>
-      <c r="E35" s="75" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="C36" s="106" t="s">
-        <v>720</v>
-      </c>
-      <c r="D36" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E36" s="75" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="C37" s="106" t="s">
-        <v>723</v>
-      </c>
-      <c r="D37" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E37" s="75" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="C38" s="106" t="s">
-        <v>726</v>
-      </c>
-      <c r="D38" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E38" s="75" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="C39" s="106" t="s">
-        <v>729</v>
-      </c>
-      <c r="D39" s="109" t="s">
-        <v>708</v>
-      </c>
-      <c r="E39" s="75" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="C40" s="106" t="s">
-        <v>732</v>
-      </c>
-      <c r="D40" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E40" s="75" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="C41" s="106" t="s">
-        <v>735</v>
-      </c>
-      <c r="D41" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E41" s="75" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="C42" s="106" t="s">
-        <v>738</v>
-      </c>
-      <c r="D42" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E42" s="75" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="C43" s="106" t="s">
-        <v>741</v>
-      </c>
-      <c r="D43" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E43" s="75" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="5" t="s">
-        <v>743</v>
-      </c>
-      <c r="C44" s="106" t="s">
-        <v>744</v>
-      </c>
-      <c r="D44" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E44" s="75" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="5" t="s">
-        <v>746</v>
-      </c>
-      <c r="C45" s="106" t="s">
-        <v>747</v>
-      </c>
-      <c r="D45" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E45" s="75" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="C46" s="106" t="s">
-        <v>750</v>
-      </c>
-      <c r="D46" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E46" s="75" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="C47" s="106" t="s">
-        <v>753</v>
-      </c>
-      <c r="D47" s="109" t="s">
-        <v>658</v>
-      </c>
-      <c r="E47" s="75" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="C48" s="106" t="s">
-        <v>756</v>
-      </c>
-      <c r="D48" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E48" s="75" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="C49" s="106" t="s">
-        <v>759</v>
-      </c>
-      <c r="D49" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E49" s="75" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="C50" s="106" t="s">
-        <v>762</v>
-      </c>
-      <c r="D50" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E50" s="75" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="C51" s="106" t="s">
-        <v>765</v>
-      </c>
-      <c r="D51" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E51" s="75" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="C52" s="106" t="s">
-        <v>768</v>
-      </c>
-      <c r="D52" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E52" s="75" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="C53" s="106" t="s">
-        <v>771</v>
-      </c>
-      <c r="D53" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E53" s="75" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="C54" s="106" t="s">
-        <v>774</v>
-      </c>
-      <c r="D54" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E54" s="75" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="C55" s="106" t="s">
-        <v>777</v>
-      </c>
-      <c r="D55" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E55" s="75" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="C56" s="106" t="s">
-        <v>780</v>
-      </c>
-      <c r="D56" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E56" s="75" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="C57" s="106" t="s">
-        <v>783</v>
-      </c>
-      <c r="D57" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E57" s="75" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="C58" s="106" t="s">
-        <v>786</v>
-      </c>
-      <c r="D58" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E58" s="75" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="C59" s="106" t="s">
-        <v>789</v>
-      </c>
-      <c r="D59" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E59" s="75" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="C60" s="106" t="s">
-        <v>791</v>
-      </c>
-      <c r="D60" s="108" t="s">
-        <v>648</v>
-      </c>
-      <c r="E60" s="75" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="11" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="11" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="11" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="11" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="11" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="11" t="s">
-        <v>797</v>
       </c>
     </row>
   </sheetData>
@@ -8629,6 +8724,849 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF5A6472"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E67"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="6" style="0" width="11.5"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="12" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="13" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="68" t="s">
+        <v>606</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>426</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>691</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="112" t="s">
+        <v>693</v>
+      </c>
+      <c r="D7" s="113" t="s">
+        <v>694</v>
+      </c>
+      <c r="E7" s="75" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="112" t="s">
+        <v>696</v>
+      </c>
+      <c r="D8" s="113" t="s">
+        <v>694</v>
+      </c>
+      <c r="E8" s="75" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="112" t="s">
+        <v>698</v>
+      </c>
+      <c r="D9" s="113" t="s">
+        <v>694</v>
+      </c>
+      <c r="E9" s="75" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C10" s="112" t="s">
+        <v>701</v>
+      </c>
+      <c r="D10" s="113" t="s">
+        <v>694</v>
+      </c>
+      <c r="E10" s="75" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="C11" s="112" t="s">
+        <v>704</v>
+      </c>
+      <c r="D11" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E11" s="75" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="C12" s="112" t="s">
+        <v>708</v>
+      </c>
+      <c r="D12" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E12" s="75" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C13" s="112" t="s">
+        <v>711</v>
+      </c>
+      <c r="D13" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E13" s="75" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="C14" s="112" t="s">
+        <v>714</v>
+      </c>
+      <c r="D14" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E14" s="75" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="C15" s="112" t="s">
+        <v>718</v>
+      </c>
+      <c r="D15" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E15" s="75" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="C16" s="112" t="s">
+        <v>721</v>
+      </c>
+      <c r="D16" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E16" s="75" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="C17" s="112" t="s">
+        <v>724</v>
+      </c>
+      <c r="D17" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E17" s="75" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="C18" s="112" t="s">
+        <v>727</v>
+      </c>
+      <c r="D18" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E18" s="75" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="C19" s="112" t="s">
+        <v>729</v>
+      </c>
+      <c r="D19" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E19" s="75" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="C20" s="112" t="s">
+        <v>732</v>
+      </c>
+      <c r="D20" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E20" s="75" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C21" s="112" t="s">
+        <v>735</v>
+      </c>
+      <c r="D21" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E21" s="75" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="C22" s="112" t="s">
+        <v>738</v>
+      </c>
+      <c r="D22" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E22" s="75" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="C23" s="112" t="s">
+        <v>741</v>
+      </c>
+      <c r="D23" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E23" s="75" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="C24" s="112" t="s">
+        <v>744</v>
+      </c>
+      <c r="D24" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="112" t="s">
+        <v>746</v>
+      </c>
+      <c r="D25" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="C26" s="112" t="s">
+        <v>749</v>
+      </c>
+      <c r="D26" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E26" s="75" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="C27" s="112" t="s">
+        <v>752</v>
+      </c>
+      <c r="D27" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E27" s="75" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="C28" s="112" t="s">
+        <v>754</v>
+      </c>
+      <c r="D28" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E28" s="75" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="C29" s="112" t="s">
+        <v>756</v>
+      </c>
+      <c r="D29" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E29" s="75" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="C30" s="112" t="s">
+        <v>758</v>
+      </c>
+      <c r="D30" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E30" s="75" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="C31" s="112" t="s">
+        <v>761</v>
+      </c>
+      <c r="D31" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E31" s="75" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="C32" s="112" t="s">
+        <v>764</v>
+      </c>
+      <c r="D32" s="115" t="s">
+        <v>765</v>
+      </c>
+      <c r="E32" s="75" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C33" s="112" t="s">
+        <v>768</v>
+      </c>
+      <c r="D33" s="115" t="s">
+        <v>765</v>
+      </c>
+      <c r="E33" s="75" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="C34" s="112" t="s">
+        <v>771</v>
+      </c>
+      <c r="D34" s="115" t="s">
+        <v>765</v>
+      </c>
+      <c r="E34" s="75" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="C35" s="112" t="s">
+        <v>774</v>
+      </c>
+      <c r="D35" s="115" t="s">
+        <v>765</v>
+      </c>
+      <c r="E35" s="75" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C36" s="112" t="s">
+        <v>777</v>
+      </c>
+      <c r="D36" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E36" s="75" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="C37" s="112" t="s">
+        <v>780</v>
+      </c>
+      <c r="D37" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E37" s="75" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C38" s="112" t="s">
+        <v>783</v>
+      </c>
+      <c r="D38" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E38" s="75" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C39" s="112" t="s">
+        <v>786</v>
+      </c>
+      <c r="D39" s="115" t="s">
+        <v>765</v>
+      </c>
+      <c r="E39" s="75" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="C40" s="112" t="s">
+        <v>789</v>
+      </c>
+      <c r="D40" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E40" s="75" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="C41" s="112" t="s">
+        <v>792</v>
+      </c>
+      <c r="D41" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E41" s="75" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="C42" s="112" t="s">
+        <v>795</v>
+      </c>
+      <c r="D42" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E42" s="75" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="C43" s="112" t="s">
+        <v>798</v>
+      </c>
+      <c r="D43" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E43" s="75" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="C44" s="112" t="s">
+        <v>801</v>
+      </c>
+      <c r="D44" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E44" s="75" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="C45" s="112" t="s">
+        <v>804</v>
+      </c>
+      <c r="D45" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E45" s="75" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="C46" s="112" t="s">
+        <v>807</v>
+      </c>
+      <c r="D46" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E46" s="75" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C47" s="112" t="s">
+        <v>810</v>
+      </c>
+      <c r="D47" s="115" t="s">
+        <v>715</v>
+      </c>
+      <c r="E47" s="75" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C48" s="112" t="s">
+        <v>813</v>
+      </c>
+      <c r="D48" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E48" s="75" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C49" s="112" t="s">
+        <v>816</v>
+      </c>
+      <c r="D49" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E49" s="75" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="C50" s="112" t="s">
+        <v>819</v>
+      </c>
+      <c r="D50" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E50" s="75" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="C51" s="112" t="s">
+        <v>822</v>
+      </c>
+      <c r="D51" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E51" s="75" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="C52" s="112" t="s">
+        <v>825</v>
+      </c>
+      <c r="D52" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E52" s="75" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="C53" s="112" t="s">
+        <v>828</v>
+      </c>
+      <c r="D53" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E53" s="75" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="C54" s="112" t="s">
+        <v>831</v>
+      </c>
+      <c r="D54" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E54" s="75" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="C55" s="112" t="s">
+        <v>834</v>
+      </c>
+      <c r="D55" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E55" s="75" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="C56" s="112" t="s">
+        <v>837</v>
+      </c>
+      <c r="D56" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E56" s="75" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="C57" s="112" t="s">
+        <v>840</v>
+      </c>
+      <c r="D57" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E57" s="75" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C58" s="112" t="s">
+        <v>843</v>
+      </c>
+      <c r="D58" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E58" s="75" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="C59" s="112" t="s">
+        <v>846</v>
+      </c>
+      <c r="D59" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E59" s="75" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C60" s="112" t="s">
+        <v>848</v>
+      </c>
+      <c r="D60" s="114" t="s">
+        <v>705</v>
+      </c>
+      <c r="E60" s="75" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="11" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="11" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="11" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="11" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="11" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="11" t="s">
+        <v>854</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
